--- a/Corporate File.xlsx
+++ b/Corporate File.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gotekna-my.sharepoint.com/personal/robert_tekna_com_au/Documents/Accounts - Internal/Corporate File/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robertharder/GitHub/teeem/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1759" documentId="8_{41BE9946-5620-4396-A678-DE12D60591BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC059A41-452E-FC41-B324-E4E0420BC1FD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4777C4-2F5D-7E44-905A-15A3FD9EB5F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45010" yWindow="1990" windowWidth="28210" windowHeight="16600" tabRatio="812" firstSheet="7" activeTab="11" xr2:uid="{951165B7-8C6F-4A78-8B71-C16B81CE59C4}"/>
+    <workbookView xWindow="30240" yWindow="-3540" windowWidth="38400" windowHeight="21000" tabRatio="812" activeTab="3" xr2:uid="{951165B7-8C6F-4A78-8B71-C16B81CE59C4}"/>
   </bookViews>
   <sheets>
     <sheet name="2022 Charity (2)" sheetId="11" state="hidden" r:id="rId1"/>
@@ -61,7 +61,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2022 Team Harder (2)'!$A$1:$Z$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'All Companies'!$A$1:$M$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Co Invest Capital'!$B$26:$H$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Co Invest Homes'!$B$30:$H$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Co Invest Homes'!$B$31:$H$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Director Details'!$B$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Director Details (2)'!$B$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Gen2612'!$A$26:$G$61</definedName>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4965" uniqueCount="1505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4966" uniqueCount="1505">
   <si>
     <t>Group</t>
   </si>
@@ -4769,23 +4769,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="17">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
-    <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;* #,##0.0000_-;\-&quot;$&quot;* #,##0.0000_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.0000%"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;* #,##0.0000_-;\-&quot;$&quot;* #,##0.0000_-;_-&quot;$&quot;* &quot;-&quot;????_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;* #,##0.000_-;\-&quot;$&quot;* #,##0.000_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;* #,##0.00000_-;\-&quot;$&quot;* #,##0.00000_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="_-&quot;$&quot;* #,##0.0000000_-;\-&quot;$&quot;* #,##0.0000000_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="0.0%"/>
-    <numFmt numFmtId="174" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="175" formatCode="000000"/>
-    <numFmt numFmtId="176" formatCode="_-[$$-C09]* #,##0.00_-;\-[$$-C09]* #,##0.00_-;_-[$$-C09]* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;* #,##0.0000_-;\-&quot;$&quot;* #,##0.0000_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="0.0000%"/>
+    <numFmt numFmtId="172" formatCode="_-&quot;$&quot;* #,##0.0000_-;\-&quot;$&quot;* #,##0.0000_-;_-&quot;$&quot;* &quot;-&quot;????_-;_-@_-"/>
+    <numFmt numFmtId="173" formatCode="_-&quot;$&quot;* #,##0.000_-;\-&quot;$&quot;* #,##0.000_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="_-&quot;$&quot;* #,##0.00000_-;\-&quot;$&quot;* #,##0.00000_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="175" formatCode="_-&quot;$&quot;* #,##0.0000000_-;\-&quot;$&quot;* #,##0.0000000_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="000000"/>
+    <numFmt numFmtId="179" formatCode="_-[$$-C09]* #,##0.00_-;\-[$$-C09]* #,##0.00_-;_-[$$-C09]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="32">
     <font>
@@ -6183,11 +6183,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -6204,10 +6204,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6240,8 +6240,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -6264,7 +6264,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6284,8 +6284,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6304,7 +6304,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6323,7 +6323,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6340,7 +6340,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6394,7 +6394,7 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="10" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6434,7 +6434,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6446,7 +6446,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -6455,7 +6455,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6473,7 +6473,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6483,7 +6483,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="4"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6503,11 +6503,11 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="14" fillId="10" borderId="10" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -6539,7 +6539,7 @@
     <xf numFmtId="14" fontId="15" fillId="12" borderId="10" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="12" borderId="10" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="15" fillId="12" borderId="10" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="10" xfId="6" applyBorder="1" applyAlignment="1">
@@ -6555,48 +6555,48 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="7" applyFont="1"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="7" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="35" xfId="7" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="13" borderId="35" xfId="8" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="35" xfId="7" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="13" borderId="35" xfId="8" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="14" borderId="0" xfId="9" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="17" fillId="14" borderId="0" xfId="9" applyNumberFormat="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="14" borderId="0" xfId="9" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="17" fillId="14" borderId="0" xfId="9" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6663,22 +6663,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="47" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="47" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6699,33 +6699,33 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6784,7 +6784,7 @@
     <xf numFmtId="0" fontId="14" fillId="10" borderId="18" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="10" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="10" xfId="5" applyBorder="1" applyAlignment="1">
@@ -6796,7 +6796,7 @@
     <xf numFmtId="0" fontId="14" fillId="10" borderId="10" xfId="5" applyBorder="1"/>
     <xf numFmtId="2" fontId="14" fillId="10" borderId="10" xfId="5" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="5" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="10" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="10" borderId="10" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="14" fillId="10" borderId="10" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -6820,24 +6820,24 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="14" fillId="10" borderId="10" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="14" fillId="10" borderId="10" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="14" fillId="10" borderId="10" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="14" fillId="10" borderId="10" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="65" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="65" xfId="11" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -6860,7 +6860,7 @@
     <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -6891,17 +6891,17 @@
     <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
@@ -6910,7 +6910,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="6" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6931,16 +6931,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6952,10 +6952,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="3" fillId="2" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="2" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6983,10 +6983,10 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="18" xfId="5" applyBorder="1"/>
     <xf numFmtId="2" fontId="14" fillId="10" borderId="18" xfId="5" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="14" fillId="10" borderId="18" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="14" fillId="10" borderId="18" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="0" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="10" borderId="0" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="14" fillId="10" borderId="0" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -7017,7 +7017,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="18" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7033,7 +7033,7 @@
     <xf numFmtId="2" fontId="14" fillId="10" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="14" fillId="10" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="14" fillId="10" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="16" borderId="65" xfId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7054,7 +7054,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="82" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="82" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="82" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1" applyAlignment="1">
@@ -7368,7 +7368,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="177" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+      <numFmt numFmtId="180" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -7533,7 +7533,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="167" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -7574,7 +7574,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="177" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+      <numFmt numFmtId="180" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -7759,7 +7759,7 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -8041,7 +8041,7 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -8856,7 +8856,7 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -8931,7 +8931,7 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -9102,8 +9102,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="62" xr:uid="{A6AD0D40-0E45-4074-821F-6EBAB9DBE759}" name="Table16115963" displayName="Table16115963" ref="B70:Q97" totalsRowShown="0" headerRowDxfId="340" dataDxfId="339">
-  <autoFilter ref="B70:Q97" xr:uid="{25AF81B3-DBAC-40C5-8E99-FA8DBF67F1CB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="62" xr:uid="{A6AD0D40-0E45-4074-821F-6EBAB9DBE759}" name="Table16115963" displayName="Table16115963" ref="B71:Q98" totalsRowShown="0" headerRowDxfId="340" dataDxfId="339">
+  <autoFilter ref="B71:Q98" xr:uid="{25AF81B3-DBAC-40C5-8E99-FA8DBF67F1CB}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{46950132-FAFD-487E-8526-4772C377C699}" name="Date" dataDxfId="338"/>
     <tableColumn id="13" xr3:uid="{186AD468-1D77-4092-8ED2-99D12A8FC84A}" name="Issue, transfer,share split, buy back or Cancelation" dataDxfId="337"/>
@@ -9324,8 +9324,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="63" xr:uid="{414AA4D4-F8C8-4445-BCA1-233FB194D8D0}" name="Table27126064" displayName="Table27126064" ref="B100:G106" totalsRowShown="0">
-  <autoFilter ref="B100:G106" xr:uid="{4E2287C6-AD1B-45AF-9498-357AC56F07FC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="63" xr:uid="{414AA4D4-F8C8-4445-BCA1-233FB194D8D0}" name="Table27126064" displayName="Table27126064" ref="B101:G107" totalsRowShown="0">
+  <autoFilter ref="B101:G107" xr:uid="{4E2287C6-AD1B-45AF-9498-357AC56F07FC}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{562E9864-5C5A-4072-87DB-46B658943EDE}" name="From"/>
     <tableColumn id="2" xr3:uid="{B5B54E19-8BC8-469E-9DCE-332358E66028}" name="To"/>
@@ -9530,8 +9530,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="64" xr:uid="{A3BABCD1-B767-4A4B-9948-7C2BE4BAAB12}" name="Table79136165" displayName="Table79136165" ref="B109:H127" totalsRowShown="0">
-  <autoFilter ref="B109:H127" xr:uid="{D74208A7-2477-458E-B7C7-42B491F56C62}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="64" xr:uid="{A3BABCD1-B767-4A4B-9948-7C2BE4BAAB12}" name="Table79136165" displayName="Table79136165" ref="B110:H128" totalsRowShown="0">
+  <autoFilter ref="B110:H128" xr:uid="{D74208A7-2477-458E-B7C7-42B491F56C62}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{CF3BDAD9-967C-480E-8285-857C72C1A09F}" name="Item"/>
     <tableColumn id="2" xr3:uid="{0FC554B2-CC29-4A8A-B9B8-E0302BBC254E}" name="Purchase Date"/>
@@ -9736,13 +9736,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="65" xr:uid="{E87FADDB-8012-4477-85BD-817BE8892B33}" name="Table96266" displayName="Table96266" ref="B30:H68" totalsRowShown="0" headerRowDxfId="321">
-  <autoFilter ref="B30:H68" xr:uid="{C023E9AF-2873-48A9-9B76-629859D4DFE7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="65" xr:uid="{E87FADDB-8012-4477-85BD-817BE8892B33}" name="Table96266" displayName="Table96266" ref="B31:H69" totalsRowShown="0" headerRowDxfId="321">
+  <autoFilter ref="B31:H69" xr:uid="{C023E9AF-2873-48A9-9B76-629859D4DFE7}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{340DBADC-971F-48A3-92EA-C0EACA99570F}" name="Company Register"/>
     <tableColumn id="2" xr3:uid="{E409C3E0-C315-4AC3-8891-2C43DD68ACC7}" name="Type"/>
     <tableColumn id="3" xr3:uid="{63091695-11E0-4F76-B7A2-AFC1136D8240}" name="Folder">
-      <calculatedColumnFormula>VLOOKUP(C31,'Document Type'!$B$6:$C$34,2,FALSE)</calculatedColumnFormula>
+      <calculatedColumnFormula>VLOOKUP(C32,'Document Type'!$B$6:$C$34,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{5DAA1A38-DBCE-45D2-962C-885DC77C44DC}" name="Date"/>
     <tableColumn id="5" xr3:uid="{0E0E1B5F-F329-4544-99CC-0D45490FDC88}" name="Manual"/>
@@ -10650,35 +10650,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E043BA7F-D218-4A3D-9D21-A1F0DAE1CF05}">
   <dimension ref="A1:U11"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.3046875" style="44" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" style="44" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="44" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" style="44" customWidth="1"/>
-    <col min="4" max="4" width="57.3046875" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.15234375" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.15234375" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.1640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1640625" style="28" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="44" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.15234375" style="46" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.15234375" style="44" customWidth="1"/>
-    <col min="10" max="10" width="16.69140625" style="44" customWidth="1"/>
+    <col min="8" max="8" width="26.1640625" style="46" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1640625" style="44" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" style="44" customWidth="1"/>
     <col min="11" max="11" width="16" style="44" customWidth="1"/>
-    <col min="12" max="12" width="17.69140625" style="44" customWidth="1"/>
-    <col min="13" max="13" width="14.15234375" style="44" customWidth="1"/>
-    <col min="14" max="14" width="18.3046875" style="47" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.3046875" style="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.15234375" style="48" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.69140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.15234375" style="44" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="57.3046875" style="44" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="55.15234375" style="49" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="55.15234375" style="14" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="9.15234375" style="14"/>
-    <col min="25" max="25" width="31.69140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.15234375" style="14"/>
+    <col min="12" max="12" width="17.6640625" style="44" customWidth="1"/>
+    <col min="13" max="13" width="14.1640625" style="44" customWidth="1"/>
+    <col min="14" max="14" width="18.33203125" style="47" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.1640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.6640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.1640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="57.33203125" style="44" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="55.1640625" style="49" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="55.1640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="9.1640625" style="14"/>
+    <col min="25" max="25" width="31.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.1640625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.8" customHeight="1" thickBot="1">
+    <row r="1" spans="1:21" ht="14.75" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10739,7 +10739,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="14.8" customHeight="1">
+    <row r="2" spans="1:21" ht="14.75" customHeight="1">
       <c r="A2" s="64" t="s">
         <v>19</v>
       </c>
@@ -10800,7 +10800,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" ht="16">
       <c r="A3" s="15" t="s">
         <v>19</v>
       </c>
@@ -10853,7 +10853,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="14.8" customHeight="1">
+    <row r="4" spans="1:21" ht="14.75" customHeight="1">
       <c r="A4" s="15" t="s">
         <v>19</v>
       </c>
@@ -10916,7 +10916,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="14.8" customHeight="1">
+    <row r="5" spans="1:21" ht="14.75" customHeight="1">
       <c r="A5" s="15" t="s">
         <v>19</v>
       </c>
@@ -10967,7 +10967,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="14.8" customHeight="1">
+    <row r="6" spans="1:21" ht="14.75" customHeight="1">
       <c r="A6" s="15" t="s">
         <v>19</v>
       </c>
@@ -11032,7 +11032,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="14.8" customHeight="1">
+    <row r="7" spans="1:21" ht="14.75" customHeight="1">
       <c r="A7" s="15" t="s">
         <v>19</v>
       </c>
@@ -11087,7 +11087,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="14.8" customHeight="1">
+    <row r="9" spans="1:21" ht="14.75" customHeight="1">
       <c r="A9" s="15" t="s">
         <v>19</v>
       </c>
@@ -11138,7 +11138,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="14.8" customHeight="1">
+    <row r="10" spans="1:21" ht="14.75" customHeight="1">
       <c r="A10" s="15" t="s">
         <v>19</v>
       </c>
@@ -11219,24 +11219,24 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3877225-7962-435D-92DD-D2AF8F31F0F8}">
   <dimension ref="A1:P100"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="38.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.15234375" customWidth="1"/>
-    <col min="4" max="4" width="18.3046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.69140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.4609375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.4609375" customWidth="1"/>
-    <col min="10" max="10" width="76.3046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.69140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="34.15234375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="32.3046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="40.3046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.5" customWidth="1"/>
+    <col min="10" max="10" width="76.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="34.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -11244,8 +11244,8 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" thickBot="1"/>
-    <row r="3" spans="1:9" ht="26.8" customHeight="1" thickBot="1">
+    <row r="2" spans="1:9" ht="16" thickBot="1"/>
+    <row r="3" spans="1:9" ht="26.75" customHeight="1" thickBot="1">
       <c r="A3" s="373" t="s">
         <v>404</v>
       </c>
@@ -11259,7 +11259,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="17.8" customHeight="1">
+    <row r="4" spans="1:9" ht="17.75" customHeight="1">
       <c r="A4" s="245" t="s">
         <v>201</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.9">
+    <row r="26" spans="1:9" ht="16">
       <c r="A26" s="170" t="s">
         <v>262</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15.9">
+    <row r="64" spans="1:7" ht="16">
       <c r="A64" s="170" t="s">
         <v>289</v>
       </c>
@@ -12315,7 +12315,7 @@
       <c r="O69" s="93"/>
       <c r="P69" s="93"/>
     </row>
-    <row r="71" spans="1:16" ht="15.9">
+    <row r="71" spans="1:16" ht="16">
       <c r="A71" s="170" t="s">
         <v>305</v>
       </c>
@@ -12426,7 +12426,7 @@
     <row r="78" spans="1:16" outlineLevel="1">
       <c r="C78" s="112"/>
     </row>
-    <row r="80" spans="1:16" ht="15.9">
+    <row r="80" spans="1:16" ht="16">
       <c r="A80" s="170" t="s">
         <v>309</v>
       </c>
@@ -12614,19 +12614,19 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{936974DC-448B-4453-B525-7E5DB9FEEDB8}">
   <dimension ref="A1:P121"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="38.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.15234375" customWidth="1"/>
-    <col min="4" max="4" width="18.3046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.69140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.4609375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.4609375" customWidth="1"/>
-    <col min="10" max="10" width="76.3046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.5" customWidth="1"/>
+    <col min="10" max="10" width="76.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -12634,8 +12634,8 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" thickBot="1"/>
-    <row r="3" spans="1:9" ht="26.8" customHeight="1" thickBot="1">
+    <row r="2" spans="1:9" ht="16" thickBot="1"/>
+    <row r="3" spans="1:9" ht="26.75" customHeight="1" thickBot="1">
       <c r="A3" s="373" t="s">
         <v>441</v>
       </c>
@@ -12649,7 +12649,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="17.8" customHeight="1">
+    <row r="4" spans="1:9" ht="17.75" customHeight="1">
       <c r="A4" s="245" t="s">
         <v>201</v>
       </c>
@@ -12834,7 +12834,7 @@
       <c r="F17" s="255"/>
       <c r="G17" s="255"/>
     </row>
-    <row r="18" spans="1:9" ht="15.9">
+    <row r="18" spans="1:9" ht="16">
       <c r="A18" s="240"/>
       <c r="B18" s="232" t="s">
         <v>254</v>
@@ -12901,7 +12901,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.9">
+    <row r="26" spans="1:9" ht="16">
       <c r="A26" s="170" t="s">
         <v>262</v>
       </c>
@@ -13387,7 +13387,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.9">
+    <row r="64" spans="1:5" ht="16">
       <c r="A64" s="170" t="s">
         <v>289</v>
       </c>
@@ -13911,7 +13911,7 @@
       <c r="P91" s="93"/>
     </row>
     <row r="92" spans="1:16" collapsed="1"/>
-    <row r="93" spans="1:16" ht="15.9">
+    <row r="93" spans="1:16" ht="16">
       <c r="A93" s="170" t="s">
         <v>305</v>
       </c>
@@ -13959,7 +13959,7 @@
       <c r="C100" s="112"/>
     </row>
     <row r="101" spans="1:6" collapsed="1"/>
-    <row r="102" spans="1:6" ht="15.9">
+    <row r="102" spans="1:6" ht="16">
       <c r="A102" s="170" t="s">
         <v>309</v>
       </c>
@@ -14145,24 +14145,24 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{295F58DB-5942-43F7-9336-EA17EFEAB2F4}">
   <dimension ref="A1:P121"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="38.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.15234375" customWidth="1"/>
+    <col min="1" max="1" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="28.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.69140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.4609375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.4609375" customWidth="1"/>
-    <col min="10" max="10" width="76.3046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.69140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="34.15234375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="32.3046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.5" customWidth="1"/>
+    <col min="10" max="10" width="76.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="34.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="32.33203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="24" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.69140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -14170,8 +14170,8 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" thickBot="1"/>
-    <row r="3" spans="1:9" ht="26.8" customHeight="1" thickBot="1">
+    <row r="2" spans="1:9" ht="16" thickBot="1"/>
+    <row r="3" spans="1:9" ht="26.75" customHeight="1" thickBot="1">
       <c r="A3" s="373" t="s">
         <v>454</v>
       </c>
@@ -14185,7 +14185,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="17.8" customHeight="1">
+    <row r="4" spans="1:9" ht="17.75" customHeight="1">
       <c r="A4" s="245" t="s">
         <v>201</v>
       </c>
@@ -14453,7 +14453,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.9">
+    <row r="26" spans="1:7" ht="16">
       <c r="A26" s="170" t="s">
         <v>262</v>
       </c>
@@ -14476,7 +14476,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.3" customHeight="1" outlineLevel="1">
+    <row r="27" spans="1:7" ht="16.25" customHeight="1" outlineLevel="1">
       <c r="A27" s="14" t="s">
         <v>270</v>
       </c>
@@ -15049,7 +15049,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="15.9">
+    <row r="63" spans="1:16" ht="16">
       <c r="A63" s="170" t="s">
         <v>289</v>
       </c>
@@ -15613,7 +15613,7 @@
       <c r="P90" s="93"/>
     </row>
     <row r="91" spans="1:16" collapsed="1"/>
-    <row r="92" spans="1:16" ht="15.9">
+    <row r="92" spans="1:16" ht="16">
       <c r="A92" s="170" t="s">
         <v>305</v>
       </c>
@@ -15661,7 +15661,7 @@
       <c r="C99" s="112"/>
     </row>
     <row r="100" spans="1:6" collapsed="1"/>
-    <row r="101" spans="1:6" ht="15.9">
+    <row r="101" spans="1:6" ht="16">
       <c r="A101" s="170" t="s">
         <v>309</v>
       </c>
@@ -15686,7 +15686,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="17.8" hidden="1" customHeight="1" outlineLevel="1"/>
+    <row r="103" spans="1:6" ht="17.75" hidden="1" customHeight="1" outlineLevel="1"/>
     <row r="104" spans="1:6" hidden="1" outlineLevel="1"/>
     <row r="105" spans="1:6" hidden="1" outlineLevel="1"/>
     <row r="106" spans="1:6" hidden="1" outlineLevel="1"/>
@@ -15758,24 +15758,24 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB35024E-5EF1-4F84-8DB8-3508E601D619}">
   <dimension ref="A1:Q81"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="38.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.15234375" customWidth="1"/>
-    <col min="4" max="4" width="18.3046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.69140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.4609375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.4609375" customWidth="1"/>
-    <col min="10" max="10" width="25.15234375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.69140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="30.15234375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.4609375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="23.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.5" customWidth="1"/>
+    <col min="10" max="10" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -15783,8 +15783,8 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" thickBot="1"/>
-    <row r="3" spans="1:9" ht="26.8" customHeight="1" thickBot="1">
+    <row r="2" spans="1:9" ht="16" thickBot="1"/>
+    <row r="3" spans="1:9" ht="26.75" customHeight="1" thickBot="1">
       <c r="A3" s="373" t="s">
         <v>499</v>
       </c>
@@ -15798,7 +15798,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="17.8" customHeight="1">
+    <row r="4" spans="1:9" ht="17.75" customHeight="1">
       <c r="A4" s="245" t="s">
         <v>201</v>
       </c>
@@ -16012,7 +16012,7 @@
       <c r="F18" s="256"/>
       <c r="G18" s="257"/>
     </row>
-    <row r="19" spans="1:9" ht="15.9">
+    <row r="19" spans="1:9" ht="16">
       <c r="A19" s="240"/>
       <c r="B19" s="292" t="s">
         <v>251</v>
@@ -16087,7 +16087,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.9">
+    <row r="27" spans="1:9" ht="16">
       <c r="A27" s="170" t="s">
         <v>262</v>
       </c>
@@ -16761,7 +16761,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="15.9">
+    <row r="65" spans="1:17" ht="16">
       <c r="A65" s="170" t="s">
         <v>289</v>
       </c>
@@ -16961,7 +16961,7 @@
       <c r="O70" s="93"/>
       <c r="P70" s="93"/>
     </row>
-    <row r="71" spans="1:17" ht="15.9">
+    <row r="71" spans="1:17" ht="16">
       <c r="A71" s="170" t="s">
         <v>305</v>
       </c>
@@ -17011,7 +17011,7 @@
       <c r="D74" s="218"/>
     </row>
     <row r="75" spans="1:17" collapsed="1"/>
-    <row r="76" spans="1:17" ht="15.9">
+    <row r="76" spans="1:17" ht="16">
       <c r="A76" s="170" t="s">
         <v>309</v>
       </c>
@@ -17113,26 +17113,26 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11D7BEED-AC20-4D0F-9C6B-774F7F4814E4}">
   <dimension ref="B1:Q147"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="1.4609375" customWidth="1"/>
-    <col min="2" max="2" width="42.4609375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.15234375" customWidth="1"/>
-    <col min="5" max="5" width="18.3046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.4609375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.4609375" customWidth="1"/>
-    <col min="11" max="11" width="76.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.69140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="34.15234375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="32.3046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="48.4609375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.69140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.3046875" customWidth="1"/>
+    <col min="1" max="1" width="1.5" customWidth="1"/>
+    <col min="2" max="2" width="42.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.1640625" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.5" customWidth="1"/>
+    <col min="11" max="11" width="76.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="34.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="48.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10">
@@ -17140,8 +17140,8 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="2:10" ht="15" thickBot="1"/>
-    <row r="3" spans="2:10" ht="26.8" customHeight="1" thickBot="1">
+    <row r="2" spans="2:10" ht="16" thickBot="1"/>
+    <row r="3" spans="2:10" ht="26.75" customHeight="1" thickBot="1">
       <c r="B3" s="373" t="s">
         <v>539</v>
       </c>
@@ -17155,7 +17155,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="17.8" customHeight="1">
+    <row r="4" spans="2:10" ht="17.75" customHeight="1">
       <c r="B4" s="245" t="s">
         <v>201</v>
       </c>
@@ -18828,7 +18828,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="89" spans="2:17" ht="15.9">
+    <row r="89" spans="2:17" ht="16">
       <c r="B89" s="170" t="s">
         <v>289</v>
       </c>
@@ -19631,7 +19631,7 @@
       <c r="P116" s="93"/>
       <c r="Q116" s="93"/>
     </row>
-    <row r="118" spans="2:17" ht="15.9">
+    <row r="118" spans="2:17" ht="16">
       <c r="B118" s="170" t="s">
         <v>305</v>
       </c>
@@ -19743,7 +19743,7 @@
       <c r="D125" s="112"/>
     </row>
     <row r="126" spans="2:17" collapsed="1"/>
-    <row r="128" spans="2:17" ht="15.9">
+    <row r="128" spans="2:17" ht="16">
       <c r="B128" s="170" t="s">
         <v>309</v>
       </c>
@@ -19883,25 +19883,25 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16F904C0-056F-4191-B088-AF8BF57FC0F9}">
   <dimension ref="B1:R121"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" customWidth="1"/>
-    <col min="2" max="2" width="38.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.1640625" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.15234375" customWidth="1"/>
-    <col min="5" max="5" width="18.3046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.4609375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.4609375" customWidth="1"/>
-    <col min="11" max="11" width="76.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.3046875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="31.69140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.15234375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.4609375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.3046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.1640625" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.5" customWidth="1"/>
+    <col min="11" max="11" width="76.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10">
@@ -19909,8 +19909,8 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="2:10" ht="15" thickBot="1"/>
-    <row r="3" spans="2:10" ht="26.8" customHeight="1" thickBot="1">
+    <row r="2" spans="2:10" ht="16" thickBot="1"/>
+    <row r="3" spans="2:10" ht="26.75" customHeight="1" thickBot="1">
       <c r="B3" s="373" t="s">
         <v>612</v>
       </c>
@@ -19924,7 +19924,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="17.8" customHeight="1">
+    <row r="4" spans="2:10" ht="17.75" customHeight="1">
       <c r="B4" s="245" t="s">
         <v>201</v>
       </c>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="H13" s="276"/>
     </row>
-    <row r="14" spans="2:10" ht="17.8" customHeight="1">
+    <row r="14" spans="2:10" ht="17.75" customHeight="1">
       <c r="B14" s="250"/>
       <c r="C14" s="380"/>
       <c r="D14" s="381"/>
@@ -20221,7 +20221,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="26" spans="2:10" ht="15.9">
+    <row r="26" spans="2:10" ht="16">
       <c r="B26" s="170" t="s">
         <v>262</v>
       </c>
@@ -20728,7 +20728,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="63" spans="2:18" ht="15.9">
+    <row r="63" spans="2:18" ht="16">
       <c r="B63" s="170" t="s">
         <v>289</v>
       </c>
@@ -21279,7 +21279,7 @@
       <c r="Q90" s="93"/>
     </row>
     <row r="91" spans="2:17" collapsed="1"/>
-    <row r="92" spans="2:17" ht="15.9">
+    <row r="92" spans="2:17" ht="16">
       <c r="B92" s="170" t="s">
         <v>305</v>
       </c>
@@ -21343,7 +21343,7 @@
       <c r="D99" s="112"/>
     </row>
     <row r="100" spans="2:7" collapsed="1"/>
-    <row r="101" spans="2:7" ht="15.9">
+    <row r="101" spans="2:7" ht="16">
       <c r="B101" s="170" t="s">
         <v>309</v>
       </c>
@@ -21599,25 +21599,25 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FD3B640-62A8-43CF-B93C-12FB62F0F6D6}">
   <dimension ref="B1:R136"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="38.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.15234375" customWidth="1"/>
-    <col min="5" max="5" width="18.3046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.4609375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="40.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.4609375" customWidth="1"/>
-    <col min="11" max="11" width="76.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.3046875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="31.69140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.15234375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="45.3046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.1640625" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.5" customWidth="1"/>
+    <col min="11" max="11" width="76.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="45.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10">
@@ -21625,8 +21625,8 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="2:10" ht="15" thickBot="1"/>
-    <row r="3" spans="2:10" ht="26.8" customHeight="1" thickBot="1">
+    <row r="2" spans="2:10" ht="16" thickBot="1"/>
+    <row r="3" spans="2:10" ht="26.75" customHeight="1" thickBot="1">
       <c r="B3" s="373" t="s">
         <v>505</v>
       </c>
@@ -21640,7 +21640,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="17.8" customHeight="1">
+    <row r="4" spans="2:10" ht="17.75" customHeight="1">
       <c r="B4" s="245" t="s">
         <v>201</v>
       </c>
@@ -21993,7 +21993,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="31" spans="2:10" ht="15.9">
+    <row r="31" spans="2:10" ht="16">
       <c r="B31" s="170" t="s">
         <v>262</v>
       </c>
@@ -22677,7 +22677,7 @@
     <row r="77" spans="2:18">
       <c r="E77" s="218"/>
     </row>
-    <row r="79" spans="2:18" ht="15.9">
+    <row r="79" spans="2:18" ht="16">
       <c r="B79" s="170" t="s">
         <v>289</v>
       </c>
@@ -23325,7 +23325,7 @@
       <c r="Q106" s="93"/>
     </row>
     <row r="107" spans="2:17" collapsed="1"/>
-    <row r="108" spans="2:17" ht="15.9">
+    <row r="108" spans="2:17" ht="16">
       <c r="B108" s="170" t="s">
         <v>305</v>
       </c>
@@ -23404,7 +23404,7 @@
     <row r="115" spans="2:7" outlineLevel="1">
       <c r="D115" s="112"/>
     </row>
-    <row r="117" spans="2:7" ht="15.9">
+    <row r="117" spans="2:7" ht="16">
       <c r="B117" s="170" t="s">
         <v>309</v>
       </c>
@@ -23557,6 +23557,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G19:H19"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="C14:D14"/>
@@ -23566,12 +23572,6 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G19:H19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B1" location="'All Companies'!A1" display="All Companies" xr:uid="{7647C392-B3A3-4B71-80F7-0D613A000A1F}"/>
@@ -23624,20 +23624,20 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F7EDF72-3FFF-5B48-8A8A-DF5DE9D35241}">
   <dimension ref="B1:R121"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="4.15234375" customWidth="1"/>
-    <col min="2" max="2" width="38.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.15234375" customWidth="1"/>
-    <col min="5" max="5" width="18.3046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.3046875" customWidth="1"/>
-    <col min="11" max="11" width="76.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.1640625" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.1640625" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.33203125" customWidth="1"/>
+    <col min="11" max="11" width="76.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12">
@@ -23645,7 +23645,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="2:12" ht="15" thickBot="1">
+    <row r="2" spans="2:12" ht="16" thickBot="1">
       <c r="J2" t="s">
         <v>196</v>
       </c>
@@ -23656,7 +23656,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="26.8" customHeight="1" thickBot="1">
+    <row r="3" spans="2:12" ht="26.75" customHeight="1" thickBot="1">
       <c r="B3" s="373" t="s">
         <v>687</v>
       </c>
@@ -23673,7 +23673,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="17.8" customHeight="1">
+    <row r="4" spans="2:12" ht="17.75" customHeight="1">
       <c r="B4" s="245" t="s">
         <v>201</v>
       </c>
@@ -24007,7 +24007,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="26" spans="2:10" ht="15.9">
+    <row r="26" spans="2:10" ht="16">
       <c r="B26" s="170" t="s">
         <v>262</v>
       </c>
@@ -24275,7 +24275,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="63" spans="2:18" ht="15.9">
+    <row r="63" spans="2:18" ht="16">
       <c r="B63" s="170" t="s">
         <v>289</v>
       </c>
@@ -24800,7 +24800,7 @@
       <c r="Q90" s="93"/>
     </row>
     <row r="91" spans="2:17" collapsed="1"/>
-    <row r="92" spans="2:17" ht="15.9">
+    <row r="92" spans="2:17" ht="16">
       <c r="B92" s="170" t="s">
         <v>305</v>
       </c>
@@ -24848,7 +24848,7 @@
       <c r="D99" s="112"/>
     </row>
     <row r="100" spans="2:7" collapsed="1"/>
-    <row r="101" spans="2:7" ht="15.9">
+    <row r="101" spans="2:7" ht="16">
       <c r="B101" s="170" t="s">
         <v>309</v>
       </c>
@@ -25034,20 +25034,20 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C023E9AF-2873-48A9-9B76-629859D4DFE7}">
   <dimension ref="B1:R122"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="0.4609375" customWidth="1"/>
-    <col min="2" max="2" width="38.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.15234375" customWidth="1"/>
-    <col min="5" max="5" width="18.3046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.4609375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="76.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.5" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.1640625" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="76.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12">
@@ -25055,7 +25055,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="2:12" ht="15" thickBot="1">
+    <row r="2" spans="2:12" ht="16" thickBot="1">
       <c r="J2" t="s">
         <v>196</v>
       </c>
@@ -25066,7 +25066,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="26.6" thickBot="1">
+    <row r="3" spans="2:12" ht="27" thickBot="1">
       <c r="B3" s="373" t="s">
         <v>650</v>
       </c>
@@ -25083,7 +25083,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="17.8" customHeight="1">
+    <row r="4" spans="2:12" ht="17.75" customHeight="1">
       <c r="B4" s="245" t="s">
         <v>201</v>
       </c>
@@ -25432,7 +25432,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15.9">
+    <row r="26" spans="2:11" ht="16">
       <c r="B26" s="170" t="s">
         <v>262</v>
       </c>
@@ -25826,7 +25826,7 @@
       </c>
     </row>
     <row r="62" spans="2:4" outlineLevel="1"/>
-    <row r="64" spans="2:4" ht="15.9">
+    <row r="64" spans="2:4" ht="16">
       <c r="B64" s="170" t="s">
         <v>289</v>
       </c>
@@ -26351,7 +26351,7 @@
       <c r="Q91" s="93"/>
     </row>
     <row r="92" spans="2:17" collapsed="1"/>
-    <row r="93" spans="2:17" ht="15.9">
+    <row r="93" spans="2:17" ht="16">
       <c r="B93" s="170" t="s">
         <v>305</v>
       </c>
@@ -26399,7 +26399,7 @@
       <c r="D100" s="112"/>
     </row>
     <row r="101" spans="2:7" collapsed="1"/>
-    <row r="102" spans="2:7" ht="15.9">
+    <row r="102" spans="2:7" ht="16">
       <c r="B102" s="170" t="s">
         <v>309</v>
       </c>
@@ -26590,25 +26590,25 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98232C0A-9392-4CB0-BFD4-73BE4A15933E}">
   <dimension ref="B1:Q121"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" customWidth="1"/>
-    <col min="2" max="2" width="30.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.1640625" customWidth="1"/>
+    <col min="2" max="2" width="30.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.3046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.69140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.3046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.3046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.3046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="25" customWidth="1"/>
-    <col min="12" max="12" width="16.69140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.3046875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="31.69140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.15234375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.4609375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.3046875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12">
@@ -26616,7 +26616,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="2:12" ht="15" thickBot="1">
+    <row r="2" spans="2:12" ht="16" thickBot="1">
       <c r="J2" t="s">
         <v>196</v>
       </c>
@@ -26627,7 +26627,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="26.6" thickBot="1">
+    <row r="3" spans="2:12" ht="27" thickBot="1">
       <c r="B3" s="373" t="s">
         <v>650</v>
       </c>
@@ -26644,7 +26644,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="17.8" customHeight="1">
+    <row r="4" spans="2:12" ht="17.75" customHeight="1">
       <c r="B4" s="245" t="s">
         <v>201</v>
       </c>
@@ -26960,7 +26960,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="26" spans="2:10" ht="15.9">
+    <row r="26" spans="2:10" ht="16">
       <c r="B26" s="170" t="s">
         <v>262</v>
       </c>
@@ -27221,7 +27221,7 @@
       </c>
     </row>
     <row r="62" spans="2:17" collapsed="1"/>
-    <row r="63" spans="2:17" ht="15.9">
+    <row r="63" spans="2:17" ht="16">
       <c r="B63" s="170" t="s">
         <v>289</v>
       </c>
@@ -27745,7 +27745,7 @@
       <c r="Q90" s="93"/>
     </row>
     <row r="91" spans="2:17" collapsed="1"/>
-    <row r="92" spans="2:17" ht="15.9">
+    <row r="92" spans="2:17" ht="16">
       <c r="B92" s="170" t="s">
         <v>305</v>
       </c>
@@ -27793,7 +27793,7 @@
       <c r="D99" s="112"/>
     </row>
     <row r="100" spans="2:8" collapsed="1"/>
-    <row r="101" spans="2:8" ht="15.9">
+    <row r="101" spans="2:8" ht="16">
       <c r="B101" s="170" t="s">
         <v>309</v>
       </c>
@@ -27980,40 +27980,40 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FF52C3A-2443-41B3-9F46-CE750C79C8D8}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:Z34"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.3046875" style="44" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" style="44" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="44" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.15234375" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.15234375" style="44" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.3046875" style="44" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.3046875" style="44" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.3046875" style="44" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.1640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" style="44" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" style="44" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.33203125" style="44" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="44" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.69140625" style="45" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.6640625" style="45" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="28" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.15234375" style="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.69140625" style="46" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.3046875" style="44" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.69140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.15234375" style="44" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.69140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.3046875" style="48" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.3046875" style="14" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.15234375" style="48" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.69140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.15234375" style="44" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.1640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" style="46" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" style="44" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.1640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.6640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.1640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.6640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.1640625" style="44" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="30" style="14" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="55.15234375" style="49" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="42.3046875" style="14" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="56.3046875" style="14" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="55.1640625" style="49" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="42.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="56.33203125" style="14" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="55" style="14" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="9.15234375" style="14"/>
-    <col min="30" max="30" width="31.69140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.15234375" style="14"/>
+    <col min="27" max="29" width="9.1640625" style="14"/>
+    <col min="30" max="30" width="31.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.1640625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="14.8" customHeight="1">
+    <row r="1" spans="1:26" ht="14.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -28091,7 +28091,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:26" hidden="1">
+    <row r="2" spans="1:26" ht="16" hidden="1">
       <c r="A2" s="15">
         <v>485</v>
       </c>
@@ -28147,7 +28147,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:26" hidden="1">
+    <row r="3" spans="1:26" ht="16" hidden="1">
       <c r="A3" s="15">
         <v>485</v>
       </c>
@@ -28239,7 +28239,7 @@
       <c r="Y4" s="20"/>
       <c r="Z4" s="25"/>
     </row>
-    <row r="5" spans="1:26" ht="29.15">
+    <row r="5" spans="1:26" ht="16">
       <c r="A5" s="15" t="s">
         <v>106</v>
       </c>
@@ -28302,7 +28302,7 @@
       </c>
       <c r="Z5" s="25"/>
     </row>
-    <row r="6" spans="1:26" ht="29.15" hidden="1">
+    <row r="6" spans="1:26" ht="16" hidden="1">
       <c r="A6" s="15" t="s">
         <v>106</v>
       </c>
@@ -28415,7 +28415,7 @@
       </c>
       <c r="Z7" s="25"/>
     </row>
-    <row r="8" spans="1:26" ht="29.15">
+    <row r="8" spans="1:26" ht="16">
       <c r="A8" s="15" t="s">
         <v>106</v>
       </c>
@@ -28753,7 +28753,7 @@
       <c r="Y15" s="20"/>
       <c r="Z15" s="25"/>
     </row>
-    <row r="16" spans="1:26" ht="14.8" customHeight="1">
+    <row r="16" spans="1:26" ht="14.75" customHeight="1">
       <c r="A16" s="15" t="s">
         <v>149</v>
       </c>
@@ -28847,7 +28847,7 @@
       <c r="Y17" s="36"/>
       <c r="Z17" s="43"/>
     </row>
-    <row r="18" spans="1:26" ht="14.8" customHeight="1">
+    <row r="18" spans="1:26" ht="14.75" customHeight="1">
       <c r="A18" s="16" t="s">
         <v>149</v>
       </c>
@@ -28911,7 +28911,7 @@
       </c>
       <c r="Z18" s="20"/>
     </row>
-    <row r="19" spans="1:26" s="138" customFormat="1" ht="14.8" hidden="1" customHeight="1">
+    <row r="19" spans="1:26" s="138" customFormat="1" ht="14.75" hidden="1" customHeight="1">
       <c r="A19" s="133" t="s">
         <v>149</v>
       </c>
@@ -28973,7 +28973,7 @@
       </c>
       <c r="Z19" s="134"/>
     </row>
-    <row r="20" spans="1:26" ht="14.8" hidden="1" customHeight="1">
+    <row r="20" spans="1:26" ht="14.75" hidden="1" customHeight="1">
       <c r="A20" s="16" t="s">
         <v>149</v>
       </c>
@@ -29039,7 +29039,7 @@
       </c>
       <c r="Z20" s="20"/>
     </row>
-    <row r="21" spans="1:26" ht="14.8" customHeight="1">
+    <row r="21" spans="1:26" ht="14.75" customHeight="1">
       <c r="A21" s="16" t="s">
         <v>149</v>
       </c>
@@ -29188,22 +29188,22 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DD9D655-87D6-4A7E-961B-EEAF4654BB13}">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.3046875" style="44" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.3046875" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" style="44" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.33203125" style="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30" style="281" customWidth="1"/>
-    <col min="4" max="4" width="12.3046875" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.3046875" style="44" customWidth="1"/>
-    <col min="6" max="6" width="11.69140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.69140625" style="14" customWidth="1"/>
-    <col min="8" max="8" width="28.69140625" style="283" customWidth="1"/>
-    <col min="9" max="9" width="23.15234375" style="44" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.3046875" style="28" customWidth="1"/>
-    <col min="11" max="11" width="17.15234375" style="14" customWidth="1"/>
-    <col min="12" max="12" width="25.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.4609375" style="44" customWidth="1"/>
-    <col min="14" max="16384" width="9.15234375" style="14"/>
+    <col min="4" max="4" width="12.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" style="44" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.6640625" style="14" customWidth="1"/>
+    <col min="8" max="8" width="28.6640625" style="283" customWidth="1"/>
+    <col min="9" max="9" width="23.1640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.33203125" style="28" customWidth="1"/>
+    <col min="11" max="11" width="17.1640625" style="14" customWidth="1"/>
+    <col min="12" max="12" width="25.33203125" style="46" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5" style="44" customWidth="1"/>
+    <col min="14" max="16384" width="9.1640625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -29247,7 +29247,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="253" customFormat="1" ht="15" thickBot="1">
+    <row r="2" spans="1:13" s="253" customFormat="1" ht="16" thickBot="1">
       <c r="A2" s="267" t="s">
         <v>440</v>
       </c>
@@ -29293,7 +29293,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="253" customFormat="1" ht="15" thickBot="1">
+    <row r="3" spans="1:13" s="253" customFormat="1" ht="17" thickBot="1">
       <c r="A3" s="267" t="s">
         <v>440</v>
       </c>
@@ -29339,7 +29339,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="253" customFormat="1" ht="15" thickBot="1">
+    <row r="4" spans="1:13" s="253" customFormat="1" ht="16" thickBot="1">
       <c r="A4" s="340" t="s">
         <v>440</v>
       </c>
@@ -29385,7 +29385,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="253" customFormat="1" ht="15" thickBot="1">
+    <row r="5" spans="1:13" s="253" customFormat="1" ht="16" thickBot="1">
       <c r="A5" s="340" t="s">
         <v>440</v>
       </c>
@@ -29431,7 +29431,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="253" customFormat="1" ht="15" thickBot="1">
+    <row r="6" spans="1:13" s="253" customFormat="1" ht="16" thickBot="1">
       <c r="A6" s="263" t="s">
         <v>149</v>
       </c>
@@ -30044,11 +30044,11 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{587F58AB-3A41-4CD2-A0EE-DF855F0201DD}">
   <dimension ref="B2:F51"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28.4609375" customWidth="1"/>
-    <col min="3" max="3" width="18.3046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.69140625" customWidth="1"/>
+    <col min="2" max="2" width="28.5" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6">
@@ -30422,10 +30422,10 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69704E3A-2FF3-744C-9E1F-FBDC65EE282B}">
   <dimension ref="A1:M52"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="15.69140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="40.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="40.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -30433,8 +30433,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" thickBot="1"/>
-    <row r="3" spans="1:13" ht="15" thickBot="1">
+    <row r="2" spans="1:13" ht="16" thickBot="1"/>
+    <row r="3" spans="1:13" ht="16" thickBot="1">
       <c r="B3" t="s">
         <v>1435</v>
       </c>
@@ -30445,7 +30445,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" thickBot="1">
+    <row r="4" spans="1:13" ht="16" thickBot="1">
       <c r="B4" t="s">
         <v>1437</v>
       </c>
@@ -30456,7 +30456,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" thickBot="1">
+    <row r="5" spans="1:13" ht="16" thickBot="1">
       <c r="B5" t="s">
         <v>1438</v>
       </c>
@@ -30464,7 +30464,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15" thickBot="1">
+    <row r="6" spans="1:13" ht="16" thickBot="1">
       <c r="B6" t="s">
         <v>1439</v>
       </c>
@@ -30472,7 +30472,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15" thickBot="1">
+    <row r="7" spans="1:13" ht="16" thickBot="1">
       <c r="B7" t="s">
         <v>1442</v>
       </c>
@@ -30486,7 +30486,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15" thickBot="1">
+    <row r="8" spans="1:13" ht="16" thickBot="1">
       <c r="B8" t="s">
         <v>1440</v>
       </c>
@@ -30500,7 +30500,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="18" thickBot="1">
+    <row r="9" spans="1:13" ht="19" thickBot="1">
       <c r="B9" t="s">
         <v>1441</v>
       </c>
@@ -30514,7 +30514,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="18" thickBot="1">
+    <row r="10" spans="1:13" ht="19" thickBot="1">
       <c r="B10" t="s">
         <v>1443</v>
       </c>
@@ -30528,7 +30528,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="17.600000000000001">
+    <row r="11" spans="1:13" ht="18">
       <c r="L11" s="372" t="s">
         <v>250</v>
       </c>
@@ -30834,16 +30834,16 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{529DB9A7-C937-4941-8FBC-D31FC9ABC549}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="15.9" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="36" style="170" customWidth="1"/>
     <col min="2" max="2" width="58" style="168" customWidth="1"/>
-    <col min="3" max="3" width="11.69140625" style="168" customWidth="1"/>
-    <col min="4" max="4" width="8.69140625" style="295"/>
-    <col min="5" max="5" width="15.3046875" style="301" customWidth="1"/>
-    <col min="6" max="6" width="24.69140625" style="301" customWidth="1"/>
-    <col min="7" max="7" width="16.3046875" style="168" customWidth="1"/>
-    <col min="8" max="16384" width="8.69140625" style="168"/>
+    <col min="3" max="3" width="11.6640625" style="168" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="295"/>
+    <col min="5" max="5" width="15.33203125" style="301" customWidth="1"/>
+    <col min="6" max="6" width="24.6640625" style="301" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" style="168" customWidth="1"/>
+    <col min="8" max="16384" width="8.6640625" style="168"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="169" customFormat="1">
@@ -31409,17 +31409,17 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B80AD34E-A42A-4DEA-9906-693E6DA78DE2}">
   <dimension ref="A1:R212"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.3046875" customWidth="1"/>
-    <col min="2" max="2" width="14.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.3046875" style="112" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.3046875" style="112" customWidth="1"/>
-    <col min="16" max="16" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.69140625" style="112" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" style="112" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.33203125" style="112" customWidth="1"/>
+    <col min="16" max="16" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.6640625" style="112" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -33784,9 +33784,9 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D45B2845-0028-4F1C-8E8B-D3152459823D}">
   <dimension ref="B3:F11"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="12.3046875" style="112" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" style="112" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:6">
@@ -33846,15 +33846,15 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5A4B320-615F-41EE-8587-CBBA4C9AD44F}">
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.3046875" customWidth="1"/>
-    <col min="3" max="5" width="22.69140625" customWidth="1"/>
-    <col min="6" max="6" width="50.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="3" max="5" width="22.6640625" customWidth="1"/>
+    <col min="6" max="6" width="50.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1">
+    <row r="1" spans="1:6" ht="16" thickBot="1">
       <c r="A1" s="215"/>
       <c r="B1" s="215"/>
       <c r="C1" s="386" t="s">
@@ -33866,7 +33866,7 @@
       </c>
       <c r="F1" s="387"/>
     </row>
-    <row r="2" spans="1:6" ht="15" thickBot="1">
+    <row r="2" spans="1:6" ht="16" thickBot="1">
       <c r="A2" s="217" t="s">
         <v>776</v>
       </c>
@@ -33884,7 +33884,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" thickBot="1">
+    <row r="3" spans="1:6" ht="16" thickBot="1">
       <c r="A3" s="217">
         <v>911</v>
       </c>
@@ -33904,7 +33904,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" thickBot="1">
+    <row r="4" spans="1:6" ht="16" thickBot="1">
       <c r="A4" s="215"/>
       <c r="B4" s="215"/>
       <c r="C4" s="213">
@@ -33920,7 +33920,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" thickBot="1">
+    <row r="5" spans="1:6" ht="16" thickBot="1">
       <c r="A5" s="215"/>
       <c r="B5" s="215"/>
       <c r="C5" s="212"/>
@@ -33928,7 +33928,7 @@
       <c r="E5" s="212"/>
       <c r="F5" s="215"/>
     </row>
-    <row r="6" spans="1:6" ht="26.15" thickBot="1">
+    <row r="6" spans="1:6" ht="30" thickBot="1">
       <c r="A6" s="217">
         <v>931</v>
       </c>
@@ -33948,7 +33948,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15" thickBot="1">
+    <row r="7" spans="1:6" ht="16" thickBot="1">
       <c r="A7" s="215"/>
       <c r="B7" s="215"/>
       <c r="C7" s="213">
@@ -33964,7 +33964,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" thickBot="1">
+    <row r="8" spans="1:6" ht="16" thickBot="1">
       <c r="A8" s="215"/>
       <c r="B8" s="215"/>
       <c r="C8" s="212"/>
@@ -33976,7 +33976,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" thickBot="1">
+    <row r="9" spans="1:6" ht="16" thickBot="1">
       <c r="A9" s="215"/>
       <c r="B9" s="215"/>
       <c r="C9" s="212"/>
@@ -33988,7 +33988,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15" thickBot="1">
+    <row r="10" spans="1:6" ht="16" thickBot="1">
       <c r="A10" s="215"/>
       <c r="B10" s="215"/>
       <c r="C10" s="212"/>
@@ -33996,7 +33996,7 @@
       <c r="E10" s="212"/>
       <c r="F10" s="215"/>
     </row>
-    <row r="11" spans="1:6" ht="26.15" thickBot="1">
+    <row r="11" spans="1:6" ht="30" thickBot="1">
       <c r="A11" s="217">
         <v>902</v>
       </c>
@@ -34016,7 +34016,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" thickBot="1">
+    <row r="12" spans="1:6" ht="16" thickBot="1">
       <c r="A12" s="215"/>
       <c r="B12" s="215"/>
       <c r="C12" s="213">
@@ -34032,7 +34032,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="26.15" thickBot="1">
+    <row r="13" spans="1:6" ht="30" thickBot="1">
       <c r="A13" s="215"/>
       <c r="B13" s="215"/>
       <c r="C13" s="213">
@@ -34044,7 +34044,7 @@
       <c r="E13" s="212"/>
       <c r="F13" s="215"/>
     </row>
-    <row r="14" spans="1:6" ht="26.15" thickBot="1">
+    <row r="14" spans="1:6" ht="30" thickBot="1">
       <c r="A14" s="215"/>
       <c r="B14" s="215" t="s">
         <v>956</v>
@@ -34058,7 +34058,7 @@
       <c r="E14" s="212"/>
       <c r="F14" s="215"/>
     </row>
-    <row r="15" spans="1:6" ht="15" thickBot="1">
+    <row r="15" spans="1:6" ht="16" thickBot="1">
       <c r="A15" s="215"/>
       <c r="B15" s="215"/>
       <c r="C15" s="213">
@@ -34070,7 +34070,7 @@
       <c r="E15" s="212"/>
       <c r="F15" s="215"/>
     </row>
-    <row r="16" spans="1:6" ht="26.15" thickBot="1">
+    <row r="16" spans="1:6" ht="30" thickBot="1">
       <c r="A16" s="215"/>
       <c r="B16" s="215" t="s">
         <v>956</v>
@@ -34084,7 +34084,7 @@
       <c r="E16" s="212"/>
       <c r="F16" s="215"/>
     </row>
-    <row r="17" spans="1:6" ht="15" thickBot="1">
+    <row r="17" spans="1:6" ht="16" thickBot="1">
       <c r="A17" s="215"/>
       <c r="B17" s="215" t="s">
         <v>956</v>
@@ -34098,7 +34098,7 @@
       <c r="E17" s="212"/>
       <c r="F17" s="215"/>
     </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1">
+    <row r="18" spans="1:6" ht="16" thickBot="1">
       <c r="A18" s="215"/>
       <c r="B18" s="215"/>
       <c r="C18" s="213">
@@ -34110,7 +34110,7 @@
       <c r="E18" s="212"/>
       <c r="F18" s="215"/>
     </row>
-    <row r="19" spans="1:6" ht="15" thickBot="1">
+    <row r="19" spans="1:6" ht="16" thickBot="1">
       <c r="A19" s="215"/>
       <c r="B19" s="215"/>
       <c r="C19" s="212"/>
@@ -34118,7 +34118,7 @@
       <c r="E19" s="212"/>
       <c r="F19" s="215"/>
     </row>
-    <row r="20" spans="1:6" ht="15" thickBot="1">
+    <row r="20" spans="1:6" ht="16" thickBot="1">
       <c r="A20" s="217">
         <v>900</v>
       </c>
@@ -34138,7 +34138,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15" thickBot="1">
+    <row r="21" spans="1:6" ht="16" thickBot="1">
       <c r="A21" s="215"/>
       <c r="B21" s="215"/>
       <c r="C21" s="213">
@@ -34154,7 +34154,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15" thickBot="1">
+    <row r="22" spans="1:6" ht="16" thickBot="1">
       <c r="A22" s="215"/>
       <c r="B22" s="215"/>
       <c r="C22" s="213">
@@ -34166,7 +34166,7 @@
       <c r="E22" s="212"/>
       <c r="F22" s="215"/>
     </row>
-    <row r="23" spans="1:6" ht="15" thickBot="1">
+    <row r="23" spans="1:6" ht="16" thickBot="1">
       <c r="A23" s="215"/>
       <c r="B23" s="215"/>
       <c r="C23" s="213">
@@ -34178,7 +34178,7 @@
       <c r="E23" s="212"/>
       <c r="F23" s="215"/>
     </row>
-    <row r="24" spans="1:6" ht="15" thickBot="1">
+    <row r="24" spans="1:6" ht="16" thickBot="1">
       <c r="A24" s="215"/>
       <c r="B24" s="215"/>
       <c r="C24" s="213">
@@ -34190,7 +34190,7 @@
       <c r="E24" s="212"/>
       <c r="F24" s="215"/>
     </row>
-    <row r="25" spans="1:6" ht="15" thickBot="1">
+    <row r="25" spans="1:6" ht="16" thickBot="1">
       <c r="A25" s="215"/>
       <c r="B25" s="215"/>
       <c r="C25" s="212"/>
@@ -34198,7 +34198,7 @@
       <c r="E25" s="212"/>
       <c r="F25" s="215"/>
     </row>
-    <row r="26" spans="1:6" ht="15" thickBot="1">
+    <row r="26" spans="1:6" ht="16" thickBot="1">
       <c r="A26" s="217">
         <v>915</v>
       </c>
@@ -34218,7 +34218,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15" thickBot="1">
+    <row r="27" spans="1:6" ht="16" thickBot="1">
       <c r="A27" s="215"/>
       <c r="B27" s="215"/>
       <c r="C27" s="213">
@@ -34230,7 +34230,7 @@
       <c r="E27" s="212"/>
       <c r="F27" s="215"/>
     </row>
-    <row r="28" spans="1:6" ht="15" thickBot="1">
+    <row r="28" spans="1:6" ht="16" thickBot="1">
       <c r="A28" s="215"/>
       <c r="B28" s="215"/>
       <c r="C28" s="213">
@@ -34242,7 +34242,7 @@
       <c r="E28" s="212"/>
       <c r="F28" s="215"/>
     </row>
-    <row r="29" spans="1:6" ht="15" thickBot="1">
+    <row r="29" spans="1:6" ht="16" thickBot="1">
       <c r="A29" s="215"/>
       <c r="B29" s="215" t="s">
         <v>956</v>
@@ -34256,7 +34256,7 @@
       <c r="E29" s="212"/>
       <c r="F29" s="215"/>
     </row>
-    <row r="30" spans="1:6" ht="15" thickBot="1">
+    <row r="30" spans="1:6" ht="16" thickBot="1">
       <c r="A30" s="215"/>
       <c r="B30" s="215"/>
       <c r="C30" s="212"/>
@@ -34264,7 +34264,7 @@
       <c r="E30" s="212"/>
       <c r="F30" s="215"/>
     </row>
-    <row r="31" spans="1:6" ht="15" thickBot="1">
+    <row r="31" spans="1:6" ht="16" thickBot="1">
       <c r="A31" s="217">
         <v>917</v>
       </c>
@@ -34284,7 +34284,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15" thickBot="1">
+    <row r="32" spans="1:6" ht="16" thickBot="1">
       <c r="A32" s="215"/>
       <c r="B32" s="215"/>
       <c r="C32" s="212"/>
@@ -34292,7 +34292,7 @@
       <c r="E32" s="212"/>
       <c r="F32" s="215"/>
     </row>
-    <row r="33" spans="1:6" ht="15" thickBot="1">
+    <row r="33" spans="1:6" ht="16" thickBot="1">
       <c r="A33" s="217">
         <v>916</v>
       </c>
@@ -34312,7 +34312,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15" thickBot="1">
+    <row r="34" spans="1:6" ht="16" thickBot="1">
       <c r="A34" s="215"/>
       <c r="B34" s="215"/>
       <c r="C34" s="213">
@@ -34324,7 +34324,7 @@
       <c r="E34" s="212"/>
       <c r="F34" s="215"/>
     </row>
-    <row r="35" spans="1:6" ht="15" thickBot="1">
+    <row r="35" spans="1:6" ht="16" thickBot="1">
       <c r="A35" s="215"/>
       <c r="B35" s="215"/>
       <c r="C35" s="213">
@@ -34336,7 +34336,7 @@
       <c r="E35" s="212"/>
       <c r="F35" s="215"/>
     </row>
-    <row r="36" spans="1:6" ht="15" thickBot="1">
+    <row r="36" spans="1:6" ht="16" thickBot="1">
       <c r="A36" s="215"/>
       <c r="B36" s="215"/>
       <c r="C36" s="212"/>
@@ -34356,20 +34356,20 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14DCD37F-6375-4175-839F-9595D9E8DD60}">
   <dimension ref="B1:J3"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="12.15234375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.69140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.69140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="15" thickBot="1"/>
-    <row r="2" spans="2:10" ht="15" thickBot="1">
+    <row r="1" spans="2:10" ht="16" thickBot="1"/>
+    <row r="2" spans="2:10" ht="16" thickBot="1">
       <c r="B2" s="80" t="s">
         <v>967</v>
       </c>
@@ -34433,19 +34433,19 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C723EF5-7931-4A5F-B16E-3583673DB5E6}">
   <dimension ref="B1:P42"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="16.15234375" style="93" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.3046875" style="93" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.69140625" style="93" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="16.3046875" style="93" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.69140625" style="93" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.15234375" style="93" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38.15234375" style="93" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.3046875" style="93" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.15234375" customWidth="1"/>
-    <col min="12" max="12" width="17.69140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="34.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.1640625" style="93" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="93" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.6640625" style="93" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.33203125" style="93" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" style="93" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1640625" style="93" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.1640625" style="93" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="93" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.1640625" customWidth="1"/>
+    <col min="12" max="12" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="34.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11">
@@ -34942,23 +34942,23 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D66FFE-FD7D-40A2-A3CD-E745AC571708}">
   <dimension ref="B1:Q41"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="16.15234375" style="93" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.3046875" style="93" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.69140625" style="93" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.69140625" style="93" customWidth="1"/>
-    <col min="6" max="7" width="16.3046875" style="93" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.69140625" style="93" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.15234375" style="93" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="38.15234375" style="93" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.3046875" style="93" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.15234375" customWidth="1"/>
-    <col min="13" max="13" width="17.69140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="34.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.1640625" style="93" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="93" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.6640625" style="93" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.6640625" style="93" customWidth="1"/>
+    <col min="6" max="7" width="16.33203125" style="93" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" style="93" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1640625" style="93" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="38.1640625" style="93" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" style="93" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.1640625" customWidth="1"/>
+    <col min="13" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="34.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="15" thickBot="1">
+    <row r="1" spans="2:14" ht="16" thickBot="1">
       <c r="B1" s="80" t="s">
         <v>967</v>
       </c>
@@ -35367,7 +35367,7 @@
       <c r="M17" s="93"/>
       <c r="N17" s="93"/>
     </row>
-    <row r="18" spans="2:14" ht="15" thickBot="1">
+    <row r="18" spans="2:14" ht="16" thickBot="1">
       <c r="B18" s="107" t="s">
         <v>1428</v>
       </c>
@@ -35443,7 +35443,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F527C28E-3D8D-4262-8F54-5C40F2EFFA62}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -35473,15 +35473,15 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43F381E2-3CBF-45A8-824B-7E0831B518EE}">
   <dimension ref="C1:K28"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.3046875" style="219" customWidth="1"/>
-    <col min="5" max="6" width="13.3046875" style="218" customWidth="1"/>
-    <col min="7" max="8" width="10.3046875" style="218" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.3046875" customWidth="1"/>
-    <col min="11" max="11" width="12.15234375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" style="219" customWidth="1"/>
+    <col min="5" max="6" width="13.33203125" style="218" customWidth="1"/>
+    <col min="7" max="8" width="10.33203125" style="218" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:11">
@@ -36051,10 +36051,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA8F787D-9EF5-47E7-BABC-AC8ACF705BDF}">
   <dimension ref="A2:B12"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:2">
@@ -36130,12 +36130,12 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C526E686-54A9-4E9B-AE94-2192922AE4B4}">
   <dimension ref="B1:E6"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="48.3046875" customWidth="1"/>
-    <col min="3" max="3" width="11.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.69140625" customWidth="1"/>
-    <col min="5" max="5" width="14.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.33203125" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5">
@@ -36215,36 +36215,36 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2442E6A2-A8FC-452C-93E4-EE666257E769}">
   <dimension ref="A1:V50"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.3046875" style="44" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.3046875" style="44" customWidth="1"/>
-    <col min="3" max="3" width="57.3046875" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.15234375" style="44" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.15234375" style="28" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" style="44" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" style="44" customWidth="1"/>
+    <col min="3" max="3" width="57.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.1640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.1640625" style="28" customWidth="1"/>
     <col min="6" max="6" width="12" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.15234375" style="44" customWidth="1"/>
-    <col min="9" max="9" width="12.3046875" style="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.69140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.69140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.3046875" style="47" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="30.69140625" style="14" customWidth="1"/>
-    <col min="14" max="14" width="15.3046875" style="14" customWidth="1"/>
-    <col min="15" max="15" width="14.15234375" style="48" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.69140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.15234375" style="44" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.33203125" style="46" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1640625" style="44" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" style="47" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.6640625" style="14" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" style="14" customWidth="1"/>
+    <col min="15" max="15" width="14.1640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.6640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.1640625" style="44" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="30" style="14" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="55.15234375" style="49" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="51.69140625" style="14" customWidth="1"/>
-    <col min="21" max="21" width="56.3046875" style="14" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="55.1640625" style="49" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="51.6640625" style="14" customWidth="1"/>
+    <col min="21" max="21" width="56.33203125" style="14" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="55" style="14" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="9.15234375" style="14"/>
-    <col min="26" max="26" width="31.69140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.15234375" style="14"/>
+    <col min="23" max="25" width="9.1640625" style="14"/>
+    <col min="26" max="26" width="31.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.1640625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="14.8" customHeight="1">
+    <row r="1" spans="1:22" ht="14.75" customHeight="1">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -36310,7 +36310,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" ht="16">
       <c r="A2" s="15" t="s">
         <v>440</v>
       </c>
@@ -36376,7 +36376,7 @@
       </c>
       <c r="V2" s="25"/>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" ht="16">
       <c r="A3" s="15" t="s">
         <v>440</v>
       </c>
@@ -36442,7 +36442,7 @@
       </c>
       <c r="V3" s="25"/>
     </row>
-    <row r="4" spans="1:22" ht="15" thickBot="1">
+    <row r="4" spans="1:22" ht="17" thickBot="1">
       <c r="A4" s="56" t="s">
         <v>440</v>
       </c>
@@ -36508,7 +36508,7 @@
       </c>
       <c r="V4" s="63"/>
     </row>
-    <row r="5" spans="1:22" ht="15" thickBot="1">
+    <row r="5" spans="1:22" ht="16" thickBot="1">
       <c r="A5" s="56" t="s">
         <v>440</v>
       </c>
@@ -36806,42 +36806,42 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C9359EF-DF3A-4DD4-BE37-B7999E03CF61}">
   <dimension ref="A1:AB33"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.15234375" style="44" customWidth="1"/>
-    <col min="2" max="2" width="9.69140625" style="44" customWidth="1"/>
-    <col min="3" max="3" width="43.3046875" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" style="44" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" style="44" customWidth="1"/>
+    <col min="3" max="3" width="43.33203125" style="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" style="44" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.69140625" style="44" customWidth="1"/>
-    <col min="6" max="6" width="9.69140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.15234375" style="44" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.69140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.69140625" style="45" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.3046875" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" style="44" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.1640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" style="45" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" style="28" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="30" style="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.69140625" style="46" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.69140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.69140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.69140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.69140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.3046875" style="44" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.69140625" style="44" customWidth="1"/>
-    <col min="19" max="19" width="18.3046875" style="48" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.3046875" style="14" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.15234375" style="48" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.69140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.15234375" style="44" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" style="46" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.6640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.6640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" style="44" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" style="44" customWidth="1"/>
+    <col min="19" max="19" width="18.33203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.1640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.6640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.1640625" style="44" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="30" style="14" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="55.15234375" style="49" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="42.3046875" style="14" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="56.3046875" style="14" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="55.1640625" style="49" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="42.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="56.33203125" style="14" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="55" style="14" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="9.15234375" style="14"/>
-    <col min="32" max="32" width="31.69140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.15234375" style="14"/>
+    <col min="29" max="31" width="9.1640625" style="14"/>
+    <col min="32" max="32" width="31.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.1640625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="14.8" customHeight="1">
+    <row r="1" spans="1:28" ht="14.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -36925,7 +36925,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="29.15">
+    <row r="2" spans="1:28" ht="32">
       <c r="A2" s="15" t="s">
         <v>106</v>
       </c>
@@ -37002,7 +37002,7 @@
       </c>
       <c r="AB2" s="25"/>
     </row>
-    <row r="3" spans="1:28" ht="29.15">
+    <row r="3" spans="1:28" ht="32">
       <c r="A3" s="15" t="s">
         <v>106</v>
       </c>
@@ -37306,7 +37306,7 @@
       <c r="AA9" s="20"/>
       <c r="AB9" s="25"/>
     </row>
-    <row r="10" spans="1:28" ht="14.8" customHeight="1">
+    <row r="10" spans="1:28" ht="14.75" customHeight="1">
       <c r="A10" s="15" t="s">
         <v>149</v>
       </c>
@@ -37424,7 +37424,7 @@
       <c r="AA11" s="36"/>
       <c r="AB11" s="43"/>
     </row>
-    <row r="12" spans="1:28" ht="14.8" customHeight="1">
+    <row r="12" spans="1:28" ht="14.75" customHeight="1">
       <c r="A12" s="16" t="s">
         <v>149</v>
       </c>
@@ -37502,7 +37502,7 @@
       </c>
       <c r="AB12" s="20"/>
     </row>
-    <row r="13" spans="1:28" ht="14.8" customHeight="1">
+    <row r="13" spans="1:28" ht="14.75" customHeight="1">
       <c r="A13" s="16" t="s">
         <v>149</v>
       </c>
@@ -37673,19 +37673,19 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB8EE759-7611-4D35-83F2-3AB89B42D69B}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.15234375" customWidth="1"/>
-    <col min="2" max="2" width="47.3046875" customWidth="1"/>
-    <col min="3" max="3" width="12.15234375" customWidth="1"/>
-    <col min="4" max="4" width="13.3046875" customWidth="1"/>
-    <col min="5" max="5" width="27.15234375" customWidth="1"/>
-    <col min="6" max="6" width="20.15234375" customWidth="1"/>
+    <col min="1" max="1" width="43.1640625" customWidth="1"/>
+    <col min="2" max="2" width="47.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="27.1640625" customWidth="1"/>
+    <col min="6" max="6" width="20.1640625" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="33.3046875" customWidth="1"/>
-    <col min="9" max="9" width="30.3046875" customWidth="1"/>
-    <col min="10" max="10" width="14.3046875" customWidth="1"/>
-    <col min="11" max="11" width="30.3046875" customWidth="1"/>
+    <col min="8" max="8" width="33.33203125" customWidth="1"/>
+    <col min="9" max="9" width="30.33203125" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" customWidth="1"/>
+    <col min="11" max="11" width="30.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="227" customFormat="1">
@@ -37912,21 +37912,21 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D70DD022-C907-4F7D-BD70-3DF9AC5265AE}">
   <dimension ref="A1:V28"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.15234375" customWidth="1"/>
-    <col min="3" max="3" width="15.15234375" customWidth="1"/>
-    <col min="4" max="4" width="16.15234375" style="152" customWidth="1"/>
-    <col min="5" max="5" width="16.15234375" style="151" customWidth="1"/>
-    <col min="6" max="6" width="16.3046875" style="152" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.15234375" style="152" customWidth="1"/>
-    <col min="8" max="8" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.3046875" customWidth="1"/>
-    <col min="10" max="12" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="14.3046875" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="15.3046875" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="17.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.1640625" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" style="152" customWidth="1"/>
+    <col min="5" max="5" width="16.1640625" style="151" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="152" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" style="152" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" customWidth="1"/>
+    <col min="10" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="17.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="151" customFormat="1">
@@ -38045,7 +38045,7 @@
         <v>1202098</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="14.8" customHeight="1" thickBot="1">
+    <row r="6" spans="1:22" ht="14.75" customHeight="1" thickBot="1">
       <c r="D6" s="153">
         <f>SUM(D2:D5)</f>
         <v>20305000</v>
@@ -38120,7 +38120,7 @@
         <v>2030500000</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="15" thickTop="1">
+    <row r="7" spans="1:22" ht="16" thickTop="1">
       <c r="D7" s="152">
         <f>D2+D3+D5</f>
         <v>16805000</v>
@@ -38467,14 +38467,14 @@
     <row r="17" spans="1:14">
       <c r="N17" s="93"/>
     </row>
-    <row r="18" spans="1:14" ht="15" thickBot="1">
+    <row r="18" spans="1:14" ht="16" thickBot="1">
       <c r="E18" s="156">
         <f>E16-E8</f>
         <v>369860</v>
       </c>
       <c r="N18" s="93"/>
     </row>
-    <row r="19" spans="1:14" ht="15" thickTop="1">
+    <row r="19" spans="1:14" ht="16" thickTop="1">
       <c r="D19" s="164"/>
       <c r="N19" s="93"/>
     </row>
@@ -38592,22 +38592,22 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21885EEA-E36D-495C-AFC1-AD3AA099FE5F}">
   <dimension ref="B1:L89"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="32.15234375" style="93" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.15234375" style="93" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.3046875" style="93"/>
-    <col min="5" max="5" width="37.3046875" style="93" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.3046875" style="141" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="38.3046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.3046875" style="141"/>
-    <col min="9" max="9" width="49.15234375" customWidth="1"/>
-    <col min="10" max="10" width="44.69140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="54.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.1640625" style="93" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" style="93" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" style="93"/>
+    <col min="5" max="5" width="37.33203125" style="93" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" style="141" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.33203125" style="141"/>
+    <col min="9" max="9" width="49.1640625" customWidth="1"/>
+    <col min="10" max="10" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="54.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15" thickBot="1"/>
-    <row r="2" spans="2:12" ht="15" thickBot="1">
+    <row r="1" spans="2:12" ht="16" thickBot="1"/>
+    <row r="2" spans="2:12" ht="16" thickBot="1">
       <c r="B2" s="172" t="s">
         <v>134</v>
       </c>
@@ -38625,11 +38625,11 @@
       <c r="C3" s="176"/>
       <c r="E3" s="174"/>
     </row>
-    <row r="4" spans="2:12" ht="15" thickBot="1">
+    <row r="4" spans="2:12" ht="16" thickBot="1">
       <c r="C4" s="177"/>
       <c r="E4" s="175"/>
     </row>
-    <row r="5" spans="2:12" ht="15" thickBot="1">
+    <row r="5" spans="2:12" ht="16" thickBot="1">
       <c r="B5" s="392" t="s">
         <v>1181</v>
       </c>
@@ -38643,8 +38643,8 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" thickBot="1"/>
-    <row r="8" spans="2:12" ht="15" thickBot="1">
+    <row r="7" spans="2:12" ht="16" thickBot="1"/>
+    <row r="8" spans="2:12" ht="16" thickBot="1">
       <c r="B8" s="392" t="s">
         <v>440</v>
       </c>
@@ -38684,7 +38684,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" thickBot="1">
+    <row r="11" spans="2:12" ht="16" thickBot="1">
       <c r="B11" s="192"/>
       <c r="E11" s="191"/>
       <c r="G11" s="194"/>
@@ -38697,13 +38697,13 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" thickBot="1">
+    <row r="12" spans="2:12" ht="16" thickBot="1">
       <c r="B12" s="177"/>
       <c r="E12" s="175"/>
       <c r="G12" s="195"/>
       <c r="I12" s="190"/>
     </row>
-    <row r="13" spans="2:12" ht="15" thickBot="1">
+    <row r="13" spans="2:12" ht="16" thickBot="1">
       <c r="B13" s="172" t="s">
         <v>538</v>
       </c>
@@ -38755,8 +38755,8 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="15" thickBot="1"/>
-    <row r="19" spans="2:12" ht="15" thickBot="1">
+    <row r="18" spans="2:12" ht="16" thickBot="1"/>
+    <row r="19" spans="2:12" ht="16" thickBot="1">
       <c r="J19" s="180" t="s">
         <v>1195</v>
       </c>
@@ -38774,7 +38774,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="15" thickBot="1">
+    <row r="24" spans="2:12" ht="16" thickBot="1">
       <c r="B24" s="196"/>
       <c r="C24" s="196"/>
       <c r="D24" s="196"/>
@@ -38787,7 +38787,7 @@
       <c r="K24" s="198"/>
       <c r="L24" s="198"/>
     </row>
-    <row r="26" spans="2:12" ht="15" thickBot="1">
+    <row r="26" spans="2:12" ht="16" thickBot="1">
       <c r="B26" s="199" t="s">
         <v>1199</v>
       </c>
@@ -38863,7 +38863,7 @@
       </c>
       <c r="G34" s="122"/>
     </row>
-    <row r="35" spans="2:10" ht="15" thickBot="1">
+    <row r="35" spans="2:10" ht="16" thickBot="1">
       <c r="B35" s="199"/>
       <c r="G35" s="122"/>
     </row>
@@ -38876,7 +38876,7 @@
       <c r="E36" s="390"/>
       <c r="F36" s="391"/>
     </row>
-    <row r="37" spans="2:10" ht="15" thickBot="1">
+    <row r="37" spans="2:10" ht="16" thickBot="1">
       <c r="B37" s="200">
         <v>0.03</v>
       </c>
@@ -39011,7 +39011,7 @@
         <v>312500</v>
       </c>
     </row>
-    <row r="43" spans="2:10" ht="15" thickBot="1">
+    <row r="43" spans="2:10" ht="16" thickBot="1">
       <c r="B43" s="200"/>
       <c r="C43"/>
       <c r="D43" s="203">
@@ -39027,7 +39027,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="44" spans="2:10" ht="15.45" thickTop="1" thickBot="1">
+    <row r="44" spans="2:10" ht="17" thickTop="1" thickBot="1">
       <c r="B44" s="206"/>
       <c r="C44" s="198"/>
       <c r="D44" s="198"/>
@@ -39037,7 +39037,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="45" spans="2:10" ht="15" thickBot="1">
+    <row r="45" spans="2:10" ht="16" thickBot="1">
       <c r="B45" s="161"/>
       <c r="C45"/>
       <c r="D45"/>
@@ -39175,7 +39175,7 @@
         <v>374999.99999999988</v>
       </c>
     </row>
-    <row r="52" spans="2:10" ht="15" thickBot="1">
+    <row r="52" spans="2:10" ht="16" thickBot="1">
       <c r="B52" s="200"/>
       <c r="C52"/>
       <c r="D52" s="203">
@@ -39188,14 +39188,14 @@
         <v>1250000</v>
       </c>
     </row>
-    <row r="53" spans="2:10" ht="15.45" thickTop="1" thickBot="1">
+    <row r="53" spans="2:10" ht="17" thickTop="1" thickBot="1">
       <c r="B53" s="178"/>
       <c r="C53" s="198"/>
       <c r="D53" s="198"/>
       <c r="E53" s="207"/>
       <c r="F53" s="208"/>
     </row>
-    <row r="54" spans="2:10" ht="15" thickBot="1">
+    <row r="54" spans="2:10" ht="16" thickBot="1">
       <c r="B54"/>
       <c r="C54"/>
       <c r="D54"/>
@@ -39291,7 +39291,7 @@
         <v>437499.99999999983</v>
       </c>
     </row>
-    <row r="60" spans="2:10" ht="15" thickBot="1">
+    <row r="60" spans="2:10" ht="16" thickBot="1">
       <c r="B60" s="200"/>
       <c r="C60"/>
       <c r="D60" s="203">
@@ -39304,14 +39304,14 @@
         <v>999999.99999999977</v>
       </c>
     </row>
-    <row r="61" spans="2:10" ht="15.45" thickTop="1" thickBot="1">
+    <row r="61" spans="2:10" ht="17" thickTop="1" thickBot="1">
       <c r="B61" s="178"/>
       <c r="C61" s="198"/>
       <c r="D61" s="198"/>
       <c r="E61" s="207"/>
       <c r="F61" s="208"/>
     </row>
-    <row r="62" spans="2:10" ht="15" thickBot="1">
+    <row r="62" spans="2:10" ht="16" thickBot="1">
       <c r="B62"/>
       <c r="C62"/>
       <c r="D62"/>
@@ -39386,7 +39386,7 @@
         <v>499999.99999999983</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" thickBot="1">
+    <row r="67" spans="2:6" ht="16" thickBot="1">
       <c r="B67" s="200"/>
       <c r="C67"/>
       <c r="D67" s="203">
@@ -39399,14 +39399,14 @@
         <v>812499.99999999977</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="15.45" thickTop="1" thickBot="1">
+    <row r="68" spans="2:6" ht="17" thickTop="1" thickBot="1">
       <c r="B68" s="178"/>
       <c r="C68" s="198"/>
       <c r="D68" s="198"/>
       <c r="E68" s="207"/>
       <c r="F68" s="208"/>
     </row>
-    <row r="69" spans="2:6" ht="15" thickBot="1">
+    <row r="69" spans="2:6" ht="16" thickBot="1">
       <c r="B69"/>
       <c r="C69"/>
       <c r="D69"/>
@@ -39460,7 +39460,7 @@
         <v>562500</v>
       </c>
     </row>
-    <row r="73" spans="2:6" ht="15" thickBot="1">
+    <row r="73" spans="2:6" ht="16" thickBot="1">
       <c r="B73" s="200"/>
       <c r="C73"/>
       <c r="D73" s="203">
@@ -39473,14 +39473,14 @@
         <v>687500</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15.45" thickTop="1" thickBot="1">
+    <row r="74" spans="2:6" ht="17" thickTop="1" thickBot="1">
       <c r="B74" s="178"/>
       <c r="C74" s="198"/>
       <c r="D74" s="198"/>
       <c r="E74" s="207"/>
       <c r="F74" s="208"/>
     </row>
-    <row r="75" spans="2:6" ht="15" thickBot="1">
+    <row r="75" spans="2:6" ht="16" thickBot="1">
       <c r="B75"/>
       <c r="C75"/>
       <c r="D75"/>
@@ -39513,7 +39513,7 @@
         <v>625000</v>
       </c>
     </row>
-    <row r="78" spans="2:6" ht="15" thickBot="1">
+    <row r="78" spans="2:6" ht="16" thickBot="1">
       <c r="B78" s="200"/>
       <c r="C78"/>
       <c r="D78" s="203">
@@ -39526,7 +39526,7 @@
         <v>625000</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="15.45" thickTop="1" thickBot="1">
+    <row r="79" spans="2:6" ht="17" thickTop="1" thickBot="1">
       <c r="B79" s="178"/>
       <c r="C79" s="198"/>
       <c r="D79" s="198"/>
@@ -39552,13 +39552,13 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="83" spans="2:6" ht="15" thickBot="1">
+    <row r="83" spans="2:6" ht="16" thickBot="1">
       <c r="D83" s="211">
         <f>SUM(D81:D82)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="2:6" ht="15" thickTop="1"/>
+    <row r="84" spans="2:6" ht="16" thickTop="1"/>
     <row r="85" spans="2:6">
       <c r="B85" s="93">
         <v>100</v>
@@ -39663,32 +39663,32 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DD69E55-8751-4702-BEB3-64908D78129A}">
   <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.3046875" style="44" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" style="44" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="44" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" style="44" customWidth="1"/>
-    <col min="4" max="4" width="57.3046875" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.15234375" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.15234375" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.1640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1640625" style="28" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="44" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.15234375" style="46" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.15234375" style="44" customWidth="1"/>
-    <col min="10" max="10" width="16.69140625" style="44" customWidth="1"/>
+    <col min="8" max="8" width="26.1640625" style="46" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1640625" style="44" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" style="44" customWidth="1"/>
     <col min="11" max="11" width="16" style="44" customWidth="1"/>
-    <col min="12" max="12" width="17.69140625" style="44" customWidth="1"/>
-    <col min="13" max="13" width="14.15234375" style="44" customWidth="1"/>
-    <col min="14" max="14" width="18.3046875" style="47" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.3046875" style="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.15234375" style="48" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.69140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.15234375" style="44" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="57.3046875" style="44" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="55.15234375" style="49" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="55.15234375" style="14" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="9.15234375" style="14"/>
-    <col min="25" max="25" width="31.69140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.15234375" style="14"/>
+    <col min="12" max="12" width="17.6640625" style="44" customWidth="1"/>
+    <col min="13" max="13" width="14.1640625" style="44" customWidth="1"/>
+    <col min="14" max="14" width="18.33203125" style="47" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.1640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.6640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.1640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="57.33203125" style="44" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="55.1640625" style="49" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="55.1640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="9.1640625" style="14"/>
+    <col min="25" max="25" width="31.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.1640625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -39752,7 +39752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" ht="16">
       <c r="A2" s="64" t="s">
         <v>19</v>
       </c>
@@ -39813,7 +39813,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" ht="16">
       <c r="A3" s="15" t="s">
         <v>19</v>
       </c>
@@ -39876,7 +39876,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" ht="16">
       <c r="A4" s="15" t="s">
         <v>19</v>
       </c>
@@ -39927,7 +39927,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" ht="16">
       <c r="A5" s="15" t="s">
         <v>19</v>
       </c>
@@ -40023,12 +40023,12 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05D244E-AB1B-41CF-B074-63433A16BC3F}">
   <dimension ref="A2:F37"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="5" width="16.15234375" customWidth="1"/>
+    <col min="2" max="5" width="16.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="15" thickBot="1">
+    <row r="2" spans="1:6" ht="16" thickBot="1">
       <c r="B2" s="20" t="s">
         <v>706</v>
       </c>
@@ -40039,7 +40039,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" thickBot="1">
+    <row r="3" spans="1:6" ht="17" thickBot="1">
       <c r="B3" s="21" t="s">
         <v>647</v>
       </c>
@@ -40343,26 +40343,26 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1846D0AE-2EAB-454A-80C7-12C3C2C9CF42}">
-  <dimension ref="B1:Q128"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
+  <dimension ref="B1:Q129"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" customWidth="1"/>
-    <col min="2" max="2" width="30.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.1640625" customWidth="1"/>
+    <col min="2" max="2" width="30.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.3046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.69140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.3046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="43.15234375" customWidth="1"/>
-    <col min="8" max="8" width="25.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.3046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.1640625" customWidth="1"/>
+    <col min="8" max="8" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="25" customWidth="1"/>
-    <col min="12" max="12" width="16.69140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.3046875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="31.69140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.15234375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.1640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="40" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.3046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12">
@@ -40370,7 +40370,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="2:12" ht="15" thickBot="1">
+    <row r="2" spans="2:12" ht="16" thickBot="1">
       <c r="J2" t="s">
         <v>196</v>
       </c>
@@ -40381,7 +40381,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="26.6" thickBot="1">
+    <row r="3" spans="2:12" ht="27" thickBot="1">
       <c r="B3" s="373" t="s">
         <v>1400</v>
       </c>
@@ -40398,7 +40398,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="17.8" customHeight="1">
+    <row r="4" spans="2:12" ht="17.75" customHeight="1">
       <c r="B4" s="245" t="s">
         <v>201</v>
       </c>
@@ -40531,9 +40531,1604 @@
       <c r="C10" s="277" t="s">
         <v>228</v>
       </c>
-      <c r="D10" s="277" t="s">
+      <c r="E10" s="232"/>
+      <c r="F10" s="232"/>
+      <c r="G10" s="232"/>
+      <c r="H10" s="276"/>
+      <c r="J10" t="s">
+        <v>229</v>
+      </c>
+      <c r="K10" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12">
+      <c r="B11" s="249" t="s">
+        <v>227</v>
+      </c>
+      <c r="C11" s="277" t="s">
         <v>1403</v>
       </c>
+      <c r="D11" s="277"/>
+      <c r="E11" s="232"/>
+      <c r="F11" s="232"/>
+      <c r="G11" s="232"/>
+      <c r="H11" s="276"/>
+    </row>
+    <row r="12" spans="2:12">
+      <c r="B12" s="250" t="s">
+        <v>231</v>
+      </c>
+      <c r="C12" s="288" t="s">
+        <v>228</v>
+      </c>
+      <c r="D12" s="237"/>
+      <c r="E12" s="237"/>
+      <c r="F12" s="237"/>
+      <c r="G12" s="285"/>
+      <c r="H12" s="289"/>
+      <c r="J12" t="s">
+        <v>232</v>
+      </c>
+      <c r="K12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12">
+      <c r="B13" s="240"/>
+      <c r="C13" s="232"/>
+      <c r="D13" s="232"/>
+      <c r="E13" s="252"/>
+      <c r="F13" s="232"/>
+      <c r="G13" s="232"/>
+      <c r="H13" s="276"/>
+      <c r="J13" t="s">
+        <v>234</v>
+      </c>
+      <c r="K13" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" s="250" t="s">
+        <v>236</v>
+      </c>
+      <c r="C14" s="237" t="s">
+        <v>212</v>
+      </c>
+      <c r="D14" s="237"/>
+      <c r="E14" s="237"/>
+      <c r="F14" s="274" t="s">
+        <v>238</v>
+      </c>
+      <c r="G14" s="237" t="s">
+        <v>212</v>
+      </c>
+      <c r="H14" s="237"/>
+      <c r="J14" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="242"/>
+      <c r="C15" s="233"/>
+      <c r="D15" s="233"/>
+      <c r="E15" s="232" t="s">
+        <v>240</v>
+      </c>
+      <c r="F15" s="232" t="s">
+        <v>241</v>
+      </c>
+      <c r="G15" s="232"/>
+      <c r="H15" s="232"/>
+      <c r="J15" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="B16" s="250" t="s">
+        <v>243</v>
+      </c>
+      <c r="C16" s="237" t="s">
+        <v>602</v>
+      </c>
+      <c r="D16" s="237" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E16" s="361">
+        <v>67</v>
+      </c>
+      <c r="F16" s="237" t="s">
+        <v>237</v>
+      </c>
+      <c r="G16" s="285" t="s">
+        <v>687</v>
+      </c>
+      <c r="H16" s="285"/>
+      <c r="J16" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" s="240"/>
+      <c r="C17" s="363" t="s">
+        <v>602</v>
+      </c>
+      <c r="D17" s="363" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E17" s="362">
+        <v>322</v>
+      </c>
+      <c r="F17" s="363" t="s">
+        <v>237</v>
+      </c>
+      <c r="G17" s="240" t="s">
+        <v>687</v>
+      </c>
+      <c r="H17" s="240"/>
+    </row>
+    <row r="18" spans="2:10">
+      <c r="B18" s="250"/>
+      <c r="C18" s="277" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D18" s="237" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E18" s="361">
+        <v>67</v>
+      </c>
+      <c r="F18" s="237" t="s">
+        <v>237</v>
+      </c>
+      <c r="G18" s="285" t="s">
+        <v>687</v>
+      </c>
+      <c r="H18" s="285"/>
+    </row>
+    <row r="19" spans="2:10">
+      <c r="B19" s="240"/>
+      <c r="C19" s="277" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D19" s="363" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E19" s="362">
+        <v>322</v>
+      </c>
+      <c r="F19" s="363" t="s">
+        <v>237</v>
+      </c>
+      <c r="G19" s="240" t="s">
+        <v>687</v>
+      </c>
+      <c r="H19" s="232"/>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" s="250"/>
+      <c r="C20" s="237"/>
+      <c r="D20" s="237"/>
+      <c r="E20" s="236"/>
+      <c r="F20" s="237"/>
+      <c r="G20" s="285"/>
+      <c r="H20" s="285"/>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21" s="242"/>
+      <c r="C21" s="233"/>
+      <c r="D21" s="233"/>
+      <c r="E21" s="232"/>
+      <c r="F21" s="232"/>
+      <c r="G21" s="232"/>
+      <c r="H21" s="232"/>
+      <c r="J21" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" s="250" t="s">
+        <v>247</v>
+      </c>
+      <c r="C22" s="237" t="s">
+        <v>248</v>
+      </c>
+      <c r="D22" s="237" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="236" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="237" t="s">
+        <v>249</v>
+      </c>
+      <c r="G22" s="285"/>
+      <c r="H22" s="285"/>
+      <c r="J22" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
+      <c r="B23" s="240"/>
+      <c r="C23" s="232" t="s">
+        <v>317</v>
+      </c>
+      <c r="D23" s="371" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E23" s="252" t="s">
+        <v>1432</v>
+      </c>
+      <c r="F23" s="232" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G23" s="232"/>
+      <c r="H23" s="232"/>
+      <c r="J23" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10">
+      <c r="B24" s="239"/>
+      <c r="C24" s="237"/>
+      <c r="D24" s="237"/>
+      <c r="E24" s="236"/>
+      <c r="F24" s="237"/>
+      <c r="G24" s="237"/>
+      <c r="H24" s="237"/>
+      <c r="J24" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
+      <c r="B25" s="240"/>
+      <c r="C25" s="232"/>
+      <c r="D25" s="232"/>
+      <c r="E25" s="252"/>
+      <c r="F25" s="232"/>
+      <c r="G25" s="232"/>
+      <c r="H25" s="232"/>
+      <c r="J25" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10">
+      <c r="B26" s="239"/>
+      <c r="C26" s="237"/>
+      <c r="D26" s="237"/>
+      <c r="E26" s="236"/>
+      <c r="F26" s="237"/>
+      <c r="G26" s="237"/>
+      <c r="H26" s="237"/>
+      <c r="J26" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10">
+      <c r="B27" s="240"/>
+      <c r="C27" s="232"/>
+      <c r="D27" s="232"/>
+      <c r="E27" s="252"/>
+      <c r="F27" s="232"/>
+      <c r="G27" s="232"/>
+      <c r="H27" s="232"/>
+    </row>
+    <row r="29" spans="2:10">
+      <c r="B29" t="s">
+        <v>259</v>
+      </c>
+      <c r="C29" s="69" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D29" t="s">
+        <v>260</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" ht="16">
+      <c r="B31" s="170" t="s">
+        <v>262</v>
+      </c>
+      <c r="C31" s="170" t="s">
+        <v>263</v>
+      </c>
+      <c r="D31" s="170" t="s">
+        <v>264</v>
+      </c>
+      <c r="E31" s="170" t="s">
+        <v>265</v>
+      </c>
+      <c r="F31" s="170" t="s">
+        <v>266</v>
+      </c>
+      <c r="G31" s="170" t="s">
+        <v>267</v>
+      </c>
+      <c r="H31" s="170" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" hidden="1" outlineLevel="1">
+      <c r="B32" s="14"/>
+      <c r="D32" t="e">
+        <f>VLOOKUP(C32,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E32" s="218"/>
+    </row>
+    <row r="33" spans="4:6" hidden="1" outlineLevel="1">
+      <c r="D33" t="e">
+        <f>VLOOKUP(C33,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E33" s="218"/>
+    </row>
+    <row r="34" spans="4:6" hidden="1" outlineLevel="1">
+      <c r="D34" t="e">
+        <f>VLOOKUP(C34,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E34" s="218"/>
+      <c r="F34" s="232"/>
+    </row>
+    <row r="35" spans="4:6" hidden="1" outlineLevel="1">
+      <c r="D35" t="e">
+        <f>VLOOKUP(C35,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E35" s="218"/>
+    </row>
+    <row r="36" spans="4:6" hidden="1" outlineLevel="1">
+      <c r="D36" t="e">
+        <f>VLOOKUP(C36,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E36" s="218"/>
+    </row>
+    <row r="37" spans="4:6" hidden="1" outlineLevel="1">
+      <c r="D37" t="e">
+        <f>VLOOKUP(C37,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E37" s="218"/>
+    </row>
+    <row r="38" spans="4:6" hidden="1" outlineLevel="1">
+      <c r="D38" t="e">
+        <f>VLOOKUP(C38,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E38" s="218"/>
+    </row>
+    <row r="39" spans="4:6" hidden="1" outlineLevel="1">
+      <c r="D39" t="e">
+        <f>VLOOKUP(C39,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E39" s="218"/>
+    </row>
+    <row r="40" spans="4:6" hidden="1" outlineLevel="1">
+      <c r="D40" t="e">
+        <f>VLOOKUP(C40,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E40" s="218"/>
+    </row>
+    <row r="41" spans="4:6" hidden="1" outlineLevel="1">
+      <c r="D41" t="e">
+        <f>VLOOKUP(C41,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E41" s="218"/>
+    </row>
+    <row r="42" spans="4:6" hidden="1" outlineLevel="1">
+      <c r="D42" t="e">
+        <f>VLOOKUP(C42,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E42" s="218"/>
+    </row>
+    <row r="43" spans="4:6" hidden="1" outlineLevel="1">
+      <c r="D43" t="e">
+        <f>VLOOKUP(C43,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E43" s="218"/>
+    </row>
+    <row r="44" spans="4:6" hidden="1" outlineLevel="1">
+      <c r="D44" t="e">
+        <f>VLOOKUP(C44,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E44" s="218"/>
+    </row>
+    <row r="45" spans="4:6" hidden="1" outlineLevel="1">
+      <c r="D45" t="e">
+        <f>VLOOKUP(C45,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E45" s="218"/>
+    </row>
+    <row r="46" spans="4:6" hidden="1" outlineLevel="1">
+      <c r="D46" t="e">
+        <f>VLOOKUP(C46,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E46" s="218"/>
+    </row>
+    <row r="47" spans="4:6" hidden="1" outlineLevel="1">
+      <c r="D47" t="e">
+        <f>VLOOKUP(C47,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E47" s="218"/>
+    </row>
+    <row r="48" spans="4:6" hidden="1" outlineLevel="1">
+      <c r="D48" t="e">
+        <f>VLOOKUP(C48,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E48" s="218"/>
+    </row>
+    <row r="49" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="D49" t="e">
+        <f>VLOOKUP(C49,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E49" s="218"/>
+    </row>
+    <row r="50" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="D50" t="e">
+        <f>VLOOKUP(C50,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E50" s="218"/>
+    </row>
+    <row r="51" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="D51" t="e">
+        <f>VLOOKUP(C51,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E51" s="218"/>
+    </row>
+    <row r="52" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="D52" t="e">
+        <f>VLOOKUP(C52,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E52" s="218"/>
+    </row>
+    <row r="53" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="D53" t="e">
+        <f>VLOOKUP(C53,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E53" s="218"/>
+    </row>
+    <row r="54" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="D54" t="e">
+        <f>VLOOKUP(C54,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E54" s="218"/>
+    </row>
+    <row r="55" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="D55" t="e">
+        <f>VLOOKUP(C55,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E55" s="218"/>
+      <c r="G55" s="69"/>
+    </row>
+    <row r="56" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="D56" t="e">
+        <f>VLOOKUP(C56,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="57" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="D57" t="e">
+        <f>VLOOKUP(C57,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="58" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="D58" t="e">
+        <f>VLOOKUP(C58,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="59" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="D59" t="e">
+        <f>VLOOKUP(C59,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="60" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="D60" t="e">
+        <f>VLOOKUP(C60,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="61" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="D61" t="e">
+        <f>VLOOKUP(C61,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="62" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="D62" t="e">
+        <f>VLOOKUP(C62,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="63" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="D63" t="e">
+        <f>VLOOKUP(C63,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="64" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="D64" t="e">
+        <f>VLOOKUP(C64,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="D65" t="e">
+        <f>VLOOKUP(C65,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="D66" t="e">
+        <f>VLOOKUP(C66,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" outlineLevel="1">
+      <c r="B67" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C67" t="s">
+        <v>204</v>
+      </c>
+      <c r="D67" t="str">
+        <f>VLOOKUP(C67,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>Company Setup</v>
+      </c>
+      <c r="E67" s="140">
+        <v>45924</v>
+      </c>
+      <c r="F67" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G67" s="69" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H67" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="68" spans="2:17" outlineLevel="1">
+      <c r="B68" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C68" t="s">
+        <v>204</v>
+      </c>
+      <c r="D68" t="str">
+        <f>VLOOKUP(C68,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>Company Setup</v>
+      </c>
+      <c r="E68" s="140">
+        <v>45899</v>
+      </c>
+      <c r="G68" s="69" t="s">
+        <v>1422</v>
+      </c>
+      <c r="H68" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17">
+      <c r="D69" t="e">
+        <f>VLOOKUP(C69,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" ht="16">
+      <c r="B70" s="170" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" s="199" customFormat="1">
+      <c r="B71" s="350" t="s">
+        <v>265</v>
+      </c>
+      <c r="C71" s="350" t="s">
+        <v>290</v>
+      </c>
+      <c r="D71" s="350" t="s">
+        <v>291</v>
+      </c>
+      <c r="E71" s="351" t="s">
+        <v>292</v>
+      </c>
+      <c r="F71" s="350" t="s">
+        <v>293</v>
+      </c>
+      <c r="G71" s="350" t="s">
+        <v>294</v>
+      </c>
+      <c r="H71" s="352" t="s">
+        <v>295</v>
+      </c>
+      <c r="I71" s="353" t="s">
+        <v>296</v>
+      </c>
+      <c r="J71" s="354" t="s">
+        <v>297</v>
+      </c>
+      <c r="K71" s="199" t="s">
+        <v>298</v>
+      </c>
+      <c r="L71" s="199" t="s">
+        <v>299</v>
+      </c>
+      <c r="M71" s="199" t="s">
+        <v>300</v>
+      </c>
+      <c r="N71" s="354" t="s">
+        <v>301</v>
+      </c>
+      <c r="O71" s="199" t="s">
+        <v>302</v>
+      </c>
+      <c r="P71" s="199" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q71" s="199" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B72" s="140"/>
+      <c r="C72" s="93"/>
+      <c r="D72" s="93"/>
+      <c r="E72" s="93"/>
+      <c r="F72" s="93"/>
+      <c r="G72" s="93"/>
+      <c r="H72" s="93"/>
+      <c r="I72" s="93"/>
+      <c r="J72" s="209"/>
+      <c r="K72" s="93"/>
+      <c r="L72" s="93"/>
+      <c r="M72" s="93"/>
+      <c r="N72" s="209"/>
+      <c r="O72" s="93"/>
+      <c r="P72" s="93"/>
+      <c r="Q72" s="93"/>
+    </row>
+    <row r="73" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B73" s="140"/>
+      <c r="C73" s="93"/>
+      <c r="D73" s="93"/>
+      <c r="E73" s="93"/>
+      <c r="F73" s="93"/>
+      <c r="G73" s="93"/>
+      <c r="H73" s="93"/>
+      <c r="I73" s="93"/>
+      <c r="J73" s="209"/>
+      <c r="K73" s="93"/>
+      <c r="L73" s="93"/>
+      <c r="M73" s="93"/>
+      <c r="N73" s="209"/>
+      <c r="O73" s="93"/>
+      <c r="P73" s="93"/>
+      <c r="Q73" s="93"/>
+    </row>
+    <row r="74" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B74" s="140"/>
+      <c r="C74" s="93"/>
+      <c r="D74" s="93"/>
+      <c r="E74" s="93"/>
+      <c r="F74" s="93"/>
+      <c r="G74" s="93"/>
+      <c r="H74" s="93"/>
+      <c r="I74" s="93"/>
+      <c r="J74" s="209"/>
+      <c r="K74" s="93"/>
+      <c r="L74" s="93"/>
+      <c r="M74" s="93"/>
+      <c r="N74" s="209"/>
+      <c r="O74" s="93"/>
+      <c r="P74" s="93"/>
+      <c r="Q74" s="93"/>
+    </row>
+    <row r="75" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B75" s="140"/>
+      <c r="C75" s="93"/>
+      <c r="D75" s="93"/>
+      <c r="E75" s="93"/>
+      <c r="F75" s="93"/>
+      <c r="G75" s="93"/>
+      <c r="H75" s="93"/>
+      <c r="I75" s="93"/>
+      <c r="J75" s="209"/>
+      <c r="K75" s="93"/>
+      <c r="L75" s="93"/>
+      <c r="M75" s="93"/>
+      <c r="N75" s="209"/>
+      <c r="O75" s="93"/>
+      <c r="P75" s="93"/>
+      <c r="Q75" s="93"/>
+    </row>
+    <row r="76" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B76" s="140"/>
+      <c r="C76" s="93"/>
+      <c r="D76" s="93"/>
+      <c r="E76" s="93"/>
+      <c r="F76" s="93"/>
+      <c r="G76" s="93"/>
+      <c r="H76" s="93"/>
+      <c r="I76" s="93"/>
+      <c r="J76" s="209"/>
+      <c r="K76" s="93"/>
+      <c r="L76" s="93"/>
+      <c r="M76" s="93"/>
+      <c r="N76" s="209"/>
+      <c r="O76" s="93"/>
+      <c r="P76" s="93"/>
+      <c r="Q76" s="93"/>
+    </row>
+    <row r="77" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B77" s="140"/>
+      <c r="C77" s="93"/>
+      <c r="D77" s="93"/>
+      <c r="E77" s="93"/>
+      <c r="F77" s="93"/>
+      <c r="G77" s="93"/>
+      <c r="H77" s="93"/>
+      <c r="I77" s="93"/>
+      <c r="J77" s="209"/>
+      <c r="K77" s="93"/>
+      <c r="L77" s="93"/>
+      <c r="M77" s="93"/>
+      <c r="N77" s="209"/>
+      <c r="O77" s="93"/>
+      <c r="P77" s="93"/>
+      <c r="Q77" s="93"/>
+    </row>
+    <row r="78" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B78" s="140"/>
+      <c r="C78" s="93"/>
+      <c r="D78" s="93"/>
+      <c r="E78" s="93"/>
+      <c r="F78" s="93"/>
+      <c r="G78" s="93"/>
+      <c r="H78" s="93"/>
+      <c r="I78" s="93"/>
+      <c r="J78" s="209"/>
+      <c r="K78" s="93"/>
+      <c r="L78" s="93"/>
+      <c r="M78" s="93"/>
+      <c r="N78" s="209"/>
+      <c r="O78" s="93"/>
+      <c r="P78" s="93"/>
+      <c r="Q78" s="93"/>
+    </row>
+    <row r="79" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B79" s="140"/>
+      <c r="C79" s="93"/>
+      <c r="D79" s="93"/>
+      <c r="E79" s="93"/>
+      <c r="F79" s="93"/>
+      <c r="G79" s="93"/>
+      <c r="H79" s="93"/>
+      <c r="I79" s="93"/>
+      <c r="J79" s="209"/>
+      <c r="K79" s="93"/>
+      <c r="L79" s="93"/>
+      <c r="M79" s="93"/>
+      <c r="N79" s="209"/>
+      <c r="O79" s="93"/>
+      <c r="P79" s="93"/>
+      <c r="Q79" s="93"/>
+    </row>
+    <row r="80" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B80" s="140"/>
+      <c r="C80" s="93"/>
+      <c r="D80" s="93"/>
+      <c r="E80" s="93"/>
+      <c r="F80" s="93"/>
+      <c r="G80" s="93"/>
+      <c r="H80" s="93"/>
+      <c r="I80" s="93"/>
+      <c r="J80" s="209"/>
+      <c r="K80" s="93"/>
+      <c r="L80" s="93"/>
+      <c r="M80" s="93"/>
+      <c r="N80" s="209"/>
+      <c r="O80" s="93"/>
+      <c r="P80" s="93"/>
+      <c r="Q80" s="93"/>
+    </row>
+    <row r="81" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B81" s="140"/>
+      <c r="C81" s="93"/>
+      <c r="D81" s="93"/>
+      <c r="E81" s="93"/>
+      <c r="F81" s="93"/>
+      <c r="G81" s="93"/>
+      <c r="H81" s="93"/>
+      <c r="I81" s="93"/>
+      <c r="J81" s="209"/>
+      <c r="K81" s="93"/>
+      <c r="L81" s="93"/>
+      <c r="M81" s="93"/>
+      <c r="N81" s="209"/>
+      <c r="O81" s="93"/>
+      <c r="P81" s="93"/>
+      <c r="Q81" s="93"/>
+    </row>
+    <row r="82" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B82" s="140"/>
+      <c r="C82" s="93"/>
+      <c r="D82" s="93"/>
+      <c r="E82" s="93"/>
+      <c r="F82" s="93"/>
+      <c r="G82" s="93"/>
+      <c r="H82" s="93"/>
+      <c r="I82" s="93"/>
+      <c r="J82" s="209"/>
+      <c r="K82" s="93"/>
+      <c r="L82" s="93"/>
+      <c r="M82" s="93"/>
+      <c r="N82" s="209"/>
+      <c r="O82" s="93"/>
+      <c r="P82" s="93"/>
+      <c r="Q82" s="93"/>
+    </row>
+    <row r="83" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B83" s="140"/>
+      <c r="C83" s="93"/>
+      <c r="D83" s="93"/>
+      <c r="E83" s="93"/>
+      <c r="F83" s="93"/>
+      <c r="G83" s="93"/>
+      <c r="H83" s="93"/>
+      <c r="I83" s="93"/>
+      <c r="J83" s="209"/>
+      <c r="K83" s="93"/>
+      <c r="L83" s="93"/>
+      <c r="M83" s="93"/>
+      <c r="N83" s="209"/>
+      <c r="O83" s="93"/>
+      <c r="P83" s="93"/>
+      <c r="Q83" s="93"/>
+    </row>
+    <row r="84" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B84" s="140"/>
+      <c r="C84" s="93"/>
+      <c r="D84" s="93"/>
+      <c r="E84" s="93"/>
+      <c r="F84" s="93"/>
+      <c r="G84" s="93"/>
+      <c r="H84" s="93"/>
+      <c r="I84" s="93"/>
+      <c r="J84" s="209"/>
+      <c r="K84" s="93"/>
+      <c r="L84" s="93"/>
+      <c r="M84" s="93"/>
+      <c r="N84" s="209"/>
+      <c r="O84" s="93"/>
+      <c r="P84" s="93"/>
+      <c r="Q84" s="93"/>
+    </row>
+    <row r="85" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B85" s="140"/>
+      <c r="C85" s="93"/>
+      <c r="D85" s="93"/>
+      <c r="E85" s="93"/>
+      <c r="F85" s="93"/>
+      <c r="G85" s="93"/>
+      <c r="H85" s="93"/>
+      <c r="I85" s="93"/>
+      <c r="J85" s="209"/>
+      <c r="K85" s="93"/>
+      <c r="L85" s="93"/>
+      <c r="M85" s="93"/>
+      <c r="N85" s="209"/>
+      <c r="O85" s="93"/>
+      <c r="P85" s="93"/>
+      <c r="Q85" s="93"/>
+    </row>
+    <row r="86" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B86" s="140"/>
+      <c r="C86" s="93"/>
+      <c r="D86" s="93"/>
+      <c r="E86" s="93"/>
+      <c r="F86" s="93"/>
+      <c r="G86" s="93"/>
+      <c r="H86" s="93"/>
+      <c r="I86" s="93"/>
+      <c r="J86" s="209"/>
+      <c r="K86" s="93"/>
+      <c r="L86" s="93"/>
+      <c r="M86" s="93"/>
+      <c r="N86" s="209"/>
+      <c r="O86" s="93"/>
+      <c r="P86" s="93"/>
+      <c r="Q86" s="93"/>
+    </row>
+    <row r="87" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B87" s="140"/>
+      <c r="C87" s="93"/>
+      <c r="D87" s="93"/>
+      <c r="E87" s="93"/>
+      <c r="F87" s="93"/>
+      <c r="G87" s="93"/>
+      <c r="H87" s="93"/>
+      <c r="I87" s="93"/>
+      <c r="J87" s="209"/>
+      <c r="K87" s="93"/>
+      <c r="L87" s="93"/>
+      <c r="M87" s="93"/>
+      <c r="N87" s="209"/>
+      <c r="O87" s="93"/>
+      <c r="P87" s="93"/>
+      <c r="Q87" s="93"/>
+    </row>
+    <row r="88" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B88" s="140"/>
+      <c r="C88" s="93"/>
+      <c r="D88" s="93"/>
+      <c r="E88" s="93"/>
+      <c r="F88" s="93"/>
+      <c r="G88" s="93"/>
+      <c r="H88" s="93"/>
+      <c r="I88" s="93"/>
+      <c r="J88" s="209"/>
+      <c r="K88" s="93"/>
+      <c r="L88" s="93"/>
+      <c r="M88" s="93"/>
+      <c r="N88" s="209"/>
+      <c r="O88" s="93"/>
+      <c r="P88" s="93"/>
+      <c r="Q88" s="93"/>
+    </row>
+    <row r="89" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B89" s="140"/>
+      <c r="C89" s="93"/>
+      <c r="D89" s="93"/>
+      <c r="E89" s="93"/>
+      <c r="F89" s="93"/>
+      <c r="G89" s="93"/>
+      <c r="H89" s="93"/>
+      <c r="I89" s="93"/>
+      <c r="J89" s="209"/>
+      <c r="K89" s="93"/>
+      <c r="L89" s="93"/>
+      <c r="M89" s="93"/>
+      <c r="N89" s="209"/>
+      <c r="O89" s="93"/>
+      <c r="P89" s="93"/>
+      <c r="Q89" s="93"/>
+    </row>
+    <row r="90" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B90" s="93"/>
+      <c r="C90" s="93"/>
+      <c r="D90" s="93"/>
+      <c r="E90" s="93"/>
+      <c r="F90" s="93"/>
+      <c r="G90" s="93"/>
+      <c r="H90" s="93"/>
+      <c r="I90" s="93"/>
+      <c r="J90" s="209"/>
+      <c r="K90" s="93"/>
+      <c r="L90" s="93"/>
+      <c r="M90" s="93"/>
+      <c r="N90" s="209"/>
+      <c r="O90" s="93"/>
+      <c r="P90" s="93"/>
+      <c r="Q90" s="93"/>
+    </row>
+    <row r="91" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B91" s="93"/>
+      <c r="C91" s="93"/>
+      <c r="D91" s="93"/>
+      <c r="E91" s="93"/>
+      <c r="F91" s="93"/>
+      <c r="G91" s="93"/>
+      <c r="H91" s="93"/>
+      <c r="I91" s="93"/>
+      <c r="J91" s="209"/>
+      <c r="K91" s="93"/>
+      <c r="L91" s="93"/>
+      <c r="M91" s="93"/>
+      <c r="N91" s="209"/>
+      <c r="O91" s="93"/>
+      <c r="P91" s="93"/>
+      <c r="Q91" s="93"/>
+    </row>
+    <row r="92" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B92" s="93"/>
+      <c r="C92" s="93"/>
+      <c r="D92" s="93"/>
+      <c r="E92" s="93"/>
+      <c r="F92" s="93"/>
+      <c r="G92" s="93"/>
+      <c r="H92" s="93"/>
+      <c r="I92" s="93"/>
+      <c r="J92" s="209"/>
+      <c r="K92" s="93"/>
+      <c r="L92" s="93"/>
+      <c r="M92" s="93"/>
+      <c r="N92" s="209"/>
+      <c r="O92" s="93"/>
+      <c r="P92" s="93"/>
+      <c r="Q92" s="93"/>
+    </row>
+    <row r="93" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B93" s="93"/>
+      <c r="C93" s="93"/>
+      <c r="D93" s="93"/>
+      <c r="E93" s="93"/>
+      <c r="F93" s="93"/>
+      <c r="G93" s="93"/>
+      <c r="H93" s="93"/>
+      <c r="I93" s="93"/>
+      <c r="J93" s="209"/>
+      <c r="K93" s="93"/>
+      <c r="L93" s="93"/>
+      <c r="M93" s="93"/>
+      <c r="N93" s="209"/>
+      <c r="O93" s="93"/>
+      <c r="P93" s="93"/>
+      <c r="Q93" s="93"/>
+    </row>
+    <row r="94" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B94" s="93"/>
+      <c r="C94" s="93"/>
+      <c r="D94" s="93"/>
+      <c r="E94" s="93"/>
+      <c r="F94" s="93"/>
+      <c r="G94" s="93"/>
+      <c r="H94" s="93"/>
+      <c r="I94" s="93"/>
+      <c r="J94" s="209"/>
+      <c r="K94" s="93"/>
+      <c r="L94" s="93"/>
+      <c r="M94" s="93"/>
+      <c r="N94" s="209"/>
+      <c r="O94" s="93"/>
+      <c r="P94" s="93"/>
+      <c r="Q94" s="93"/>
+    </row>
+    <row r="95" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B95" s="93"/>
+      <c r="C95" s="93"/>
+      <c r="D95" s="93"/>
+      <c r="E95" s="93"/>
+      <c r="F95" s="93"/>
+      <c r="G95" s="93"/>
+      <c r="H95" s="93"/>
+      <c r="I95" s="93"/>
+      <c r="J95" s="209"/>
+      <c r="K95" s="93"/>
+      <c r="L95" s="93"/>
+      <c r="M95" s="93"/>
+      <c r="N95" s="209"/>
+      <c r="O95" s="93"/>
+      <c r="P95" s="93"/>
+      <c r="Q95" s="93"/>
+    </row>
+    <row r="96" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B96" s="93"/>
+      <c r="C96" s="93"/>
+      <c r="D96" s="93"/>
+      <c r="E96" s="93"/>
+      <c r="F96" s="93"/>
+      <c r="G96" s="93"/>
+      <c r="H96" s="93"/>
+      <c r="I96" s="93"/>
+      <c r="J96" s="209"/>
+      <c r="K96" s="93"/>
+      <c r="L96" s="93"/>
+      <c r="M96" s="93"/>
+      <c r="N96" s="209"/>
+      <c r="O96" s="93"/>
+      <c r="P96" s="93"/>
+      <c r="Q96" s="93"/>
+    </row>
+    <row r="97" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B97" s="93"/>
+      <c r="C97" s="93"/>
+      <c r="D97" s="93"/>
+      <c r="E97" s="93"/>
+      <c r="F97" s="93"/>
+      <c r="G97" s="93"/>
+      <c r="H97" s="93"/>
+      <c r="I97" s="93"/>
+      <c r="J97" s="209"/>
+      <c r="K97" s="93"/>
+      <c r="L97" s="93"/>
+      <c r="M97" s="93"/>
+      <c r="N97" s="209"/>
+      <c r="O97" s="93"/>
+      <c r="P97" s="93"/>
+      <c r="Q97" s="93"/>
+    </row>
+    <row r="98" spans="2:17" outlineLevel="1">
+      <c r="B98" s="140">
+        <v>45924</v>
+      </c>
+      <c r="C98" s="93" t="s">
+        <v>437</v>
+      </c>
+      <c r="D98" s="93" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E98" s="93">
+        <v>1</v>
+      </c>
+      <c r="F98" s="93">
+        <v>1</v>
+      </c>
+      <c r="G98" s="93">
+        <v>1</v>
+      </c>
+      <c r="H98" s="93">
+        <v>100</v>
+      </c>
+      <c r="I98" s="93"/>
+      <c r="J98" s="209">
+        <v>0.01</v>
+      </c>
+      <c r="K98" s="93">
+        <v>0</v>
+      </c>
+      <c r="L98" s="93" t="s">
+        <v>403</v>
+      </c>
+      <c r="M98" s="93">
+        <v>100</v>
+      </c>
+      <c r="N98" s="209">
+        <v>1</v>
+      </c>
+      <c r="O98" s="93" t="s">
+        <v>403</v>
+      </c>
+      <c r="P98" s="93" t="s">
+        <v>684</v>
+      </c>
+      <c r="Q98" s="93"/>
+    </row>
+    <row r="100" spans="2:17" ht="16">
+      <c r="B100" s="170" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="101" spans="2:17">
+      <c r="B101" t="s">
+        <v>224</v>
+      </c>
+      <c r="C101" t="s">
+        <v>306</v>
+      </c>
+      <c r="D101" t="s">
+        <v>307</v>
+      </c>
+      <c r="E101" t="s">
+        <v>265</v>
+      </c>
+      <c r="F101" t="s">
+        <v>308</v>
+      </c>
+      <c r="G101" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="102" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="D102" s="112"/>
+      <c r="E102" s="218"/>
+    </row>
+    <row r="103" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="D103" s="112"/>
+      <c r="E103" s="218"/>
+    </row>
+    <row r="104" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="D104" s="112"/>
+      <c r="E104" s="218"/>
+    </row>
+    <row r="105" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="D105" s="112"/>
+      <c r="E105" s="218"/>
+    </row>
+    <row r="106" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="D106" s="112"/>
+    </row>
+    <row r="107" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="D107" s="112"/>
+    </row>
+    <row r="108" spans="2:17" collapsed="1"/>
+    <row r="109" spans="2:17" ht="16">
+      <c r="B109" s="170" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="110" spans="2:17">
+      <c r="B110" t="s">
+        <v>310</v>
+      </c>
+      <c r="C110" t="s">
+        <v>311</v>
+      </c>
+      <c r="D110" t="s">
+        <v>312</v>
+      </c>
+      <c r="E110" t="s">
+        <v>313</v>
+      </c>
+      <c r="F110" t="s">
+        <v>314</v>
+      </c>
+      <c r="G110" t="s">
+        <v>705</v>
+      </c>
+      <c r="H110" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="111" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="H111" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="H112" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="8:8" hidden="1" outlineLevel="1">
+      <c r="H113" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="8:8" hidden="1" outlineLevel="1">
+      <c r="H114" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="8:8" hidden="1" outlineLevel="1">
+      <c r="H115" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="8:8" hidden="1" outlineLevel="1">
+      <c r="H116" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="8:8" hidden="1" outlineLevel="1">
+      <c r="H117" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="8:8" hidden="1" outlineLevel="1">
+      <c r="H118" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="8:8" hidden="1" outlineLevel="1">
+      <c r="H119" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="8:8" hidden="1" outlineLevel="1">
+      <c r="H120" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="8:8" hidden="1" outlineLevel="1">
+      <c r="H121" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="8:8" hidden="1" outlineLevel="1">
+      <c r="H122" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="8:8" hidden="1" outlineLevel="1">
+      <c r="H123" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="8:8" hidden="1" outlineLevel="1">
+      <c r="H124" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="8:8" hidden="1" outlineLevel="1">
+      <c r="H125" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="8:8" hidden="1" outlineLevel="1">
+      <c r="H126" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="8:8" hidden="1" outlineLevel="1">
+      <c r="H127" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="8:8" hidden="1" outlineLevel="1">
+      <c r="H128" s="112">
+        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" collapsed="1"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C6:D6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C29" r:id="rId1" xr:uid="{21236431-21D4-4AD6-90BA-074538FA8A2F}"/>
+    <hyperlink ref="G67" r:id="rId2" display="../../../../../:b:/g/personal/robert_tekna_com_au/EcSxjR_BpMxLuckkSUQsPOMB3TYfXdzMGevsOWH_kuuT-w?e=D4nAbJ" xr:uid="{9DC9F06E-48B4-4A23-93FE-BDDE4F5FD03D}"/>
+    <hyperlink ref="G68" r:id="rId3" xr:uid="{22AE8784-93DF-4E6F-B478-E21F28FD9236}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <tableParts count="4">
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{571D6050-55EE-4641-B36C-3AC667D32D48}">
+          <x14:formula1>
+            <xm:f>'Document Type'!$B$38:$B$39</xm:f>
+          </x14:formula1>
+          <xm:sqref>G6 F34 G14 C14 F16:F20</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BAB77F41-2822-4361-9344-38ED25D99101}">
+          <x14:formula1>
+            <xm:f>'Document Type'!$B$45:$B$47</xm:f>
+          </x14:formula1>
+          <xm:sqref>C8 G8</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C6F8AFED-E6DC-4108-9F3F-2E82086D811A}">
+          <x14:formula1>
+            <xm:f>'Document Type'!$B$49:$B$51</xm:f>
+          </x14:formula1>
+          <xm:sqref>C10:C12 C18:C19</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C158B414-685E-4574-B4D0-B2A61B26759A}">
+          <x14:formula1>
+            <xm:f>'Document Type'!$B$6:$B$34</xm:f>
+          </x14:formula1>
+          <xm:sqref>C32:C69</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13E41263-52DA-47DA-A9DF-C248772F9CCE}">
+  <dimension ref="B1:Q123"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="3.1640625" customWidth="1"/>
+    <col min="2" max="2" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.1640625" customWidth="1"/>
+    <col min="8" max="8" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="40" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12">
+      <c r="B1" s="69" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="2:12" ht="16" thickBot="1">
+      <c r="J2" t="s">
+        <v>196</v>
+      </c>
+      <c r="K2" t="s">
+        <v>197</v>
+      </c>
+      <c r="L2">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="27" thickBot="1">
+      <c r="B3" s="373" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C3" s="374"/>
+      <c r="D3" s="374"/>
+      <c r="E3" s="374"/>
+      <c r="F3" s="374"/>
+      <c r="G3" s="374"/>
+      <c r="H3" s="375"/>
+      <c r="J3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="17.75" customHeight="1">
+      <c r="B4" s="245" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C4" s="93"/>
+      <c r="D4" s="273" t="s">
+        <v>202</v>
+      </c>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="273" t="s">
+        <v>203</v>
+      </c>
+      <c r="H4" s="93"/>
+      <c r="J4" t="s">
+        <v>204</v>
+      </c>
+      <c r="K4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12">
+      <c r="B5" s="250" t="s">
+        <v>206</v>
+      </c>
+      <c r="C5" s="236">
+        <v>45924</v>
+      </c>
+      <c r="D5" s="236"/>
+      <c r="E5" s="237"/>
+      <c r="F5" s="274" t="s">
+        <v>207</v>
+      </c>
+      <c r="G5" s="285">
+        <v>100</v>
+      </c>
+      <c r="H5" s="289"/>
+      <c r="J5" t="s">
+        <v>208</v>
+      </c>
+      <c r="K5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
+      <c r="B6" s="251" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6" s="376" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D6" s="376"/>
+      <c r="E6" s="232"/>
+      <c r="F6" s="275" t="s">
+        <v>211</v>
+      </c>
+      <c r="G6" s="232"/>
+      <c r="H6" s="276"/>
+      <c r="J6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12">
+      <c r="B7" s="250" t="s">
+        <v>215</v>
+      </c>
+      <c r="C7" s="237"/>
+      <c r="D7" s="237"/>
+      <c r="E7" s="236"/>
+      <c r="F7" s="237"/>
+      <c r="G7" s="237"/>
+      <c r="H7" s="241"/>
+      <c r="J7" t="s">
+        <v>216</v>
+      </c>
+      <c r="K7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="B8" s="249" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" s="232" t="s">
+        <v>221</v>
+      </c>
+      <c r="D8" s="232"/>
+      <c r="E8" s="252"/>
+      <c r="F8" s="275" t="s">
+        <v>220</v>
+      </c>
+      <c r="G8" s="232"/>
+      <c r="H8" s="276"/>
+      <c r="J8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K8" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12">
+      <c r="B9" s="239"/>
+      <c r="C9" s="237"/>
+      <c r="D9" s="237" t="s">
+        <v>224</v>
+      </c>
+      <c r="E9" s="236"/>
+      <c r="F9" s="237"/>
+      <c r="G9" s="237"/>
+      <c r="H9" s="241"/>
+      <c r="J9" t="s">
+        <v>225</v>
+      </c>
+      <c r="K9" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" s="249" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="277" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" s="252"/>
       <c r="E10" s="232"/>
       <c r="F10" s="232"/>
       <c r="G10" s="232"/>
@@ -40619,230 +42214,181 @@
       <c r="B15" s="250" t="s">
         <v>243</v>
       </c>
-      <c r="C15" s="237" t="s">
+      <c r="C15" s="377" t="s">
         <v>602</v>
       </c>
-      <c r="D15" s="237" t="s">
-        <v>1399</v>
-      </c>
-      <c r="E15" s="361">
-        <v>67</v>
+      <c r="D15" s="377"/>
+      <c r="E15" s="237">
+        <v>100</v>
       </c>
       <c r="F15" s="237" t="s">
         <v>237</v>
       </c>
-      <c r="G15" s="285" t="s">
-        <v>687</v>
-      </c>
-      <c r="H15" s="285"/>
+      <c r="G15" s="237"/>
+      <c r="H15" s="237"/>
       <c r="J15" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="16" spans="2:12">
-      <c r="B16" s="240"/>
-      <c r="C16" s="363" t="s">
-        <v>602</v>
-      </c>
-      <c r="D16" s="363" t="s">
-        <v>1404</v>
-      </c>
-      <c r="E16" s="362">
-        <v>322</v>
-      </c>
-      <c r="F16" s="363" t="s">
-        <v>237</v>
-      </c>
-      <c r="G16" s="240" t="s">
-        <v>687</v>
-      </c>
-      <c r="H16" s="240"/>
+      <c r="B16" s="242"/>
+      <c r="C16" s="233"/>
+      <c r="D16" s="233"/>
+      <c r="E16" s="232"/>
+      <c r="F16" s="232"/>
+      <c r="G16" s="232"/>
+      <c r="H16" s="232"/>
+      <c r="J16" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="17" spans="2:10">
-      <c r="B17" s="250"/>
+      <c r="B17" s="250" t="s">
+        <v>247</v>
+      </c>
       <c r="C17" s="237" t="s">
-        <v>602</v>
+        <v>248</v>
       </c>
       <c r="D17" s="237" t="s">
-        <v>1399</v>
-      </c>
-      <c r="E17" s="361">
-        <v>67</v>
+        <v>82</v>
+      </c>
+      <c r="E17" s="236" t="s">
+        <v>83</v>
       </c>
       <c r="F17" s="237" t="s">
-        <v>237</v>
-      </c>
-      <c r="G17" s="285" t="s">
-        <v>687</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="G17" s="285"/>
       <c r="H17" s="285"/>
+      <c r="J17" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="18" spans="2:10">
       <c r="B18" s="240"/>
-      <c r="C18" s="363" t="s">
-        <v>602</v>
-      </c>
-      <c r="D18" s="363" t="s">
-        <v>1404</v>
-      </c>
-      <c r="E18" s="362">
-        <v>322</v>
-      </c>
-      <c r="F18" s="363" t="s">
-        <v>237</v>
-      </c>
-      <c r="G18" s="240" t="s">
-        <v>687</v>
-      </c>
+      <c r="C18" s="232"/>
+      <c r="D18" s="232"/>
+      <c r="E18" s="252"/>
+      <c r="F18" s="232"/>
+      <c r="G18" s="232"/>
       <c r="H18" s="232"/>
+      <c r="J18" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="250"/>
+      <c r="B19" s="239"/>
       <c r="C19" s="237"/>
       <c r="D19" s="237"/>
       <c r="E19" s="236"/>
       <c r="F19" s="237"/>
-      <c r="G19" s="285"/>
-      <c r="H19" s="285"/>
+      <c r="G19" s="237"/>
+      <c r="H19" s="237"/>
+      <c r="J19" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="20" spans="2:10">
-      <c r="B20" s="242"/>
-      <c r="C20" s="233"/>
-      <c r="D20" s="233"/>
-      <c r="E20" s="232"/>
+      <c r="B20" s="240"/>
+      <c r="C20" s="232"/>
+      <c r="D20" s="232"/>
+      <c r="E20" s="252"/>
       <c r="F20" s="232"/>
       <c r="G20" s="232"/>
       <c r="H20" s="232"/>
       <c r="J20" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="250" t="s">
-        <v>247</v>
-      </c>
-      <c r="C21" s="237" t="s">
-        <v>248</v>
-      </c>
-      <c r="D21" s="237" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" s="236" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" s="237" t="s">
-        <v>249</v>
-      </c>
-      <c r="G21" s="285"/>
-      <c r="H21" s="285"/>
+      <c r="B21" s="239"/>
+      <c r="C21" s="237"/>
+      <c r="D21" s="237"/>
+      <c r="E21" s="236"/>
+      <c r="F21" s="237"/>
+      <c r="G21" s="237"/>
+      <c r="H21" s="237"/>
       <c r="J21" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="2:10">
       <c r="B22" s="240"/>
-      <c r="C22" s="232" t="s">
-        <v>317</v>
-      </c>
-      <c r="D22" s="371" t="s">
-        <v>1431</v>
-      </c>
-      <c r="E22" s="252" t="s">
-        <v>1432</v>
-      </c>
-      <c r="F22" s="232" t="s">
-        <v>1433</v>
-      </c>
+      <c r="C22" s="232"/>
+      <c r="D22" s="232"/>
+      <c r="E22" s="252"/>
+      <c r="F22" s="232"/>
       <c r="G22" s="232"/>
       <c r="H22" s="232"/>
-      <c r="J22" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10">
-      <c r="B23" s="239"/>
-      <c r="C23" s="237"/>
-      <c r="D23" s="237"/>
-      <c r="E23" s="236"/>
-      <c r="F23" s="237"/>
-      <c r="G23" s="237"/>
-      <c r="H23" s="237"/>
-      <c r="J23" t="s">
-        <v>256</v>
-      </c>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="240"/>
-      <c r="C24" s="232"/>
-      <c r="D24" s="232"/>
-      <c r="E24" s="252"/>
-      <c r="F24" s="232"/>
-      <c r="G24" s="232"/>
-      <c r="H24" s="232"/>
-      <c r="J24" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10">
-      <c r="B25" s="239"/>
-      <c r="C25" s="237"/>
-      <c r="D25" s="237"/>
-      <c r="E25" s="236"/>
-      <c r="F25" s="237"/>
-      <c r="G25" s="237"/>
-      <c r="H25" s="237"/>
-      <c r="J25" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10">
-      <c r="B26" s="240"/>
-      <c r="C26" s="232"/>
-      <c r="D26" s="232"/>
-      <c r="E26" s="252"/>
-      <c r="F26" s="232"/>
-      <c r="G26" s="232"/>
-      <c r="H26" s="232"/>
-    </row>
-    <row r="28" spans="2:10">
-      <c r="B28" t="s">
+      <c r="B24" t="s">
         <v>259</v>
       </c>
-      <c r="C28" s="69" t="s">
-        <v>1405</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="C24" s="69" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D24" t="s">
         <v>260</v>
       </c>
-      <c r="E28" t="s">
-        <v>1406</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" ht="15.9">
-      <c r="B30" s="170" t="s">
+      <c r="E24" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" ht="16">
+      <c r="B26" s="170" t="s">
         <v>262</v>
       </c>
-      <c r="C30" s="170" t="s">
+      <c r="C26" s="170" t="s">
         <v>263</v>
       </c>
-      <c r="D30" s="170" t="s">
+      <c r="D26" s="170" t="s">
         <v>264</v>
       </c>
-      <c r="E30" s="170" t="s">
+      <c r="E26" s="170" t="s">
         <v>265</v>
       </c>
-      <c r="F30" s="170" t="s">
+      <c r="F26" s="170" t="s">
         <v>266</v>
       </c>
-      <c r="G30" s="170" t="s">
+      <c r="G26" s="170" t="s">
         <v>267</v>
       </c>
-      <c r="H30" s="170" t="s">
+      <c r="H26" s="170" t="s">
         <v>268</v>
       </c>
     </row>
+    <row r="27" spans="2:10" hidden="1" outlineLevel="1">
+      <c r="B27" s="14"/>
+      <c r="D27" t="e">
+        <f>VLOOKUP(C27,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E27" s="218"/>
+    </row>
+    <row r="28" spans="2:10" hidden="1" outlineLevel="1">
+      <c r="D28" t="e">
+        <f>VLOOKUP(C28,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E28" s="218"/>
+    </row>
+    <row r="29" spans="2:10" hidden="1" outlineLevel="1">
+      <c r="D29" t="e">
+        <f>VLOOKUP(C29,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E29" s="218"/>
+      <c r="F29" s="232"/>
+    </row>
+    <row r="30" spans="2:10" hidden="1" outlineLevel="1">
+      <c r="D30" t="e">
+        <f>VLOOKUP(C30,'Document Type'!$B$6:$C$34,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E30" s="218"/>
+    </row>
     <row r="31" spans="2:10" hidden="1" outlineLevel="1">
-      <c r="B31" s="14"/>
       <c r="D31" t="e">
         <f>VLOOKUP(C31,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
@@ -40856,333 +42402,367 @@
       </c>
       <c r="E32" s="218"/>
     </row>
-    <row r="33" spans="4:6" hidden="1" outlineLevel="1">
+    <row r="33" spans="4:5" hidden="1" outlineLevel="1">
       <c r="D33" t="e">
         <f>VLOOKUP(C33,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E33" s="218"/>
-      <c r="F33" s="232"/>
-    </row>
-    <row r="34" spans="4:6" hidden="1" outlineLevel="1">
+    </row>
+    <row r="34" spans="4:5" hidden="1" outlineLevel="1">
       <c r="D34" t="e">
         <f>VLOOKUP(C34,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E34" s="218"/>
     </row>
-    <row r="35" spans="4:6" hidden="1" outlineLevel="1">
+    <row r="35" spans="4:5" hidden="1" outlineLevel="1">
       <c r="D35" t="e">
         <f>VLOOKUP(C35,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E35" s="218"/>
     </row>
-    <row r="36" spans="4:6" hidden="1" outlineLevel="1">
+    <row r="36" spans="4:5" hidden="1" outlineLevel="1">
       <c r="D36" t="e">
         <f>VLOOKUP(C36,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E36" s="218"/>
     </row>
-    <row r="37" spans="4:6" hidden="1" outlineLevel="1">
+    <row r="37" spans="4:5" hidden="1" outlineLevel="1">
       <c r="D37" t="e">
         <f>VLOOKUP(C37,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E37" s="218"/>
     </row>
-    <row r="38" spans="4:6" hidden="1" outlineLevel="1">
+    <row r="38" spans="4:5" hidden="1" outlineLevel="1">
       <c r="D38" t="e">
         <f>VLOOKUP(C38,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E38" s="218"/>
     </row>
-    <row r="39" spans="4:6" hidden="1" outlineLevel="1">
+    <row r="39" spans="4:5" hidden="1" outlineLevel="1">
       <c r="D39" t="e">
         <f>VLOOKUP(C39,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E39" s="218"/>
     </row>
-    <row r="40" spans="4:6" hidden="1" outlineLevel="1">
+    <row r="40" spans="4:5" hidden="1" outlineLevel="1">
       <c r="D40" t="e">
         <f>VLOOKUP(C40,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E40" s="218"/>
     </row>
-    <row r="41" spans="4:6" hidden="1" outlineLevel="1">
+    <row r="41" spans="4:5" hidden="1" outlineLevel="1">
       <c r="D41" t="e">
         <f>VLOOKUP(C41,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E41" s="218"/>
     </row>
-    <row r="42" spans="4:6" hidden="1" outlineLevel="1">
+    <row r="42" spans="4:5" hidden="1" outlineLevel="1">
       <c r="D42" t="e">
         <f>VLOOKUP(C42,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E42" s="218"/>
     </row>
-    <row r="43" spans="4:6" hidden="1" outlineLevel="1">
+    <row r="43" spans="4:5" hidden="1" outlineLevel="1">
       <c r="D43" t="e">
         <f>VLOOKUP(C43,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E43" s="218"/>
     </row>
-    <row r="44" spans="4:6" hidden="1" outlineLevel="1">
+    <row r="44" spans="4:5" hidden="1" outlineLevel="1">
       <c r="D44" t="e">
         <f>VLOOKUP(C44,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E44" s="218"/>
     </row>
-    <row r="45" spans="4:6" hidden="1" outlineLevel="1">
+    <row r="45" spans="4:5" hidden="1" outlineLevel="1">
       <c r="D45" t="e">
         <f>VLOOKUP(C45,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E45" s="218"/>
     </row>
-    <row r="46" spans="4:6" hidden="1" outlineLevel="1">
+    <row r="46" spans="4:5" hidden="1" outlineLevel="1">
       <c r="D46" t="e">
         <f>VLOOKUP(C46,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E46" s="218"/>
     </row>
-    <row r="47" spans="4:6" hidden="1" outlineLevel="1">
+    <row r="47" spans="4:5" hidden="1" outlineLevel="1">
       <c r="D47" t="e">
         <f>VLOOKUP(C47,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E47" s="218"/>
     </row>
-    <row r="48" spans="4:6" hidden="1" outlineLevel="1">
+    <row r="48" spans="4:5" hidden="1" outlineLevel="1">
       <c r="D48" t="e">
         <f>VLOOKUP(C48,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E48" s="218"/>
     </row>
-    <row r="49" spans="4:7" hidden="1" outlineLevel="1">
+    <row r="49" spans="2:8" hidden="1" outlineLevel="1">
       <c r="D49" t="e">
         <f>VLOOKUP(C49,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E49" s="218"/>
     </row>
-    <row r="50" spans="4:7" hidden="1" outlineLevel="1">
+    <row r="50" spans="2:8" hidden="1" outlineLevel="1">
       <c r="D50" t="e">
         <f>VLOOKUP(C50,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E50" s="218"/>
-    </row>
-    <row r="51" spans="4:7" hidden="1" outlineLevel="1">
+      <c r="G50" s="69"/>
+    </row>
+    <row r="51" spans="2:8" hidden="1" outlineLevel="1">
       <c r="D51" t="e">
         <f>VLOOKUP(C51,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="E51" s="218"/>
-    </row>
-    <row r="52" spans="4:7" hidden="1" outlineLevel="1">
+    </row>
+    <row r="52" spans="2:8" hidden="1" outlineLevel="1">
       <c r="D52" t="e">
         <f>VLOOKUP(C52,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="E52" s="218"/>
-    </row>
-    <row r="53" spans="4:7" hidden="1" outlineLevel="1">
+    </row>
+    <row r="53" spans="2:8" hidden="1" outlineLevel="1">
       <c r="D53" t="e">
         <f>VLOOKUP(C53,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="E53" s="218"/>
-    </row>
-    <row r="54" spans="4:7" hidden="1" outlineLevel="1">
+    </row>
+    <row r="54" spans="2:8" hidden="1" outlineLevel="1">
       <c r="D54" t="e">
         <f>VLOOKUP(C54,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="E54" s="218"/>
-      <c r="G54" s="69"/>
-    </row>
-    <row r="55" spans="4:7" hidden="1" outlineLevel="1">
+    </row>
+    <row r="55" spans="2:8" hidden="1" outlineLevel="1">
       <c r="D55" t="e">
         <f>VLOOKUP(C55,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="56" spans="4:7" hidden="1" outlineLevel="1">
+    <row r="56" spans="2:8" hidden="1" outlineLevel="1">
       <c r="D56" t="e">
         <f>VLOOKUP(C56,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="57" spans="4:7" hidden="1" outlineLevel="1">
+    <row r="57" spans="2:8" hidden="1" outlineLevel="1">
       <c r="D57" t="e">
         <f>VLOOKUP(C57,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="58" spans="4:7" hidden="1" outlineLevel="1">
+    <row r="58" spans="2:8" hidden="1" outlineLevel="1">
       <c r="D58" t="e">
         <f>VLOOKUP(C58,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="59" spans="4:7" hidden="1" outlineLevel="1">
+    <row r="59" spans="2:8" hidden="1" outlineLevel="1">
       <c r="D59" t="e">
         <f>VLOOKUP(C59,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="60" spans="4:7" hidden="1" outlineLevel="1">
+    <row r="60" spans="2:8" hidden="1" outlineLevel="1">
       <c r="D60" t="e">
         <f>VLOOKUP(C60,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="61" spans="4:7" hidden="1" outlineLevel="1">
+    <row r="61" spans="2:8" hidden="1" outlineLevel="1">
       <c r="D61" t="e">
         <f>VLOOKUP(C61,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="62" spans="4:7" hidden="1" outlineLevel="1">
-      <c r="D62" t="e">
+    <row r="62" spans="2:8" outlineLevel="1">
+      <c r="B62" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C62" t="s">
+        <v>204</v>
+      </c>
+      <c r="D62" t="str">
         <f>VLOOKUP(C62,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="63" spans="4:7" hidden="1" outlineLevel="1">
-      <c r="D63" t="e">
-        <f>VLOOKUP(C63,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="64" spans="4:7" hidden="1" outlineLevel="1">
-      <c r="D64" t="e">
-        <f>VLOOKUP(C64,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="65" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="D65" t="e">
-        <f>VLOOKUP(C65,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="66" spans="2:17" outlineLevel="1">
-      <c r="B66" t="s">
-        <v>1398</v>
-      </c>
-      <c r="C66" t="s">
-        <v>204</v>
-      </c>
-      <c r="D66" t="str">
-        <f>VLOOKUP(C66,'Document Type'!$B$6:$C$34,2,FALSE)</f>
         <v>Company Setup</v>
       </c>
-      <c r="E66" s="140">
+      <c r="E62" s="140">
         <v>45924</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F62" t="s">
         <v>1396</v>
       </c>
-      <c r="G66" s="69" t="s">
-        <v>1407</v>
-      </c>
-      <c r="H66" t="s">
+      <c r="G62" s="69" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H62" t="s">
         <v>1236</v>
       </c>
     </row>
-    <row r="67" spans="2:17" outlineLevel="1">
-      <c r="B67" t="s">
-        <v>1421</v>
-      </c>
-      <c r="C67" t="s">
-        <v>204</v>
-      </c>
-      <c r="D67" t="str">
-        <f>VLOOKUP(C67,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>Company Setup</v>
-      </c>
-      <c r="E67" s="140">
-        <v>45899</v>
-      </c>
-      <c r="G67" s="69" t="s">
-        <v>1422</v>
-      </c>
-      <c r="H67" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="68" spans="2:17">
-      <c r="D68" t="e">
-        <f>VLOOKUP(C68,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="69" spans="2:17" ht="15.9">
-      <c r="B69" s="170" t="s">
+    <row r="64" spans="2:8" ht="16">
+      <c r="B64" s="170" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="70" spans="2:17" s="199" customFormat="1">
-      <c r="B70" s="350" t="s">
+    <row r="65" spans="2:17" s="199" customFormat="1">
+      <c r="B65" s="350" t="s">
         <v>265</v>
       </c>
-      <c r="C70" s="350" t="s">
+      <c r="C65" s="350" t="s">
         <v>290</v>
       </c>
-      <c r="D70" s="350" t="s">
+      <c r="D65" s="350" t="s">
         <v>291</v>
       </c>
-      <c r="E70" s="351" t="s">
+      <c r="E65" s="351" t="s">
         <v>292</v>
       </c>
-      <c r="F70" s="350" t="s">
+      <c r="F65" s="350" t="s">
         <v>293</v>
       </c>
-      <c r="G70" s="350" t="s">
+      <c r="G65" s="350" t="s">
         <v>294</v>
       </c>
-      <c r="H70" s="352" t="s">
+      <c r="H65" s="352" t="s">
         <v>295</v>
       </c>
-      <c r="I70" s="353" t="s">
+      <c r="I65" s="353" t="s">
         <v>296</v>
       </c>
-      <c r="J70" s="354" t="s">
+      <c r="J65" s="354" t="s">
         <v>297</v>
       </c>
-      <c r="K70" s="199" t="s">
+      <c r="K65" s="199" t="s">
         <v>298</v>
       </c>
-      <c r="L70" s="199" t="s">
+      <c r="L65" s="199" t="s">
         <v>299</v>
       </c>
-      <c r="M70" s="199" t="s">
+      <c r="M65" s="199" t="s">
         <v>300</v>
       </c>
-      <c r="N70" s="354" t="s">
+      <c r="N65" s="354" t="s">
         <v>301</v>
       </c>
-      <c r="O70" s="199" t="s">
+      <c r="O65" s="199" t="s">
         <v>302</v>
       </c>
-      <c r="P70" s="199" t="s">
+      <c r="P65" s="199" t="s">
         <v>303</v>
       </c>
-      <c r="Q70" s="199" t="s">
+      <c r="Q65" s="199" t="s">
         <v>304</v>
       </c>
+    </row>
+    <row r="66" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B66" s="140"/>
+      <c r="C66" s="93"/>
+      <c r="D66" s="93"/>
+      <c r="E66" s="93"/>
+      <c r="F66" s="93"/>
+      <c r="G66" s="93"/>
+      <c r="H66" s="93"/>
+      <c r="I66" s="93"/>
+      <c r="J66" s="209"/>
+      <c r="K66" s="93"/>
+      <c r="L66" s="93"/>
+      <c r="M66" s="93"/>
+      <c r="N66" s="209"/>
+      <c r="O66" s="93"/>
+      <c r="P66" s="93"/>
+      <c r="Q66" s="93"/>
+    </row>
+    <row r="67" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B67" s="140"/>
+      <c r="C67" s="93"/>
+      <c r="D67" s="93"/>
+      <c r="E67" s="93"/>
+      <c r="F67" s="93"/>
+      <c r="G67" s="93"/>
+      <c r="H67" s="93"/>
+      <c r="I67" s="93"/>
+      <c r="J67" s="209"/>
+      <c r="K67" s="93"/>
+      <c r="L67" s="93"/>
+      <c r="M67" s="93"/>
+      <c r="N67" s="209"/>
+      <c r="O67" s="93"/>
+      <c r="P67" s="93"/>
+      <c r="Q67" s="93"/>
+    </row>
+    <row r="68" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B68" s="140"/>
+      <c r="C68" s="93"/>
+      <c r="D68" s="93"/>
+      <c r="E68" s="93"/>
+      <c r="F68" s="93"/>
+      <c r="G68" s="93"/>
+      <c r="H68" s="93"/>
+      <c r="I68" s="93"/>
+      <c r="J68" s="209"/>
+      <c r="K68" s="93"/>
+      <c r="L68" s="93"/>
+      <c r="M68" s="93"/>
+      <c r="N68" s="209"/>
+      <c r="O68" s="93"/>
+      <c r="P68" s="93"/>
+      <c r="Q68" s="93"/>
+    </row>
+    <row r="69" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B69" s="140"/>
+      <c r="C69" s="93"/>
+      <c r="D69" s="93"/>
+      <c r="E69" s="93"/>
+      <c r="F69" s="93"/>
+      <c r="G69" s="93"/>
+      <c r="H69" s="93"/>
+      <c r="I69" s="93"/>
+      <c r="J69" s="209"/>
+      <c r="K69" s="93"/>
+      <c r="L69" s="93"/>
+      <c r="M69" s="93"/>
+      <c r="N69" s="209"/>
+      <c r="O69" s="93"/>
+      <c r="P69" s="93"/>
+      <c r="Q69" s="93"/>
+    </row>
+    <row r="70" spans="2:17" hidden="1" outlineLevel="1">
+      <c r="B70" s="140"/>
+      <c r="C70" s="93"/>
+      <c r="D70" s="93"/>
+      <c r="E70" s="93"/>
+      <c r="F70" s="93"/>
+      <c r="G70" s="93"/>
+      <c r="H70" s="93"/>
+      <c r="I70" s="93"/>
+      <c r="J70" s="209"/>
+      <c r="K70" s="93"/>
+      <c r="L70" s="93"/>
+      <c r="M70" s="93"/>
+      <c r="N70" s="209"/>
+      <c r="O70" s="93"/>
+      <c r="P70" s="93"/>
+      <c r="Q70" s="93"/>
     </row>
     <row r="71" spans="2:17" hidden="1" outlineLevel="1">
       <c r="B71" s="140"/>
@@ -41419,7 +42999,7 @@
       <c r="Q83" s="93"/>
     </row>
     <row r="84" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B84" s="140"/>
+      <c r="B84" s="93"/>
       <c r="C84" s="93"/>
       <c r="D84" s="93"/>
       <c r="E84" s="93"/>
@@ -41437,7 +43017,7 @@
       <c r="Q84" s="93"/>
     </row>
     <row r="85" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B85" s="140"/>
+      <c r="B85" s="93"/>
       <c r="C85" s="93"/>
       <c r="D85" s="93"/>
       <c r="E85" s="93"/>
@@ -41455,7 +43035,7 @@
       <c r="Q85" s="93"/>
     </row>
     <row r="86" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B86" s="140"/>
+      <c r="B86" s="93"/>
       <c r="C86" s="93"/>
       <c r="D86" s="93"/>
       <c r="E86" s="93"/>
@@ -41473,7 +43053,7 @@
       <c r="Q86" s="93"/>
     </row>
     <row r="87" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B87" s="140"/>
+      <c r="B87" s="93"/>
       <c r="C87" s="93"/>
       <c r="D87" s="93"/>
       <c r="E87" s="93"/>
@@ -41491,7 +43071,7 @@
       <c r="Q87" s="93"/>
     </row>
     <row r="88" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B88" s="140"/>
+      <c r="B88" s="93"/>
       <c r="C88" s="93"/>
       <c r="D88" s="93"/>
       <c r="E88" s="93"/>
@@ -41562,1576 +43142,6 @@
       <c r="P91" s="93"/>
       <c r="Q91" s="93"/>
     </row>
-    <row r="92" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B92" s="93"/>
-      <c r="C92" s="93"/>
-      <c r="D92" s="93"/>
-      <c r="E92" s="93"/>
-      <c r="F92" s="93"/>
-      <c r="G92" s="93"/>
-      <c r="H92" s="93"/>
-      <c r="I92" s="93"/>
-      <c r="J92" s="209"/>
-      <c r="K92" s="93"/>
-      <c r="L92" s="93"/>
-      <c r="M92" s="93"/>
-      <c r="N92" s="209"/>
-      <c r="O92" s="93"/>
-      <c r="P92" s="93"/>
-      <c r="Q92" s="93"/>
-    </row>
-    <row r="93" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B93" s="93"/>
-      <c r="C93" s="93"/>
-      <c r="D93" s="93"/>
-      <c r="E93" s="93"/>
-      <c r="F93" s="93"/>
-      <c r="G93" s="93"/>
-      <c r="H93" s="93"/>
-      <c r="I93" s="93"/>
-      <c r="J93" s="209"/>
-      <c r="K93" s="93"/>
-      <c r="L93" s="93"/>
-      <c r="M93" s="93"/>
-      <c r="N93" s="209"/>
-      <c r="O93" s="93"/>
-      <c r="P93" s="93"/>
-      <c r="Q93" s="93"/>
-    </row>
-    <row r="94" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B94" s="93"/>
-      <c r="C94" s="93"/>
-      <c r="D94" s="93"/>
-      <c r="E94" s="93"/>
-      <c r="F94" s="93"/>
-      <c r="G94" s="93"/>
-      <c r="H94" s="93"/>
-      <c r="I94" s="93"/>
-      <c r="J94" s="209"/>
-      <c r="K94" s="93"/>
-      <c r="L94" s="93"/>
-      <c r="M94" s="93"/>
-      <c r="N94" s="209"/>
-      <c r="O94" s="93"/>
-      <c r="P94" s="93"/>
-      <c r="Q94" s="93"/>
-    </row>
-    <row r="95" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B95" s="93"/>
-      <c r="C95" s="93"/>
-      <c r="D95" s="93"/>
-      <c r="E95" s="93"/>
-      <c r="F95" s="93"/>
-      <c r="G95" s="93"/>
-      <c r="H95" s="93"/>
-      <c r="I95" s="93"/>
-      <c r="J95" s="209"/>
-      <c r="K95" s="93"/>
-      <c r="L95" s="93"/>
-      <c r="M95" s="93"/>
-      <c r="N95" s="209"/>
-      <c r="O95" s="93"/>
-      <c r="P95" s="93"/>
-      <c r="Q95" s="93"/>
-    </row>
-    <row r="96" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B96" s="93"/>
-      <c r="C96" s="93"/>
-      <c r="D96" s="93"/>
-      <c r="E96" s="93"/>
-      <c r="F96" s="93"/>
-      <c r="G96" s="93"/>
-      <c r="H96" s="93"/>
-      <c r="I96" s="93"/>
-      <c r="J96" s="209"/>
-      <c r="K96" s="93"/>
-      <c r="L96" s="93"/>
-      <c r="M96" s="93"/>
-      <c r="N96" s="209"/>
-      <c r="O96" s="93"/>
-      <c r="P96" s="93"/>
-      <c r="Q96" s="93"/>
-    </row>
-    <row r="97" spans="2:17" outlineLevel="1">
-      <c r="B97" s="140">
-        <v>45924</v>
-      </c>
-      <c r="C97" s="93" t="s">
-        <v>437</v>
-      </c>
-      <c r="D97" s="93" t="s">
-        <v>1399</v>
-      </c>
-      <c r="E97" s="93">
-        <v>1</v>
-      </c>
-      <c r="F97" s="93">
-        <v>1</v>
-      </c>
-      <c r="G97" s="93">
-        <v>1</v>
-      </c>
-      <c r="H97" s="93">
-        <v>100</v>
-      </c>
-      <c r="I97" s="93"/>
-      <c r="J97" s="209">
-        <v>0.01</v>
-      </c>
-      <c r="K97" s="93">
-        <v>0</v>
-      </c>
-      <c r="L97" s="93" t="s">
-        <v>403</v>
-      </c>
-      <c r="M97" s="93">
-        <v>100</v>
-      </c>
-      <c r="N97" s="209">
-        <v>1</v>
-      </c>
-      <c r="O97" s="93" t="s">
-        <v>403</v>
-      </c>
-      <c r="P97" s="93" t="s">
-        <v>684</v>
-      </c>
-      <c r="Q97" s="93"/>
-    </row>
-    <row r="99" spans="2:17" ht="15.9">
-      <c r="B99" s="170" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="100" spans="2:17">
-      <c r="B100" t="s">
-        <v>224</v>
-      </c>
-      <c r="C100" t="s">
-        <v>306</v>
-      </c>
-      <c r="D100" t="s">
-        <v>307</v>
-      </c>
-      <c r="E100" t="s">
-        <v>265</v>
-      </c>
-      <c r="F100" t="s">
-        <v>308</v>
-      </c>
-      <c r="G100" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="101" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="D101" s="112"/>
-      <c r="E101" s="218"/>
-    </row>
-    <row r="102" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="D102" s="112"/>
-      <c r="E102" s="218"/>
-    </row>
-    <row r="103" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="D103" s="112"/>
-      <c r="E103" s="218"/>
-    </row>
-    <row r="104" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="D104" s="112"/>
-      <c r="E104" s="218"/>
-    </row>
-    <row r="105" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="D105" s="112"/>
-    </row>
-    <row r="106" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="D106" s="112"/>
-    </row>
-    <row r="107" spans="2:17" collapsed="1"/>
-    <row r="108" spans="2:17" ht="15.9">
-      <c r="B108" s="170" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="109" spans="2:17">
-      <c r="B109" t="s">
-        <v>310</v>
-      </c>
-      <c r="C109" t="s">
-        <v>311</v>
-      </c>
-      <c r="D109" t="s">
-        <v>312</v>
-      </c>
-      <c r="E109" t="s">
-        <v>313</v>
-      </c>
-      <c r="F109" t="s">
-        <v>314</v>
-      </c>
-      <c r="G109" t="s">
-        <v>705</v>
-      </c>
-      <c r="H109" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="110" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="H110" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="H111" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="H112" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="8:8" hidden="1" outlineLevel="1">
-      <c r="H113" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="8:8" hidden="1" outlineLevel="1">
-      <c r="H114" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="8:8" hidden="1" outlineLevel="1">
-      <c r="H115" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="8:8" hidden="1" outlineLevel="1">
-      <c r="H116" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="8:8" hidden="1" outlineLevel="1">
-      <c r="H117" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="8:8" hidden="1" outlineLevel="1">
-      <c r="H118" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="8:8" hidden="1" outlineLevel="1">
-      <c r="H119" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="8:8" hidden="1" outlineLevel="1">
-      <c r="H120" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="8:8" hidden="1" outlineLevel="1">
-      <c r="H121" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="8:8" hidden="1" outlineLevel="1">
-      <c r="H122" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="8:8" hidden="1" outlineLevel="1">
-      <c r="H123" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="8:8" hidden="1" outlineLevel="1">
-      <c r="H124" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="8:8" hidden="1" outlineLevel="1">
-      <c r="H125" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="8:8" hidden="1" outlineLevel="1">
-      <c r="H126" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="8:8" hidden="1" outlineLevel="1">
-      <c r="H127" s="112">
-        <f>Table79136165[[#This Row],[Sale Price]]-Table79136165[[#This Row],[Purchase Price]]+Table79136165[[#This Row],[Depreciation]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="8:8" collapsed="1"/>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C6:D6"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="C28" r:id="rId1" xr:uid="{21236431-21D4-4AD6-90BA-074538FA8A2F}"/>
-    <hyperlink ref="G66" r:id="rId2" display="../../../../../:b:/g/personal/robert_tekna_com_au/EcSxjR_BpMxLuckkSUQsPOMB3TYfXdzMGevsOWH_kuuT-w?e=D4nAbJ" xr:uid="{9DC9F06E-48B4-4A23-93FE-BDDE4F5FD03D}"/>
-    <hyperlink ref="G67" r:id="rId3" xr:uid="{22AE8784-93DF-4E6F-B478-E21F28FD9236}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
-  <tableParts count="4">
-    <tablePart r:id="rId5"/>
-    <tablePart r:id="rId6"/>
-    <tablePart r:id="rId7"/>
-    <tablePart r:id="rId8"/>
-  </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{571D6050-55EE-4641-B36C-3AC667D32D48}">
-          <x14:formula1>
-            <xm:f>'Document Type'!$B$38:$B$39</xm:f>
-          </x14:formula1>
-          <xm:sqref>G6 F33 G13 C13 F15:F19</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BAB77F41-2822-4361-9344-38ED25D99101}">
-          <x14:formula1>
-            <xm:f>'Document Type'!$B$45:$B$47</xm:f>
-          </x14:formula1>
-          <xm:sqref>C8 G8</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C6F8AFED-E6DC-4108-9F3F-2E82086D811A}">
-          <x14:formula1>
-            <xm:f>'Document Type'!$B$49:$B$51</xm:f>
-          </x14:formula1>
-          <xm:sqref>C10:C11</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C158B414-685E-4574-B4D0-B2A61B26759A}">
-          <x14:formula1>
-            <xm:f>'Document Type'!$B$6:$B$34</xm:f>
-          </x14:formula1>
-          <xm:sqref>C31:C68</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13E41263-52DA-47DA-A9DF-C248772F9CCE}">
-  <dimension ref="B1:Q123"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
-  <cols>
-    <col min="1" max="1" width="3.15234375" customWidth="1"/>
-    <col min="2" max="2" width="30.15234375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.3046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.69140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.3046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="43.15234375" customWidth="1"/>
-    <col min="8" max="8" width="25.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25" customWidth="1"/>
-    <col min="12" max="12" width="16.69140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.3046875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="31.69140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.15234375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="40" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.3046875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:12">
-      <c r="B1" s="69" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="2" spans="2:12" ht="15" thickBot="1">
-      <c r="J2" t="s">
-        <v>196</v>
-      </c>
-      <c r="K2" t="s">
-        <v>197</v>
-      </c>
-      <c r="L2">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" ht="26.6" thickBot="1">
-      <c r="B3" s="373" t="s">
-        <v>1391</v>
-      </c>
-      <c r="C3" s="374"/>
-      <c r="D3" s="374"/>
-      <c r="E3" s="374"/>
-      <c r="F3" s="374"/>
-      <c r="G3" s="374"/>
-      <c r="H3" s="375"/>
-      <c r="J3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="17.8" customHeight="1">
-      <c r="B4" s="245" t="s">
-        <v>1392</v>
-      </c>
-      <c r="C4" s="93"/>
-      <c r="D4" s="273" t="s">
-        <v>202</v>
-      </c>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="273" t="s">
-        <v>203</v>
-      </c>
-      <c r="H4" s="93"/>
-      <c r="J4" t="s">
-        <v>204</v>
-      </c>
-      <c r="K4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12">
-      <c r="B5" s="250" t="s">
-        <v>206</v>
-      </c>
-      <c r="C5" s="236">
-        <v>45924</v>
-      </c>
-      <c r="D5" s="236"/>
-      <c r="E5" s="237"/>
-      <c r="F5" s="274" t="s">
-        <v>207</v>
-      </c>
-      <c r="G5" s="285">
-        <v>100</v>
-      </c>
-      <c r="H5" s="289"/>
-      <c r="J5" t="s">
-        <v>208</v>
-      </c>
-      <c r="K5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12">
-      <c r="B6" s="251" t="s">
-        <v>210</v>
-      </c>
-      <c r="C6" s="376" t="s">
-        <v>1393</v>
-      </c>
-      <c r="D6" s="376"/>
-      <c r="E6" s="232"/>
-      <c r="F6" s="275" t="s">
-        <v>211</v>
-      </c>
-      <c r="G6" s="232"/>
-      <c r="H6" s="276"/>
-      <c r="J6" t="s">
-        <v>213</v>
-      </c>
-      <c r="K6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12">
-      <c r="B7" s="250" t="s">
-        <v>215</v>
-      </c>
-      <c r="C7" s="237"/>
-      <c r="D7" s="237"/>
-      <c r="E7" s="236"/>
-      <c r="F7" s="237"/>
-      <c r="G7" s="237"/>
-      <c r="H7" s="241"/>
-      <c r="J7" t="s">
-        <v>216</v>
-      </c>
-      <c r="K7" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12">
-      <c r="B8" s="249" t="s">
-        <v>218</v>
-      </c>
-      <c r="C8" s="232" t="s">
-        <v>221</v>
-      </c>
-      <c r="D8" s="232"/>
-      <c r="E8" s="252"/>
-      <c r="F8" s="275" t="s">
-        <v>220</v>
-      </c>
-      <c r="G8" s="232"/>
-      <c r="H8" s="276"/>
-      <c r="J8" t="s">
-        <v>222</v>
-      </c>
-      <c r="K8" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12">
-      <c r="B9" s="239"/>
-      <c r="C9" s="237"/>
-      <c r="D9" s="237" t="s">
-        <v>224</v>
-      </c>
-      <c r="E9" s="236"/>
-      <c r="F9" s="237"/>
-      <c r="G9" s="237"/>
-      <c r="H9" s="241"/>
-      <c r="J9" t="s">
-        <v>225</v>
-      </c>
-      <c r="K9" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" s="249" t="s">
-        <v>227</v>
-      </c>
-      <c r="C10" s="277" t="s">
-        <v>228</v>
-      </c>
-      <c r="D10" s="252"/>
-      <c r="E10" s="232"/>
-      <c r="F10" s="232"/>
-      <c r="G10" s="232"/>
-      <c r="H10" s="276"/>
-      <c r="J10" t="s">
-        <v>229</v>
-      </c>
-      <c r="K10" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12">
-      <c r="B11" s="250" t="s">
-        <v>231</v>
-      </c>
-      <c r="C11" s="288" t="s">
-        <v>228</v>
-      </c>
-      <c r="D11" s="237"/>
-      <c r="E11" s="237"/>
-      <c r="F11" s="237"/>
-      <c r="G11" s="285"/>
-      <c r="H11" s="289"/>
-      <c r="J11" t="s">
-        <v>232</v>
-      </c>
-      <c r="K11" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12">
-      <c r="B12" s="240"/>
-      <c r="C12" s="232"/>
-      <c r="D12" s="232"/>
-      <c r="E12" s="252"/>
-      <c r="F12" s="232"/>
-      <c r="G12" s="232"/>
-      <c r="H12" s="276"/>
-      <c r="J12" t="s">
-        <v>234</v>
-      </c>
-      <c r="K12" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12">
-      <c r="B13" s="250" t="s">
-        <v>236</v>
-      </c>
-      <c r="C13" s="237" t="s">
-        <v>212</v>
-      </c>
-      <c r="D13" s="237"/>
-      <c r="E13" s="237"/>
-      <c r="F13" s="274" t="s">
-        <v>238</v>
-      </c>
-      <c r="G13" s="237" t="s">
-        <v>212</v>
-      </c>
-      <c r="H13" s="237"/>
-      <c r="J13" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12">
-      <c r="B14" s="242"/>
-      <c r="C14" s="233"/>
-      <c r="D14" s="233"/>
-      <c r="E14" s="232" t="s">
-        <v>240</v>
-      </c>
-      <c r="F14" s="232" t="s">
-        <v>241</v>
-      </c>
-      <c r="G14" s="232"/>
-      <c r="H14" s="232"/>
-      <c r="J14" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="B15" s="250" t="s">
-        <v>243</v>
-      </c>
-      <c r="C15" s="377" t="s">
-        <v>602</v>
-      </c>
-      <c r="D15" s="377"/>
-      <c r="E15" s="237">
-        <v>100</v>
-      </c>
-      <c r="F15" s="237" t="s">
-        <v>237</v>
-      </c>
-      <c r="G15" s="237"/>
-      <c r="H15" s="237"/>
-      <c r="J15" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12">
-      <c r="B16" s="242"/>
-      <c r="C16" s="233"/>
-      <c r="D16" s="233"/>
-      <c r="E16" s="232"/>
-      <c r="F16" s="232"/>
-      <c r="G16" s="232"/>
-      <c r="H16" s="232"/>
-      <c r="J16" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10">
-      <c r="B17" s="250" t="s">
-        <v>247</v>
-      </c>
-      <c r="C17" s="237" t="s">
-        <v>248</v>
-      </c>
-      <c r="D17" s="237" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" s="236" t="s">
-        <v>83</v>
-      </c>
-      <c r="F17" s="237" t="s">
-        <v>249</v>
-      </c>
-      <c r="G17" s="285"/>
-      <c r="H17" s="285"/>
-      <c r="J17" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10">
-      <c r="B18" s="240"/>
-      <c r="C18" s="232"/>
-      <c r="D18" s="232"/>
-      <c r="E18" s="252"/>
-      <c r="F18" s="232"/>
-      <c r="G18" s="232"/>
-      <c r="H18" s="232"/>
-      <c r="J18" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10">
-      <c r="B19" s="239"/>
-      <c r="C19" s="237"/>
-      <c r="D19" s="237"/>
-      <c r="E19" s="236"/>
-      <c r="F19" s="237"/>
-      <c r="G19" s="237"/>
-      <c r="H19" s="237"/>
-      <c r="J19" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10">
-      <c r="B20" s="240"/>
-      <c r="C20" s="232"/>
-      <c r="D20" s="232"/>
-      <c r="E20" s="252"/>
-      <c r="F20" s="232"/>
-      <c r="G20" s="232"/>
-      <c r="H20" s="232"/>
-      <c r="J20" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10">
-      <c r="B21" s="239"/>
-      <c r="C21" s="237"/>
-      <c r="D21" s="237"/>
-      <c r="E21" s="236"/>
-      <c r="F21" s="237"/>
-      <c r="G21" s="237"/>
-      <c r="H21" s="237"/>
-      <c r="J21" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10">
-      <c r="B22" s="240"/>
-      <c r="C22" s="232"/>
-      <c r="D22" s="232"/>
-      <c r="E22" s="252"/>
-      <c r="F22" s="232"/>
-      <c r="G22" s="232"/>
-      <c r="H22" s="232"/>
-    </row>
-    <row r="24" spans="2:10">
-      <c r="B24" t="s">
-        <v>259</v>
-      </c>
-      <c r="C24" s="69" t="s">
-        <v>1394</v>
-      </c>
-      <c r="D24" t="s">
-        <v>260</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1395</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" ht="15.9">
-      <c r="B26" s="170" t="s">
-        <v>262</v>
-      </c>
-      <c r="C26" s="170" t="s">
-        <v>263</v>
-      </c>
-      <c r="D26" s="170" t="s">
-        <v>264</v>
-      </c>
-      <c r="E26" s="170" t="s">
-        <v>265</v>
-      </c>
-      <c r="F26" s="170" t="s">
-        <v>266</v>
-      </c>
-      <c r="G26" s="170" t="s">
-        <v>267</v>
-      </c>
-      <c r="H26" s="170" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" hidden="1" outlineLevel="1">
-      <c r="B27" s="14"/>
-      <c r="D27" t="e">
-        <f>VLOOKUP(C27,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E27" s="218"/>
-    </row>
-    <row r="28" spans="2:10" hidden="1" outlineLevel="1">
-      <c r="D28" t="e">
-        <f>VLOOKUP(C28,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E28" s="218"/>
-    </row>
-    <row r="29" spans="2:10" hidden="1" outlineLevel="1">
-      <c r="D29" t="e">
-        <f>VLOOKUP(C29,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E29" s="218"/>
-      <c r="F29" s="232"/>
-    </row>
-    <row r="30" spans="2:10" hidden="1" outlineLevel="1">
-      <c r="D30" t="e">
-        <f>VLOOKUP(C30,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E30" s="218"/>
-    </row>
-    <row r="31" spans="2:10" hidden="1" outlineLevel="1">
-      <c r="D31" t="e">
-        <f>VLOOKUP(C31,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E31" s="218"/>
-    </row>
-    <row r="32" spans="2:10" hidden="1" outlineLevel="1">
-      <c r="D32" t="e">
-        <f>VLOOKUP(C32,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E32" s="218"/>
-    </row>
-    <row r="33" spans="4:5" hidden="1" outlineLevel="1">
-      <c r="D33" t="e">
-        <f>VLOOKUP(C33,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E33" s="218"/>
-    </row>
-    <row r="34" spans="4:5" hidden="1" outlineLevel="1">
-      <c r="D34" t="e">
-        <f>VLOOKUP(C34,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E34" s="218"/>
-    </row>
-    <row r="35" spans="4:5" hidden="1" outlineLevel="1">
-      <c r="D35" t="e">
-        <f>VLOOKUP(C35,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E35" s="218"/>
-    </row>
-    <row r="36" spans="4:5" hidden="1" outlineLevel="1">
-      <c r="D36" t="e">
-        <f>VLOOKUP(C36,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E36" s="218"/>
-    </row>
-    <row r="37" spans="4:5" hidden="1" outlineLevel="1">
-      <c r="D37" t="e">
-        <f>VLOOKUP(C37,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E37" s="218"/>
-    </row>
-    <row r="38" spans="4:5" hidden="1" outlineLevel="1">
-      <c r="D38" t="e">
-        <f>VLOOKUP(C38,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E38" s="218"/>
-    </row>
-    <row r="39" spans="4:5" hidden="1" outlineLevel="1">
-      <c r="D39" t="e">
-        <f>VLOOKUP(C39,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E39" s="218"/>
-    </row>
-    <row r="40" spans="4:5" hidden="1" outlineLevel="1">
-      <c r="D40" t="e">
-        <f>VLOOKUP(C40,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E40" s="218"/>
-    </row>
-    <row r="41" spans="4:5" hidden="1" outlineLevel="1">
-      <c r="D41" t="e">
-        <f>VLOOKUP(C41,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E41" s="218"/>
-    </row>
-    <row r="42" spans="4:5" hidden="1" outlineLevel="1">
-      <c r="D42" t="e">
-        <f>VLOOKUP(C42,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E42" s="218"/>
-    </row>
-    <row r="43" spans="4:5" hidden="1" outlineLevel="1">
-      <c r="D43" t="e">
-        <f>VLOOKUP(C43,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E43" s="218"/>
-    </row>
-    <row r="44" spans="4:5" hidden="1" outlineLevel="1">
-      <c r="D44" t="e">
-        <f>VLOOKUP(C44,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E44" s="218"/>
-    </row>
-    <row r="45" spans="4:5" hidden="1" outlineLevel="1">
-      <c r="D45" t="e">
-        <f>VLOOKUP(C45,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E45" s="218"/>
-    </row>
-    <row r="46" spans="4:5" hidden="1" outlineLevel="1">
-      <c r="D46" t="e">
-        <f>VLOOKUP(C46,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E46" s="218"/>
-    </row>
-    <row r="47" spans="4:5" hidden="1" outlineLevel="1">
-      <c r="D47" t="e">
-        <f>VLOOKUP(C47,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E47" s="218"/>
-    </row>
-    <row r="48" spans="4:5" hidden="1" outlineLevel="1">
-      <c r="D48" t="e">
-        <f>VLOOKUP(C48,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E48" s="218"/>
-    </row>
-    <row r="49" spans="2:8" hidden="1" outlineLevel="1">
-      <c r="D49" t="e">
-        <f>VLOOKUP(C49,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E49" s="218"/>
-    </row>
-    <row r="50" spans="2:8" hidden="1" outlineLevel="1">
-      <c r="D50" t="e">
-        <f>VLOOKUP(C50,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E50" s="218"/>
-      <c r="G50" s="69"/>
-    </row>
-    <row r="51" spans="2:8" hidden="1" outlineLevel="1">
-      <c r="D51" t="e">
-        <f>VLOOKUP(C51,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8" hidden="1" outlineLevel="1">
-      <c r="D52" t="e">
-        <f>VLOOKUP(C52,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" hidden="1" outlineLevel="1">
-      <c r="D53" t="e">
-        <f>VLOOKUP(C53,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" hidden="1" outlineLevel="1">
-      <c r="D54" t="e">
-        <f>VLOOKUP(C54,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" hidden="1" outlineLevel="1">
-      <c r="D55" t="e">
-        <f>VLOOKUP(C55,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8" hidden="1" outlineLevel="1">
-      <c r="D56" t="e">
-        <f>VLOOKUP(C56,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8" hidden="1" outlineLevel="1">
-      <c r="D57" t="e">
-        <f>VLOOKUP(C57,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8" hidden="1" outlineLevel="1">
-      <c r="D58" t="e">
-        <f>VLOOKUP(C58,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" hidden="1" outlineLevel="1">
-      <c r="D59" t="e">
-        <f>VLOOKUP(C59,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8" hidden="1" outlineLevel="1">
-      <c r="D60" t="e">
-        <f>VLOOKUP(C60,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8" hidden="1" outlineLevel="1">
-      <c r="D61" t="e">
-        <f>VLOOKUP(C61,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8" outlineLevel="1">
-      <c r="B62" t="s">
-        <v>1398</v>
-      </c>
-      <c r="C62" t="s">
-        <v>204</v>
-      </c>
-      <c r="D62" t="str">
-        <f>VLOOKUP(C62,'Document Type'!$B$6:$C$34,2,FALSE)</f>
-        <v>Company Setup</v>
-      </c>
-      <c r="E62" s="140">
-        <v>45924</v>
-      </c>
-      <c r="F62" t="s">
-        <v>1396</v>
-      </c>
-      <c r="G62" s="69" t="s">
-        <v>1397</v>
-      </c>
-      <c r="H62" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" ht="15.9">
-      <c r="B64" s="170" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="65" spans="2:17" s="199" customFormat="1">
-      <c r="B65" s="350" t="s">
-        <v>265</v>
-      </c>
-      <c r="C65" s="350" t="s">
-        <v>290</v>
-      </c>
-      <c r="D65" s="350" t="s">
-        <v>291</v>
-      </c>
-      <c r="E65" s="351" t="s">
-        <v>292</v>
-      </c>
-      <c r="F65" s="350" t="s">
-        <v>293</v>
-      </c>
-      <c r="G65" s="350" t="s">
-        <v>294</v>
-      </c>
-      <c r="H65" s="352" t="s">
-        <v>295</v>
-      </c>
-      <c r="I65" s="353" t="s">
-        <v>296</v>
-      </c>
-      <c r="J65" s="354" t="s">
-        <v>297</v>
-      </c>
-      <c r="K65" s="199" t="s">
-        <v>298</v>
-      </c>
-      <c r="L65" s="199" t="s">
-        <v>299</v>
-      </c>
-      <c r="M65" s="199" t="s">
-        <v>300</v>
-      </c>
-      <c r="N65" s="354" t="s">
-        <v>301</v>
-      </c>
-      <c r="O65" s="199" t="s">
-        <v>302</v>
-      </c>
-      <c r="P65" s="199" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q65" s="199" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="66" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B66" s="140"/>
-      <c r="C66" s="93"/>
-      <c r="D66" s="93"/>
-      <c r="E66" s="93"/>
-      <c r="F66" s="93"/>
-      <c r="G66" s="93"/>
-      <c r="H66" s="93"/>
-      <c r="I66" s="93"/>
-      <c r="J66" s="209"/>
-      <c r="K66" s="93"/>
-      <c r="L66" s="93"/>
-      <c r="M66" s="93"/>
-      <c r="N66" s="209"/>
-      <c r="O66" s="93"/>
-      <c r="P66" s="93"/>
-      <c r="Q66" s="93"/>
-    </row>
-    <row r="67" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B67" s="140"/>
-      <c r="C67" s="93"/>
-      <c r="D67" s="93"/>
-      <c r="E67" s="93"/>
-      <c r="F67" s="93"/>
-      <c r="G67" s="93"/>
-      <c r="H67" s="93"/>
-      <c r="I67" s="93"/>
-      <c r="J67" s="209"/>
-      <c r="K67" s="93"/>
-      <c r="L67" s="93"/>
-      <c r="M67" s="93"/>
-      <c r="N67" s="209"/>
-      <c r="O67" s="93"/>
-      <c r="P67" s="93"/>
-      <c r="Q67" s="93"/>
-    </row>
-    <row r="68" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B68" s="140"/>
-      <c r="C68" s="93"/>
-      <c r="D68" s="93"/>
-      <c r="E68" s="93"/>
-      <c r="F68" s="93"/>
-      <c r="G68" s="93"/>
-      <c r="H68" s="93"/>
-      <c r="I68" s="93"/>
-      <c r="J68" s="209"/>
-      <c r="K68" s="93"/>
-      <c r="L68" s="93"/>
-      <c r="M68" s="93"/>
-      <c r="N68" s="209"/>
-      <c r="O68" s="93"/>
-      <c r="P68" s="93"/>
-      <c r="Q68" s="93"/>
-    </row>
-    <row r="69" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B69" s="140"/>
-      <c r="C69" s="93"/>
-      <c r="D69" s="93"/>
-      <c r="E69" s="93"/>
-      <c r="F69" s="93"/>
-      <c r="G69" s="93"/>
-      <c r="H69" s="93"/>
-      <c r="I69" s="93"/>
-      <c r="J69" s="209"/>
-      <c r="K69" s="93"/>
-      <c r="L69" s="93"/>
-      <c r="M69" s="93"/>
-      <c r="N69" s="209"/>
-      <c r="O69" s="93"/>
-      <c r="P69" s="93"/>
-      <c r="Q69" s="93"/>
-    </row>
-    <row r="70" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B70" s="140"/>
-      <c r="C70" s="93"/>
-      <c r="D70" s="93"/>
-      <c r="E70" s="93"/>
-      <c r="F70" s="93"/>
-      <c r="G70" s="93"/>
-      <c r="H70" s="93"/>
-      <c r="I70" s="93"/>
-      <c r="J70" s="209"/>
-      <c r="K70" s="93"/>
-      <c r="L70" s="93"/>
-      <c r="M70" s="93"/>
-      <c r="N70" s="209"/>
-      <c r="O70" s="93"/>
-      <c r="P70" s="93"/>
-      <c r="Q70" s="93"/>
-    </row>
-    <row r="71" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B71" s="140"/>
-      <c r="C71" s="93"/>
-      <c r="D71" s="93"/>
-      <c r="E71" s="93"/>
-      <c r="F71" s="93"/>
-      <c r="G71" s="93"/>
-      <c r="H71" s="93"/>
-      <c r="I71" s="93"/>
-      <c r="J71" s="209"/>
-      <c r="K71" s="93"/>
-      <c r="L71" s="93"/>
-      <c r="M71" s="93"/>
-      <c r="N71" s="209"/>
-      <c r="O71" s="93"/>
-      <c r="P71" s="93"/>
-      <c r="Q71" s="93"/>
-    </row>
-    <row r="72" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B72" s="140"/>
-      <c r="C72" s="93"/>
-      <c r="D72" s="93"/>
-      <c r="E72" s="93"/>
-      <c r="F72" s="93"/>
-      <c r="G72" s="93"/>
-      <c r="H72" s="93"/>
-      <c r="I72" s="93"/>
-      <c r="J72" s="209"/>
-      <c r="K72" s="93"/>
-      <c r="L72" s="93"/>
-      <c r="M72" s="93"/>
-      <c r="N72" s="209"/>
-      <c r="O72" s="93"/>
-      <c r="P72" s="93"/>
-      <c r="Q72" s="93"/>
-    </row>
-    <row r="73" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B73" s="140"/>
-      <c r="C73" s="93"/>
-      <c r="D73" s="93"/>
-      <c r="E73" s="93"/>
-      <c r="F73" s="93"/>
-      <c r="G73" s="93"/>
-      <c r="H73" s="93"/>
-      <c r="I73" s="93"/>
-      <c r="J73" s="209"/>
-      <c r="K73" s="93"/>
-      <c r="L73" s="93"/>
-      <c r="M73" s="93"/>
-      <c r="N73" s="209"/>
-      <c r="O73" s="93"/>
-      <c r="P73" s="93"/>
-      <c r="Q73" s="93"/>
-    </row>
-    <row r="74" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B74" s="140"/>
-      <c r="C74" s="93"/>
-      <c r="D74" s="93"/>
-      <c r="E74" s="93"/>
-      <c r="F74" s="93"/>
-      <c r="G74" s="93"/>
-      <c r="H74" s="93"/>
-      <c r="I74" s="93"/>
-      <c r="J74" s="209"/>
-      <c r="K74" s="93"/>
-      <c r="L74" s="93"/>
-      <c r="M74" s="93"/>
-      <c r="N74" s="209"/>
-      <c r="O74" s="93"/>
-      <c r="P74" s="93"/>
-      <c r="Q74" s="93"/>
-    </row>
-    <row r="75" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B75" s="140"/>
-      <c r="C75" s="93"/>
-      <c r="D75" s="93"/>
-      <c r="E75" s="93"/>
-      <c r="F75" s="93"/>
-      <c r="G75" s="93"/>
-      <c r="H75" s="93"/>
-      <c r="I75" s="93"/>
-      <c r="J75" s="209"/>
-      <c r="K75" s="93"/>
-      <c r="L75" s="93"/>
-      <c r="M75" s="93"/>
-      <c r="N75" s="209"/>
-      <c r="O75" s="93"/>
-      <c r="P75" s="93"/>
-      <c r="Q75" s="93"/>
-    </row>
-    <row r="76" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B76" s="140"/>
-      <c r="C76" s="93"/>
-      <c r="D76" s="93"/>
-      <c r="E76" s="93"/>
-      <c r="F76" s="93"/>
-      <c r="G76" s="93"/>
-      <c r="H76" s="93"/>
-      <c r="I76" s="93"/>
-      <c r="J76" s="209"/>
-      <c r="K76" s="93"/>
-      <c r="L76" s="93"/>
-      <c r="M76" s="93"/>
-      <c r="N76" s="209"/>
-      <c r="O76" s="93"/>
-      <c r="P76" s="93"/>
-      <c r="Q76" s="93"/>
-    </row>
-    <row r="77" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B77" s="140"/>
-      <c r="C77" s="93"/>
-      <c r="D77" s="93"/>
-      <c r="E77" s="93"/>
-      <c r="F77" s="93"/>
-      <c r="G77" s="93"/>
-      <c r="H77" s="93"/>
-      <c r="I77" s="93"/>
-      <c r="J77" s="209"/>
-      <c r="K77" s="93"/>
-      <c r="L77" s="93"/>
-      <c r="M77" s="93"/>
-      <c r="N77" s="209"/>
-      <c r="O77" s="93"/>
-      <c r="P77" s="93"/>
-      <c r="Q77" s="93"/>
-    </row>
-    <row r="78" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B78" s="140"/>
-      <c r="C78" s="93"/>
-      <c r="D78" s="93"/>
-      <c r="E78" s="93"/>
-      <c r="F78" s="93"/>
-      <c r="G78" s="93"/>
-      <c r="H78" s="93"/>
-      <c r="I78" s="93"/>
-      <c r="J78" s="209"/>
-      <c r="K78" s="93"/>
-      <c r="L78" s="93"/>
-      <c r="M78" s="93"/>
-      <c r="N78" s="209"/>
-      <c r="O78" s="93"/>
-      <c r="P78" s="93"/>
-      <c r="Q78" s="93"/>
-    </row>
-    <row r="79" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B79" s="140"/>
-      <c r="C79" s="93"/>
-      <c r="D79" s="93"/>
-      <c r="E79" s="93"/>
-      <c r="F79" s="93"/>
-      <c r="G79" s="93"/>
-      <c r="H79" s="93"/>
-      <c r="I79" s="93"/>
-      <c r="J79" s="209"/>
-      <c r="K79" s="93"/>
-      <c r="L79" s="93"/>
-      <c r="M79" s="93"/>
-      <c r="N79" s="209"/>
-      <c r="O79" s="93"/>
-      <c r="P79" s="93"/>
-      <c r="Q79" s="93"/>
-    </row>
-    <row r="80" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B80" s="140"/>
-      <c r="C80" s="93"/>
-      <c r="D80" s="93"/>
-      <c r="E80" s="93"/>
-      <c r="F80" s="93"/>
-      <c r="G80" s="93"/>
-      <c r="H80" s="93"/>
-      <c r="I80" s="93"/>
-      <c r="J80" s="209"/>
-      <c r="K80" s="93"/>
-      <c r="L80" s="93"/>
-      <c r="M80" s="93"/>
-      <c r="N80" s="209"/>
-      <c r="O80" s="93"/>
-      <c r="P80" s="93"/>
-      <c r="Q80" s="93"/>
-    </row>
-    <row r="81" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B81" s="140"/>
-      <c r="C81" s="93"/>
-      <c r="D81" s="93"/>
-      <c r="E81" s="93"/>
-      <c r="F81" s="93"/>
-      <c r="G81" s="93"/>
-      <c r="H81" s="93"/>
-      <c r="I81" s="93"/>
-      <c r="J81" s="209"/>
-      <c r="K81" s="93"/>
-      <c r="L81" s="93"/>
-      <c r="M81" s="93"/>
-      <c r="N81" s="209"/>
-      <c r="O81" s="93"/>
-      <c r="P81" s="93"/>
-      <c r="Q81" s="93"/>
-    </row>
-    <row r="82" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B82" s="140"/>
-      <c r="C82" s="93"/>
-      <c r="D82" s="93"/>
-      <c r="E82" s="93"/>
-      <c r="F82" s="93"/>
-      <c r="G82" s="93"/>
-      <c r="H82" s="93"/>
-      <c r="I82" s="93"/>
-      <c r="J82" s="209"/>
-      <c r="K82" s="93"/>
-      <c r="L82" s="93"/>
-      <c r="M82" s="93"/>
-      <c r="N82" s="209"/>
-      <c r="O82" s="93"/>
-      <c r="P82" s="93"/>
-      <c r="Q82" s="93"/>
-    </row>
-    <row r="83" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B83" s="140"/>
-      <c r="C83" s="93"/>
-      <c r="D83" s="93"/>
-      <c r="E83" s="93"/>
-      <c r="F83" s="93"/>
-      <c r="G83" s="93"/>
-      <c r="H83" s="93"/>
-      <c r="I83" s="93"/>
-      <c r="J83" s="209"/>
-      <c r="K83" s="93"/>
-      <c r="L83" s="93"/>
-      <c r="M83" s="93"/>
-      <c r="N83" s="209"/>
-      <c r="O83" s="93"/>
-      <c r="P83" s="93"/>
-      <c r="Q83" s="93"/>
-    </row>
-    <row r="84" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B84" s="93"/>
-      <c r="C84" s="93"/>
-      <c r="D84" s="93"/>
-      <c r="E84" s="93"/>
-      <c r="F84" s="93"/>
-      <c r="G84" s="93"/>
-      <c r="H84" s="93"/>
-      <c r="I84" s="93"/>
-      <c r="J84" s="209"/>
-      <c r="K84" s="93"/>
-      <c r="L84" s="93"/>
-      <c r="M84" s="93"/>
-      <c r="N84" s="209"/>
-      <c r="O84" s="93"/>
-      <c r="P84" s="93"/>
-      <c r="Q84" s="93"/>
-    </row>
-    <row r="85" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B85" s="93"/>
-      <c r="C85" s="93"/>
-      <c r="D85" s="93"/>
-      <c r="E85" s="93"/>
-      <c r="F85" s="93"/>
-      <c r="G85" s="93"/>
-      <c r="H85" s="93"/>
-      <c r="I85" s="93"/>
-      <c r="J85" s="209"/>
-      <c r="K85" s="93"/>
-      <c r="L85" s="93"/>
-      <c r="M85" s="93"/>
-      <c r="N85" s="209"/>
-      <c r="O85" s="93"/>
-      <c r="P85" s="93"/>
-      <c r="Q85" s="93"/>
-    </row>
-    <row r="86" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B86" s="93"/>
-      <c r="C86" s="93"/>
-      <c r="D86" s="93"/>
-      <c r="E86" s="93"/>
-      <c r="F86" s="93"/>
-      <c r="G86" s="93"/>
-      <c r="H86" s="93"/>
-      <c r="I86" s="93"/>
-      <c r="J86" s="209"/>
-      <c r="K86" s="93"/>
-      <c r="L86" s="93"/>
-      <c r="M86" s="93"/>
-      <c r="N86" s="209"/>
-      <c r="O86" s="93"/>
-      <c r="P86" s="93"/>
-      <c r="Q86" s="93"/>
-    </row>
-    <row r="87" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B87" s="93"/>
-      <c r="C87" s="93"/>
-      <c r="D87" s="93"/>
-      <c r="E87" s="93"/>
-      <c r="F87" s="93"/>
-      <c r="G87" s="93"/>
-      <c r="H87" s="93"/>
-      <c r="I87" s="93"/>
-      <c r="J87" s="209"/>
-      <c r="K87" s="93"/>
-      <c r="L87" s="93"/>
-      <c r="M87" s="93"/>
-      <c r="N87" s="209"/>
-      <c r="O87" s="93"/>
-      <c r="P87" s="93"/>
-      <c r="Q87" s="93"/>
-    </row>
-    <row r="88" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B88" s="93"/>
-      <c r="C88" s="93"/>
-      <c r="D88" s="93"/>
-      <c r="E88" s="93"/>
-      <c r="F88" s="93"/>
-      <c r="G88" s="93"/>
-      <c r="H88" s="93"/>
-      <c r="I88" s="93"/>
-      <c r="J88" s="209"/>
-      <c r="K88" s="93"/>
-      <c r="L88" s="93"/>
-      <c r="M88" s="93"/>
-      <c r="N88" s="209"/>
-      <c r="O88" s="93"/>
-      <c r="P88" s="93"/>
-      <c r="Q88" s="93"/>
-    </row>
-    <row r="89" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B89" s="93"/>
-      <c r="C89" s="93"/>
-      <c r="D89" s="93"/>
-      <c r="E89" s="93"/>
-      <c r="F89" s="93"/>
-      <c r="G89" s="93"/>
-      <c r="H89" s="93"/>
-      <c r="I89" s="93"/>
-      <c r="J89" s="209"/>
-      <c r="K89" s="93"/>
-      <c r="L89" s="93"/>
-      <c r="M89" s="93"/>
-      <c r="N89" s="209"/>
-      <c r="O89" s="93"/>
-      <c r="P89" s="93"/>
-      <c r="Q89" s="93"/>
-    </row>
-    <row r="90" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B90" s="93"/>
-      <c r="C90" s="93"/>
-      <c r="D90" s="93"/>
-      <c r="E90" s="93"/>
-      <c r="F90" s="93"/>
-      <c r="G90" s="93"/>
-      <c r="H90" s="93"/>
-      <c r="I90" s="93"/>
-      <c r="J90" s="209"/>
-      <c r="K90" s="93"/>
-      <c r="L90" s="93"/>
-      <c r="M90" s="93"/>
-      <c r="N90" s="209"/>
-      <c r="O90" s="93"/>
-      <c r="P90" s="93"/>
-      <c r="Q90" s="93"/>
-    </row>
-    <row r="91" spans="2:17" hidden="1" outlineLevel="1">
-      <c r="B91" s="93"/>
-      <c r="C91" s="93"/>
-      <c r="D91" s="93"/>
-      <c r="E91" s="93"/>
-      <c r="F91" s="93"/>
-      <c r="G91" s="93"/>
-      <c r="H91" s="93"/>
-      <c r="I91" s="93"/>
-      <c r="J91" s="209"/>
-      <c r="K91" s="93"/>
-      <c r="L91" s="93"/>
-      <c r="M91" s="93"/>
-      <c r="N91" s="209"/>
-      <c r="O91" s="93"/>
-      <c r="P91" s="93"/>
-      <c r="Q91" s="93"/>
-    </row>
     <row r="92" spans="2:17" outlineLevel="1">
       <c r="B92" s="140">
         <v>45924</v>
@@ -43178,7 +43188,7 @@
       </c>
       <c r="Q92" s="93"/>
     </row>
-    <row r="94" spans="2:17" ht="15.9">
+    <row r="94" spans="2:17" ht="16">
       <c r="B94" s="170" t="s">
         <v>305</v>
       </c>
@@ -43226,7 +43236,7 @@
       <c r="D101" s="112"/>
     </row>
     <row r="102" spans="2:8" collapsed="1"/>
-    <row r="103" spans="2:8" ht="15.9">
+    <row r="103" spans="2:8" ht="16">
       <c r="B103" s="170" t="s">
         <v>309</v>
       </c>
@@ -43416,19 +43426,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB9F31C-0119-46C0-8F67-C5ACB8A1CECF}">
   <dimension ref="B1:R121"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="2" max="2" width="38.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.15234375" customWidth="1"/>
-    <col min="5" max="5" width="18.3046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.4609375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.4609375" customWidth="1"/>
-    <col min="11" max="11" width="76.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.1640625" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.5" customWidth="1"/>
+    <col min="11" max="11" width="76.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12">
@@ -43436,7 +43446,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="2:12" ht="15" thickBot="1">
+    <row r="2" spans="2:12" ht="16" thickBot="1">
       <c r="J2" t="s">
         <v>196</v>
       </c>
@@ -43447,7 +43457,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="26.8" customHeight="1" thickBot="1">
+    <row r="3" spans="2:12" ht="26.75" customHeight="1" thickBot="1">
       <c r="B3" s="373" t="s">
         <v>198</v>
       </c>
@@ -43464,7 +43474,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="17.8" customHeight="1">
+    <row r="4" spans="2:12" ht="17.75" customHeight="1">
       <c r="B4" s="245" t="s">
         <v>201</v>
       </c>
@@ -43824,7 +43834,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="26" spans="2:10" ht="15.9">
+    <row r="26" spans="2:10" ht="16">
       <c r="B26" s="170" t="s">
         <v>262</v>
       </c>
@@ -44162,7 +44172,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="63" spans="2:18" ht="15.9">
+    <row r="63" spans="2:18" ht="16">
       <c r="B63" s="170" t="s">
         <v>289</v>
       </c>
@@ -44687,7 +44697,7 @@
       <c r="Q90" s="93"/>
     </row>
     <row r="91" spans="2:17" collapsed="1"/>
-    <row r="92" spans="2:17" ht="15.9">
+    <row r="92" spans="2:17" ht="16">
       <c r="B92" s="170" t="s">
         <v>305</v>
       </c>
@@ -44735,7 +44745,7 @@
       <c r="D99" s="112"/>
     </row>
     <row r="100" spans="2:7" collapsed="1"/>
-    <row r="101" spans="2:7" ht="15.9">
+    <row r="101" spans="2:7" ht="16">
       <c r="B101" s="170" t="s">
         <v>309</v>
       </c>
@@ -44923,19 +44933,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF8B2B9-FD87-4A94-9AEB-E9283CB14C93}">
   <dimension ref="B1:R125"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="2" max="2" width="38.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.15234375" customWidth="1"/>
-    <col min="5" max="5" width="18.3046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.4609375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.4609375" customWidth="1"/>
-    <col min="11" max="11" width="76.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.1640625" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.5" customWidth="1"/>
+    <col min="11" max="11" width="76.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12">
@@ -44943,7 +44953,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="2:12" ht="15" thickBot="1">
+    <row r="2" spans="2:12" ht="16" thickBot="1">
       <c r="J2" t="s">
         <v>196</v>
       </c>
@@ -44954,7 +44964,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="26.8" customHeight="1" thickBot="1">
+    <row r="3" spans="2:12" ht="26.75" customHeight="1" thickBot="1">
       <c r="B3" s="373" t="s">
         <v>161</v>
       </c>
@@ -44971,7 +44981,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="17.8" customHeight="1">
+    <row r="4" spans="2:12" ht="17.75" customHeight="1">
       <c r="B4" s="245" t="s">
         <v>201</v>
       </c>
@@ -45333,7 +45343,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="26" spans="2:10" ht="15.9">
+    <row r="26" spans="2:10" ht="16">
       <c r="B26" s="170" t="s">
         <v>262</v>
       </c>
@@ -45726,7 +45736,7 @@
       </c>
     </row>
     <row r="64" spans="4:4" outlineLevel="1"/>
-    <row r="67" spans="2:18" ht="15.9">
+    <row r="67" spans="2:18" ht="16">
       <c r="B67" s="170" t="s">
         <v>289</v>
       </c>
@@ -46250,7 +46260,7 @@
       <c r="P94" s="93"/>
       <c r="Q94" s="93"/>
     </row>
-    <row r="96" spans="2:17" ht="15.9">
+    <row r="96" spans="2:17" ht="16">
       <c r="B96" s="170" t="s">
         <v>305</v>
       </c>
@@ -46298,7 +46308,7 @@
       <c r="D103" s="112"/>
     </row>
     <row r="104" spans="2:7" collapsed="1"/>
-    <row r="105" spans="2:7" ht="15.9">
+    <row r="105" spans="2:7" ht="16">
       <c r="B105" s="170" t="s">
         <v>309</v>
       </c>
@@ -46485,13 +46495,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{882CF2B3-0C14-47D1-AE58-BD1F630F455B}">
   <dimension ref="B1:Q131"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="0.69140625" customWidth="1"/>
-    <col min="2" max="2" width="47.3046875" customWidth="1"/>
-    <col min="3" max="6" width="27.69140625" customWidth="1"/>
-    <col min="7" max="7" width="32.4609375" customWidth="1"/>
-    <col min="8" max="17" width="27.69140625" customWidth="1"/>
+    <col min="1" max="1" width="0.6640625" customWidth="1"/>
+    <col min="2" max="2" width="47.33203125" customWidth="1"/>
+    <col min="3" max="6" width="27.6640625" customWidth="1"/>
+    <col min="7" max="7" width="32.5" customWidth="1"/>
+    <col min="8" max="17" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10">
@@ -46499,8 +46509,8 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="2:10" ht="15" thickBot="1"/>
-    <row r="3" spans="2:10" ht="26.8" customHeight="1" thickBot="1">
+    <row r="2" spans="2:10" ht="16" thickBot="1"/>
+    <row r="3" spans="2:10" ht="26.75" customHeight="1" thickBot="1">
       <c r="B3" s="373" t="s">
         <v>133</v>
       </c>
@@ -46514,7 +46524,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="17.8" customHeight="1">
+    <row r="4" spans="2:10" ht="17.75" customHeight="1">
       <c r="B4" s="245" t="s">
         <v>201</v>
       </c>
@@ -46813,7 +46823,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="26" spans="2:10" ht="15.9">
+    <row r="26" spans="2:10" ht="16">
       <c r="B26" s="170" t="s">
         <v>262</v>
       </c>
@@ -47709,7 +47719,7 @@
     <row r="73" spans="2:17" hidden="1">
       <c r="E73" s="218"/>
     </row>
-    <row r="74" spans="2:17" ht="15.9">
+    <row r="74" spans="2:17" ht="16">
       <c r="B74" s="170" t="s">
         <v>289</v>
       </c>
@@ -48232,7 +48242,7 @@
       <c r="P101" s="93"/>
       <c r="Q101" s="93"/>
     </row>
-    <row r="103" spans="2:17" ht="15.9">
+    <row r="103" spans="2:17" ht="16">
       <c r="B103" s="170" t="s">
         <v>305</v>
       </c>
@@ -48343,7 +48353,7 @@
     <row r="110" spans="2:17" outlineLevel="1">
       <c r="D110" s="112"/>
     </row>
-    <row r="112" spans="2:17" ht="15.9">
+    <row r="112" spans="2:17" ht="16">
       <c r="B112" s="170" t="s">
         <v>309</v>
       </c>
@@ -48547,24 +48557,24 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8346539B-52A5-4F2A-B274-D3BCB7C15BFB}">
   <dimension ref="A1:P120"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="38.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.15234375" customWidth="1"/>
-    <col min="4" max="4" width="20.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.69140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.4609375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.3046875" customWidth="1"/>
-    <col min="11" max="11" width="16.69140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.69140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="30.15234375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.4609375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="23.3046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.33203125" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -48572,7 +48582,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1">
+    <row r="2" spans="1:11" ht="16" thickBot="1">
       <c r="I2" t="s">
         <v>196</v>
       </c>
@@ -48583,7 +48593,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="26.8" customHeight="1" thickBot="1">
+    <row r="3" spans="1:11" ht="26.75" customHeight="1" thickBot="1">
       <c r="A3" s="373" t="s">
         <v>374</v>
       </c>
@@ -48600,7 +48610,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="17.8" customHeight="1">
+    <row r="4" spans="1:11" ht="17.75" customHeight="1">
       <c r="A4" s="245" t="s">
         <v>201</v>
       </c>
@@ -48960,7 +48970,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.9">
+    <row r="26" spans="1:9" ht="16">
       <c r="A26" s="170" t="s">
         <v>262</v>
       </c>
@@ -49405,7 +49415,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="15.9">
+    <row r="62" spans="1:16" ht="16">
       <c r="A62" s="170" t="s">
         <v>289</v>
       </c>
@@ -49944,7 +49954,7 @@
       <c r="O89" s="93"/>
       <c r="P89" s="93"/>
     </row>
-    <row r="91" spans="1:16" ht="15.9">
+    <row r="91" spans="1:16" ht="16">
       <c r="A91" s="170" t="s">
         <v>305</v>
       </c>
@@ -49992,7 +50002,7 @@
       <c r="C98" s="112"/>
     </row>
     <row r="99" spans="1:6" collapsed="1"/>
-    <row r="100" spans="1:6" ht="15.9">
+    <row r="100" spans="1:6" ht="16">
       <c r="A100" s="170" t="s">
         <v>309</v>
       </c>
